--- a/Financial Analysis/FOUR.xlsx
+++ b/Financial Analysis/FOUR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400851A3-D9F8-4158-B41F-C7C4F0F8B80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8302343E-EC7F-49AD-996D-703DB5C52945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9FA048E8-CD64-4FE4-A115-46129781B051}"/>
   </bookViews>
@@ -746,14 +746,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>82.36</v>
+        <v>90.43</v>
       </c>
       <c r="E3" s="3">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45867</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>7338.2759999999998</v>
+        <v>8057.3130000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>9014.4760000000006</v>
+        <v>9733.5130000000008</v>
       </c>
     </row>
   </sheetData>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AO35" s="4">
         <f>Main!D3</f>
-        <v>82.36</v>
+        <v>90.43</v>
       </c>
     </row>
     <row r="36" spans="2:41" x14ac:dyDescent="0.3">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AO36" s="10">
         <f>AO34/AO35-1</f>
-        <v>-0.35523475844729624</v>
+        <v>-0.41277379968726446</v>
       </c>
     </row>
     <row r="37" spans="2:41" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FOUR.xlsx
+++ b/Financial Analysis/FOUR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8302343E-EC7F-49AD-996D-703DB5C52945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB4335F-B45E-445C-AE42-7D724302729A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9FA048E8-CD64-4FE4-A115-46129781B051}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>FOUR</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Overvalued</t>
+  </si>
+  <si>
+    <t>Debt expense</t>
   </si>
 </sst>
 </file>
@@ -284,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -302,6 +305,8 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -323,15 +328,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -347,8 +352,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9982200" y="7620"/>
-          <a:ext cx="0" cy="7231380"/>
+          <a:off x="10591800" y="7620"/>
+          <a:ext cx="0" cy="7414260"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -381,7 +386,7 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -746,17 +751,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>90.43</v>
+        <v>86.88</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45875</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45875</v>
       </c>
       <c r="G3" s="3">
-        <v>45867</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,11 +769,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>67.8+19.8+1.5</f>
-        <v>89.1</v>
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,7 +782,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>8057.3130000000001</v>
+        <v>7680.1919999999991</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,11 +790,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="5">
-        <f>1167.3</f>
-        <v>1167.3</v>
+        <f>3029.3</f>
+        <v>3029.3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -797,11 +802,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="5">
-        <f>687.8+2155.7</f>
-        <v>2843.5</v>
+        <f>688.6+3043.2</f>
+        <v>3731.7999999999997</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -810,7 +815,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-1676.2</v>
+        <v>-702.49999999999955</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +824,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>9733.5130000000008</v>
+        <v>8382.6919999999991</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33074867-C015-4EB5-A6A7-44303FBA5A30}">
-  <dimension ref="B2:EP37"/>
+  <dimension ref="B2:EP38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -970,8 +975,7 @@
         <v>848.3</v>
       </c>
       <c r="P3" s="8">
-        <f>L3*1.15</f>
-        <v>951.05</v>
+        <v>966.2</v>
       </c>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:R3" si="0">M3*1.15</f>
@@ -991,47 +995,47 @@
       </c>
       <c r="AA3" s="8">
         <f>SUM(O3:R3)</f>
-        <v>3864.9799999999996</v>
+        <v>3880.13</v>
       </c>
       <c r="AB3" s="8">
         <f>AA3*1.11</f>
-        <v>4290.1278000000002</v>
+        <v>4306.9443000000001</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.07</f>
-        <v>4590.4367460000003</v>
+        <v>4608.4304010000005</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.05</f>
-        <v>4819.9585833000001</v>
+        <v>4838.8519210500008</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.04</f>
-        <v>5012.7569266320006</v>
+        <v>5032.4059978920013</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.03</f>
-        <v>5163.1396344309605</v>
+        <v>5183.3781778287612</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.03</f>
-        <v>5318.0338234638893</v>
+        <v>5338.8795231636241</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AK3" si="1">AG3*1.03</f>
-        <v>5477.5748381678059</v>
+        <v>5499.045908858533</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="1"/>
-        <v>5641.9020833128397</v>
+        <v>5664.0172861242891</v>
       </c>
       <c r="AJ3" s="8">
         <f t="shared" si="1"/>
-        <v>5811.1591458122248</v>
+        <v>5833.9378047080181</v>
       </c>
       <c r="AK3" s="8">
         <f t="shared" si="1"/>
-        <v>5985.4939201865918</v>
+        <v>6008.9559388492589</v>
       </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.3">
@@ -1066,16 +1070,15 @@
         <v>591.29999999999995</v>
       </c>
       <c r="P4" s="5">
-        <f t="shared" ref="P4:R4" si="2">P3-P5</f>
-        <v>646.71399999999994</v>
+        <v>673.7</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" si="2"/>
-        <v>700.53859999999986</v>
+        <f t="shared" ref="Q4:R4" si="2">Q3-Q5</f>
+        <v>721.4502</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="2"/>
-        <v>673.23299999999995</v>
+        <v>693.63400000000001</v>
       </c>
       <c r="Y4" s="5">
         <f>SUM(G4:J4)</f>
@@ -1087,47 +1090,47 @@
       </c>
       <c r="AA4" s="5">
         <f>SUM(O4:R4)</f>
-        <v>2611.7855999999997</v>
+        <v>2680.0842000000002</v>
       </c>
       <c r="AB4" s="5">
         <f>AB3-AB5</f>
-        <v>2831.484348</v>
+        <v>2928.7221239999999</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" ref="AC4:AK4" si="3">AC3-AC5</f>
-        <v>2937.8795174400002</v>
+        <v>3087.6483686700003</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="3"/>
-        <v>3036.5739074789999</v>
+        <v>3242.0307871035002</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="3"/>
-        <v>3107.9092945118405</v>
+        <v>3371.7120185876411</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="3"/>
-        <v>3149.515177002886</v>
+        <v>3472.8633791452698</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="3"/>
-        <v>3190.8202940783335</v>
+        <v>3577.0492805196282</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="3"/>
-        <v>3286.5449029006836</v>
+        <v>3684.3607589352168</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="3"/>
-        <v>3385.1412499877038</v>
+        <v>3794.8915817032739</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="3"/>
-        <v>3486.695487487335</v>
+        <v>3908.738329154372</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="3"/>
-        <v>3591.296352111955</v>
+        <v>4026.0004790290031</v>
       </c>
     </row>
     <row r="5" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1135,7 +1138,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:O5" si="4">G3-G4</f>
+        <f t="shared" ref="G5:P5" si="4">G3-G4</f>
         <v>145.39999999999998</v>
       </c>
       <c r="H5" s="8">
@@ -1171,16 +1174,16 @@
         <v>257</v>
       </c>
       <c r="P5" s="8">
-        <f>P3*0.32</f>
-        <v>304.33600000000001</v>
+        <f t="shared" si="4"/>
+        <v>292.5</v>
       </c>
       <c r="Q5" s="8">
-        <f>Q3*0.33</f>
-        <v>345.04140000000001</v>
+        <f>Q3*0.31</f>
+        <v>324.12979999999999</v>
       </c>
       <c r="R5" s="8">
-        <f>R3*0.34</f>
-        <v>346.81700000000001</v>
+        <f>R3*0.32</f>
+        <v>326.416</v>
       </c>
       <c r="Y5" s="8">
         <f>Y3-Y4</f>
@@ -1192,47 +1195,47 @@
       </c>
       <c r="AA5" s="8">
         <f>AA3-AA4</f>
-        <v>1253.1943999999999</v>
+        <v>1200.0457999999999</v>
       </c>
       <c r="AB5" s="8">
-        <f>AB3*0.34</f>
-        <v>1458.6434520000003</v>
+        <f>AB3*0.32</f>
+        <v>1378.222176</v>
       </c>
       <c r="AC5" s="8">
-        <f>AC3*0.36</f>
-        <v>1652.5572285600001</v>
+        <f>AC3*0.33</f>
+        <v>1520.7820323300002</v>
       </c>
       <c r="AD5" s="8">
-        <f>AD3*0.37</f>
-        <v>1783.384675821</v>
+        <f t="shared" ref="AD5:AK5" si="5">AD3*0.33</f>
+        <v>1596.8211339465004</v>
       </c>
       <c r="AE5" s="8">
-        <f>AE3*0.38</f>
-        <v>1904.8476321201601</v>
+        <f t="shared" si="5"/>
+        <v>1660.6939793043605</v>
       </c>
       <c r="AF5" s="8">
-        <f>AF3*0.39</f>
-        <v>2013.6244574280747</v>
+        <f t="shared" si="5"/>
+        <v>1710.5147986834913</v>
       </c>
       <c r="AG5" s="8">
-        <f>AG3*0.4</f>
-        <v>2127.2135293855558</v>
+        <f t="shared" si="5"/>
+        <v>1761.8302426439959</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" ref="AH5:AK5" si="5">AH3*0.4</f>
-        <v>2191.0299352671223</v>
+        <f t="shared" si="5"/>
+        <v>1814.685149923316</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="5"/>
-        <v>2256.760833325136</v>
+        <v>1869.1257044210154</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="5"/>
-        <v>2324.4636583248898</v>
+        <v>1925.1994755536462</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="5"/>
-        <v>2394.1975680746368</v>
+        <v>1982.9554598202556</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.3">
@@ -1267,68 +1270,67 @@
         <v>154</v>
       </c>
       <c r="P6" s="5">
-        <f t="shared" ref="P6:R6" si="6">L6*1.3</f>
-        <v>143.13</v>
+        <v>130.4</v>
       </c>
       <c r="Q6" s="5">
-        <f t="shared" si="6"/>
-        <v>153.66</v>
+        <f>M6*1.2</f>
+        <v>141.84</v>
       </c>
       <c r="R6" s="5">
-        <f t="shared" si="6"/>
-        <v>161.32999999999998</v>
+        <f>N6*1.2</f>
+        <v>148.91999999999999</v>
       </c>
       <c r="Y6" s="5">
-        <f t="shared" ref="Y6:Y11" si="7">SUM(G6:J6)</f>
+        <f t="shared" ref="Y6:Y11" si="6">SUM(G6:J6)</f>
         <v>329.3</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" ref="Z6:Z11" si="8">SUM(K6:N6)</f>
+        <f t="shared" ref="Z6:Z11" si="7">SUM(K6:N6)</f>
         <v>459.5</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AA11" si="9">SUM(O6:R6)</f>
-        <v>612.11999999999989</v>
+        <f t="shared" ref="AA6:AA11" si="8">SUM(O6:R6)</f>
+        <v>575.16</v>
       </c>
       <c r="AB6" s="5">
-        <f>AA6*1.2</f>
-        <v>734.54399999999987</v>
+        <f>AA6*1.12</f>
+        <v>644.17920000000004</v>
       </c>
       <c r="AC6" s="5">
-        <f>AB6*1.1</f>
-        <v>807.99839999999995</v>
+        <f>AB6*1.07</f>
+        <v>689.27174400000013</v>
       </c>
       <c r="AD6" s="5">
-        <f>AC6*1.05</f>
-        <v>848.39832000000001</v>
+        <f>AC6*1.04</f>
+        <v>716.84261376000018</v>
       </c>
       <c r="AE6" s="5">
-        <f>AD6*1.04</f>
-        <v>882.33425280000006</v>
+        <f>AD6*1.03</f>
+        <v>738.34789217280024</v>
       </c>
       <c r="AF6" s="5">
-        <f>AE6*1.03</f>
-        <v>908.80428038400009</v>
+        <f>AE6*1.02</f>
+        <v>753.11485001625624</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.02</f>
-        <v>926.98036599168006</v>
+        <v>768.17714701658133</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH6:AK6" si="10">AG6*1.02</f>
-        <v>945.5199733115137</v>
+        <f t="shared" ref="AH6:AK6" si="9">AG6*1.02</f>
+        <v>783.54068995691296</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="10"/>
-        <v>964.43037277774397</v>
+        <f t="shared" si="9"/>
+        <v>799.21150375605123</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="10"/>
-        <v>983.71898023329891</v>
+        <f t="shared" si="9"/>
+        <v>815.19573383117222</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="10"/>
-        <v>1003.3933598379649</v>
+        <f t="shared" si="9"/>
+        <v>831.49964850779565</v>
       </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.3">
@@ -1363,7 +1365,7 @@
         <v>-3.7</v>
       </c>
       <c r="P7" s="5">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="Q7" s="5">
         <v>0</v>
@@ -1372,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="Y7" s="5">
+        <f t="shared" si="6"/>
+        <v>23.1</v>
+      </c>
+      <c r="Z7" s="5">
         <f t="shared" si="7"/>
-        <v>23.1</v>
-      </c>
-      <c r="Z7" s="5">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="5">
         <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="AA7" s="5">
-        <f t="shared" si="9"/>
-        <v>-3.7</v>
+        <v>-4.6000000000000005</v>
       </c>
       <c r="AB7" s="5">
         <v>0</v>
@@ -1446,28 +1448,27 @@
         <v>56</v>
       </c>
       <c r="P8" s="5">
-        <f t="shared" ref="P8:R8" si="11">L8*1.3</f>
-        <v>60.710000000000008</v>
+        <v>57.6</v>
       </c>
       <c r="Q8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="Q8:R8" si="10">M8*1.3</f>
         <v>67.08</v>
       </c>
       <c r="R8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>73.320000000000007</v>
       </c>
       <c r="Y8" s="5">
+        <f t="shared" si="6"/>
+        <v>153.79999999999998</v>
+      </c>
+      <c r="Z8" s="5">
         <f t="shared" si="7"/>
-        <v>153.79999999999998</v>
-      </c>
-      <c r="Z8" s="5">
+        <v>199.5</v>
+      </c>
+      <c r="AA8" s="5">
         <f t="shared" si="8"/>
-        <v>199.5</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="9"/>
-        <v>257.11</v>
+        <v>254</v>
       </c>
       <c r="AB8" s="5">
         <v>0</v>
@@ -1532,7 +1533,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="P9" s="5">
-        <v>18.600000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="Q9" s="5">
         <v>18.600000000000001</v>
@@ -1541,56 +1542,56 @@
         <v>18.600000000000001</v>
       </c>
       <c r="Y9" s="5">
+        <f t="shared" si="6"/>
+        <v>33.1</v>
+      </c>
+      <c r="Z9" s="5">
         <f t="shared" si="7"/>
-        <v>33.1</v>
-      </c>
-      <c r="Z9" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="AA9" s="5">
         <f t="shared" si="8"/>
-        <v>41.4</v>
-      </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="9"/>
-        <v>74.400000000000006</v>
+        <v>71</v>
       </c>
       <c r="AB9" s="5">
         <f>AB3*0.02</f>
-        <v>85.80255600000001</v>
+        <v>86.138885999999999</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" ref="AC9:AK9" si="12">AC3*0.02</f>
-        <v>91.808734920000006</v>
+        <f t="shared" ref="AC9:AK9" si="11">AC3*0.02</f>
+        <v>92.168608020000008</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="12"/>
-        <v>96.399171666000001</v>
+        <f t="shared" si="11"/>
+        <v>96.777038421000015</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" si="12"/>
-        <v>100.25513853264002</v>
+        <f t="shared" si="11"/>
+        <v>100.64811995784002</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="12"/>
-        <v>103.26279268861921</v>
+        <f t="shared" si="11"/>
+        <v>103.66756355657523</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="12"/>
-        <v>106.36067646927779</v>
+        <f t="shared" si="11"/>
+        <v>106.77759046327249</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="12"/>
-        <v>109.55149676335611</v>
+        <f t="shared" si="11"/>
+        <v>109.98091817717066</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="12"/>
-        <v>112.8380416662568</v>
+        <f t="shared" si="11"/>
+        <v>113.28034572248578</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="12"/>
-        <v>116.2231829162445</v>
+        <f t="shared" si="11"/>
+        <v>116.67875609416036</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="12"/>
-        <v>119.70987840373184</v>
+        <f t="shared" si="11"/>
+        <v>120.17911877698518</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.3">
@@ -1625,68 +1626,67 @@
         <v>6.7</v>
       </c>
       <c r="P10" s="5">
-        <f t="shared" ref="P10:R10" si="13">P3*0.008</f>
-        <v>7.6083999999999996</v>
+        <v>7.1</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="Q10:R10" si="12">Q3*0.008</f>
         <v>8.3646399999999996</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>8.1603999999999992</v>
       </c>
       <c r="Y10" s="5">
+        <f t="shared" si="6"/>
+        <v>15.1</v>
+      </c>
+      <c r="Z10" s="5">
         <f t="shared" si="7"/>
-        <v>15.1</v>
-      </c>
-      <c r="Z10" s="5">
+        <v>21.7</v>
+      </c>
+      <c r="AA10" s="5">
         <f t="shared" si="8"/>
-        <v>21.7</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="9"/>
-        <v>30.83344</v>
+        <v>30.325039999999998</v>
       </c>
       <c r="AB10" s="5">
         <f>AB3*0.008</f>
-        <v>34.321022400000004</v>
+        <v>34.455554400000004</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" ref="AC10:AK10" si="14">AC3*0.008</f>
-        <v>36.723493968000007</v>
+        <f t="shared" ref="AC10:AK10" si="13">AC3*0.008</f>
+        <v>36.867443208000005</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="14"/>
-        <v>38.5596686664</v>
+        <f t="shared" si="13"/>
+        <v>38.710815368400006</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="14"/>
-        <v>40.102055413056007</v>
+        <f t="shared" si="13"/>
+        <v>40.259247983136014</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="14"/>
-        <v>41.305117075447683</v>
+        <f t="shared" si="13"/>
+        <v>41.467025422630087</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="14"/>
-        <v>42.544270587711118</v>
+        <f t="shared" si="13"/>
+        <v>42.711036185308991</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="14"/>
-        <v>43.820598705342448</v>
+        <f t="shared" si="13"/>
+        <v>43.992367270868264</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="14"/>
-        <v>45.135216666502721</v>
+        <f t="shared" si="13"/>
+        <v>45.312138288994312</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="14"/>
-        <v>46.489273166497796</v>
+        <f t="shared" si="13"/>
+        <v>46.671502437664145</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="14"/>
-        <v>47.883951361492734</v>
+        <f t="shared" si="13"/>
+        <v>48.071647510794072</v>
       </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.3">
@@ -1730,15 +1730,15 @@
         <v>0</v>
       </c>
       <c r="Y11" s="5">
+        <f t="shared" si="6"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="Z11" s="5">
         <f t="shared" si="7"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB11" s="5">
@@ -1777,52 +1777,52 @@
         <v>47</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" ref="G12:N12" si="15">SUM(G6:G11)</f>
+        <f t="shared" ref="G12:N12" si="14">SUM(G6:G11)</f>
         <v>136.6</v>
       </c>
       <c r="H12" s="5">
+        <f t="shared" si="14"/>
+        <v>133</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="14"/>
+        <v>135.6</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="14"/>
+        <v>167.8</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="14"/>
+        <v>166.4</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="14"/>
+        <v>172.6</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="14"/>
+        <v>186.9</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="14"/>
+        <v>200.2</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" ref="O12:R12" si="15">SUM(O6:O11)</f>
+        <v>231.6</v>
+      </c>
+      <c r="P12" s="5">
         <f t="shared" si="15"/>
-        <v>133</v>
-      </c>
-      <c r="I12" s="5">
+        <v>209.39999999999998</v>
+      </c>
+      <c r="Q12" s="5">
         <f t="shared" si="15"/>
-        <v>135.6</v>
-      </c>
-      <c r="J12" s="5">
+        <v>235.88464000000002</v>
+      </c>
+      <c r="R12" s="5">
         <f t="shared" si="15"/>
-        <v>167.8</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="15"/>
-        <v>166.4</v>
-      </c>
-      <c r="L12" s="5">
-        <f t="shared" si="15"/>
-        <v>172.6</v>
-      </c>
-      <c r="M12" s="5">
-        <f t="shared" si="15"/>
-        <v>186.9</v>
-      </c>
-      <c r="N12" s="5">
-        <f t="shared" si="15"/>
-        <v>200.2</v>
-      </c>
-      <c r="O12" s="5">
-        <f t="shared" ref="O12:R12" si="16">SUM(O6:O11)</f>
-        <v>231.6</v>
-      </c>
-      <c r="P12" s="5">
-        <f t="shared" si="16"/>
-        <v>230.04839999999999</v>
-      </c>
-      <c r="Q12" s="5">
-        <f t="shared" si="16"/>
-        <v>247.70464000000001</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="16"/>
-        <v>261.41039999999998</v>
+        <v>249.00040000000001</v>
       </c>
       <c r="Y12" s="5">
         <f>SUM(Y6:Y11)</f>
@@ -1834,47 +1834,47 @@
       </c>
       <c r="AA12" s="5">
         <f>SUM(AA6:AA11)</f>
-        <v>970.76343999999983</v>
+        <v>925.88503999999989</v>
       </c>
       <c r="AB12" s="5">
         <f>SUM(AB6:AB11)</f>
-        <v>854.66757839999991</v>
+        <v>764.77364039999998</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" ref="AC12:AK12" si="17">SUM(AC6:AC11)</f>
-        <v>936.53062888799991</v>
+        <f t="shared" ref="AC12:AK12" si="16">SUM(AC6:AC11)</f>
+        <v>818.30779522800015</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="17"/>
-        <v>983.3571603324001</v>
+        <f t="shared" si="16"/>
+        <v>852.33046754940028</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="17"/>
-        <v>1022.6914467456961</v>
+        <f t="shared" si="16"/>
+        <v>879.25526011377622</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="17"/>
-        <v>1053.3721901480669</v>
+        <f t="shared" si="16"/>
+        <v>898.24943899546156</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="17"/>
-        <v>1075.8853130486689</v>
+        <f t="shared" si="16"/>
+        <v>917.66577366516287</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="17"/>
-        <v>1098.8920687802124</v>
+        <f t="shared" si="16"/>
+        <v>937.51397540495191</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="17"/>
-        <v>1122.4036311105035</v>
+        <f t="shared" si="16"/>
+        <v>957.80398776753134</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="17"/>
-        <v>1146.4314363160411</v>
+        <f t="shared" si="16"/>
+        <v>978.54599236299669</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="17"/>
-        <v>1170.9871896031896</v>
+        <f t="shared" si="16"/>
+        <v>999.7504147955749</v>
       </c>
     </row>
     <row r="13" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1882,52 +1882,52 @@
         <v>20</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" ref="G13:N13" si="18">G5-G12</f>
+        <f t="shared" ref="G13:N13" si="17">G5-G12</f>
         <v>8.7999999999999829</v>
       </c>
       <c r="H13" s="8">
+        <f t="shared" si="17"/>
+        <v>33.899999999999977</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="17"/>
+        <v>44.69999999999996</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="17"/>
+        <v>27.399999999999977</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="17"/>
+        <v>21.399999999999949</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="17"/>
+        <v>59.19999999999996</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" si="17"/>
+        <v>80.400000000000063</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="17"/>
+        <v>86.000000000000057</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" ref="O13:R13" si="18">O5-O12</f>
+        <v>25.400000000000006</v>
+      </c>
+      <c r="P13" s="8">
         <f t="shared" si="18"/>
-        <v>33.899999999999977</v>
-      </c>
-      <c r="I13" s="8">
+        <v>83.100000000000023</v>
+      </c>
+      <c r="Q13" s="8">
         <f t="shared" si="18"/>
-        <v>44.69999999999996</v>
-      </c>
-      <c r="J13" s="8">
+        <v>88.24515999999997</v>
+      </c>
+      <c r="R13" s="8">
         <f t="shared" si="18"/>
-        <v>27.399999999999977</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="18"/>
-        <v>21.399999999999949</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="18"/>
-        <v>59.19999999999996</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" si="18"/>
-        <v>80.400000000000063</v>
-      </c>
-      <c r="N13" s="8">
-        <f t="shared" si="18"/>
-        <v>86.000000000000057</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" ref="O13:R13" si="19">O5-O12</f>
-        <v>25.400000000000006</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="19"/>
-        <v>74.287600000000026</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" si="19"/>
-        <v>97.336759999999998</v>
-      </c>
-      <c r="R13" s="8">
-        <f t="shared" si="19"/>
-        <v>85.406600000000026</v>
+        <v>77.415599999999984</v>
       </c>
       <c r="Y13" s="8">
         <f>Y5-Y12</f>
@@ -1939,261 +1939,212 @@
       </c>
       <c r="AA13" s="8">
         <f>AA5-AA12</f>
-        <v>282.43096000000003</v>
+        <v>274.16075999999998</v>
       </c>
       <c r="AB13" s="8">
         <f>AB5-AB12</f>
-        <v>603.97587360000034</v>
+        <v>613.44853560000001</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" ref="AC13:AK13" si="20">AC5-AC12</f>
-        <v>716.0265996720002</v>
+        <f t="shared" ref="AC13:AK13" si="19">AC5-AC12</f>
+        <v>702.47423710200007</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="20"/>
-        <v>800.02751548859987</v>
+        <f t="shared" si="19"/>
+        <v>744.49066639710009</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="20"/>
-        <v>882.15618537446403</v>
+        <f t="shared" si="19"/>
+        <v>781.43871919058427</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="20"/>
-        <v>960.2522672800078</v>
+        <f t="shared" si="19"/>
+        <v>812.26535968802978</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="20"/>
-        <v>1051.328216336887</v>
+        <f t="shared" si="19"/>
+        <v>844.16446897883304</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="20"/>
-        <v>1092.1378664869098</v>
+        <f t="shared" si="19"/>
+        <v>877.17117451836407</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="20"/>
-        <v>1134.3572022146325</v>
+        <f t="shared" si="19"/>
+        <v>911.32171665348403</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="20"/>
-        <v>1178.0322220088487</v>
+        <f t="shared" si="19"/>
+        <v>946.65348319064947</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="20"/>
-        <v>1223.2103784714473</v>
+        <f t="shared" si="19"/>
+        <v>983.20504502468066</v>
       </c>
     </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="5">
-        <v>-7.6</v>
-      </c>
-      <c r="H14" s="5">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="I14" s="5">
-        <v>-9.6</v>
-      </c>
-      <c r="J14" s="5">
-        <v>-5.9</v>
-      </c>
-      <c r="K14" s="5">
-        <v>-5.4</v>
-      </c>
-      <c r="L14" s="5">
-        <v>-5</v>
-      </c>
-      <c r="M14" s="5">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="N14" s="5">
-        <v>-13.6</v>
-      </c>
-      <c r="O14" s="5">
-        <v>-12.4</v>
-      </c>
-      <c r="P14" s="5">
-        <f t="shared" ref="P14:R14" si="21">L14*1.2</f>
-        <v>-6</v>
-      </c>
-      <c r="Q14" s="5">
-        <f t="shared" si="21"/>
-        <v>-11.639999999999999</v>
-      </c>
-      <c r="R14" s="5">
-        <f t="shared" si="21"/>
-        <v>-16.32</v>
-      </c>
-      <c r="Y14" s="5">
-        <f>SUM(G14:J14)</f>
-        <v>-31.9</v>
-      </c>
-      <c r="Z14" s="5">
-        <f>SUM(K14:N14)</f>
-        <v>-33.700000000000003</v>
-      </c>
-      <c r="AA14" s="5">
+    <row r="14" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="12">
         <f>SUM(O14:R14)</f>
-        <v>-46.36</v>
-      </c>
-      <c r="AB14" s="5">
-        <f>AA14*1.05</f>
-        <v>-48.678000000000004</v>
-      </c>
-      <c r="AC14" s="5">
-        <f t="shared" ref="AC14:AK14" si="22">AB14*1.05</f>
-        <v>-51.111900000000006</v>
-      </c>
-      <c r="AD14" s="5">
-        <f t="shared" si="22"/>
-        <v>-53.667495000000009</v>
-      </c>
-      <c r="AE14" s="5">
-        <f t="shared" si="22"/>
-        <v>-56.350869750000015</v>
-      </c>
-      <c r="AF14" s="5">
-        <f t="shared" si="22"/>
-        <v>-59.168413237500019</v>
-      </c>
-      <c r="AG14" s="5">
-        <f t="shared" si="22"/>
-        <v>-62.126833899375022</v>
-      </c>
-      <c r="AH14" s="5">
-        <f t="shared" si="22"/>
-        <v>-65.233175594343777</v>
-      </c>
-      <c r="AI14" s="5">
-        <f t="shared" si="22"/>
-        <v>-68.494834374060972</v>
-      </c>
-      <c r="AJ14" s="5">
-        <f t="shared" si="22"/>
-        <v>-71.919576092764018</v>
-      </c>
-      <c r="AK14" s="5">
-        <f t="shared" si="22"/>
-        <v>-75.515554897402225</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
     </row>
     <row r="15" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G15" s="5">
-        <v>-0.1</v>
+        <v>-7.6</v>
       </c>
       <c r="H15" s="5">
-        <v>0.4</v>
+        <v>-8.8000000000000007</v>
       </c>
       <c r="I15" s="5">
-        <v>0</v>
+        <v>-9.6</v>
       </c>
       <c r="J15" s="5">
-        <v>3.6</v>
+        <v>-5.9</v>
       </c>
       <c r="K15" s="5">
-        <v>-1.4</v>
+        <v>-5.4</v>
       </c>
       <c r="L15" s="5">
-        <v>-0.4</v>
+        <v>-5</v>
       </c>
       <c r="M15" s="5">
-        <v>1.5</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="N15" s="5">
-        <v>-1.5</v>
+        <v>-13.6</v>
       </c>
       <c r="O15" s="5">
-        <v>1.2</v>
+        <v>-12.4</v>
       </c>
       <c r="P15" s="5">
-        <v>0</v>
+        <v>-19.2</v>
       </c>
       <c r="Q15" s="5">
-        <v>0</v>
+        <f t="shared" ref="Q15:R15" si="20">M15*1.2</f>
+        <v>-11.639999999999999</v>
       </c>
       <c r="R15" s="5">
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-16.32</v>
       </c>
       <c r="Y15" s="5">
         <f>SUM(G15:J15)</f>
-        <v>3.9000000000000004</v>
+        <v>-31.9</v>
       </c>
       <c r="Z15" s="5">
         <f>SUM(K15:N15)</f>
-        <v>-1.7999999999999998</v>
+        <v>-33.700000000000003</v>
       </c>
       <c r="AA15" s="5">
         <f>SUM(O15:R15)</f>
-        <v>1.2</v>
+        <v>-59.56</v>
       </c>
       <c r="AB15" s="5">
-        <v>0</v>
+        <f>AA15*1.05</f>
+        <v>-62.538000000000004</v>
       </c>
       <c r="AC15" s="5">
-        <v>0</v>
+        <f t="shared" ref="AC15:AK15" si="21">AB15*1.05</f>
+        <v>-65.664900000000003</v>
       </c>
       <c r="AD15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-68.948145000000011</v>
       </c>
       <c r="AE15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-72.395552250000009</v>
       </c>
       <c r="AF15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-76.01532986250001</v>
       </c>
       <c r="AG15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-79.816096355625021</v>
       </c>
       <c r="AH15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-83.806901173406274</v>
       </c>
       <c r="AI15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-87.997246232076591</v>
       </c>
       <c r="AJ15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-92.397108543680432</v>
       </c>
       <c r="AK15" s="5">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>-97.016963970864452</v>
       </c>
     </row>
     <row r="16" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G16" s="5">
-        <v>-8.9</v>
+        <v>-0.1</v>
       </c>
       <c r="H16" s="5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I16" s="5">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5">
-        <v>-0.7</v>
+        <v>3.6</v>
       </c>
       <c r="K16" s="5">
-        <v>-11</v>
+        <v>-1.4</v>
       </c>
       <c r="L16" s="5">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M16" s="5">
-        <v>-10.8</v>
+        <v>1.5</v>
       </c>
       <c r="N16" s="5">
-        <v>-45.1</v>
+        <v>-1.5</v>
       </c>
       <c r="O16" s="5">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="P16" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="5">
         <v>0</v>
@@ -2203,15 +2154,15 @@
       </c>
       <c r="Y16" s="5">
         <f>SUM(G16:J16)</f>
-        <v>-12.2</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="Z16" s="5">
         <f>SUM(K16:N16)</f>
-        <v>-66.7</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="AA16" s="5">
         <f>SUM(O16:R16)</f>
-        <v>-0.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" s="5">
         <v>0</v>
@@ -2246,37 +2197,37 @@
     </row>
     <row r="17" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="5">
-        <v>0.5</v>
+        <v>-8.9</v>
       </c>
       <c r="H17" s="5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5">
-        <v>1.5</v>
+        <v>-2.6</v>
       </c>
       <c r="J17" s="5">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="K17" s="5">
-        <v>1.2</v>
+        <v>-11</v>
       </c>
       <c r="L17" s="5">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="M17" s="5">
-        <v>289.39999999999998</v>
+        <v>-10.8</v>
       </c>
       <c r="N17" s="5">
-        <v>-5.2</v>
+        <v>-45.1</v>
       </c>
       <c r="O17" s="5">
-        <v>-3</v>
+        <v>-0.3</v>
       </c>
       <c r="P17" s="5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="5">
         <v>0</v>
@@ -2286,15 +2237,15 @@
       </c>
       <c r="Y17" s="5">
         <f>SUM(G17:J17)</f>
-        <v>3.4</v>
+        <v>-12.2</v>
       </c>
       <c r="Z17" s="5">
         <f>SUM(K17:N17)</f>
-        <v>289</v>
+        <v>-66.7</v>
       </c>
       <c r="AA17" s="5">
         <f>SUM(O17:R17)</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="5">
         <v>0</v>
@@ -2329,2226 +2280,2307 @@
     </row>
     <row r="18" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" s="5">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="5">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="I18" s="5">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" s="5">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="K18" s="5">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="L18" s="5">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="M18" s="5">
-        <v>18.3</v>
+        <v>289.39999999999998</v>
       </c>
       <c r="N18" s="5">
-        <v>27.3</v>
+        <v>-5.2</v>
       </c>
       <c r="O18" s="5">
-        <v>28.5</v>
+        <v>-3</v>
       </c>
       <c r="P18" s="5">
-        <v>28.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" s="5">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="R18" s="5">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="5">
         <f>SUM(G18:J18)</f>
-        <v>32.1</v>
+        <v>3.4</v>
       </c>
       <c r="Z18" s="5">
         <f>SUM(K18:N18)</f>
-        <v>61.8</v>
+        <v>289</v>
       </c>
       <c r="AA18" s="5">
         <f>SUM(O18:R18)</f>
-        <v>114</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="AB18" s="5">
-        <f>AA18*1.03</f>
-        <v>117.42</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="5">
-        <f t="shared" ref="AC18:AK18" si="23">AB18*1.03</f>
-        <v>120.9426</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="5">
-        <f t="shared" si="23"/>
-        <v>124.57087800000001</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="5">
-        <f t="shared" si="23"/>
-        <v>128.30800434000002</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" si="23"/>
-        <v>132.15724447020003</v>
+        <v>0</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="23"/>
-        <v>136.12196180430604</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="23"/>
-        <v>140.20562065843524</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="5">
-        <f t="shared" si="23"/>
-        <v>144.41178927818831</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="23"/>
-        <v>148.74414295653395</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="5">
-        <f t="shared" si="23"/>
-        <v>153.20646724522996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>8</v>
+      </c>
+      <c r="I19" s="5">
+        <v>8</v>
+      </c>
+      <c r="J19" s="5">
+        <v>8</v>
+      </c>
+      <c r="K19" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="M19" s="5">
+        <v>18.3</v>
+      </c>
+      <c r="N19" s="5">
+        <v>27.3</v>
+      </c>
+      <c r="O19" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="P19" s="5">
+        <v>39.4</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="R19" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="Y19" s="5">
+        <f>SUM(G19:J19)</f>
+        <v>32.1</v>
+      </c>
+      <c r="Z19" s="5">
+        <f>SUM(K19:N19)</f>
+        <v>61.8</v>
+      </c>
+      <c r="AA19" s="5">
+        <f>SUM(O19:R19)</f>
+        <v>124.9</v>
+      </c>
+      <c r="AB19" s="5">
+        <f>AA19*1.03</f>
+        <v>128.64700000000002</v>
+      </c>
+      <c r="AC19" s="5">
+        <f t="shared" ref="AC19:AK19" si="22">AB19*1.03</f>
+        <v>132.50641000000002</v>
+      </c>
+      <c r="AD19" s="5">
+        <f t="shared" si="22"/>
+        <v>136.48160230000002</v>
+      </c>
+      <c r="AE19" s="5">
+        <f t="shared" si="22"/>
+        <v>140.57605036900003</v>
+      </c>
+      <c r="AF19" s="5">
+        <f t="shared" si="22"/>
+        <v>144.79333188007004</v>
+      </c>
+      <c r="AG19" s="5">
+        <f t="shared" si="22"/>
+        <v>149.13713183647215</v>
+      </c>
+      <c r="AH19" s="5">
+        <f t="shared" si="22"/>
+        <v>153.61124579156632</v>
+      </c>
+      <c r="AI19" s="5">
+        <f t="shared" si="22"/>
+        <v>158.21958316531331</v>
+      </c>
+      <c r="AJ19" s="5">
+        <f t="shared" si="22"/>
+        <v>162.96617066027272</v>
+      </c>
+      <c r="AK19" s="5">
+        <f t="shared" si="22"/>
+        <v>167.85515578008091</v>
+      </c>
+    </row>
+    <row r="20" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="5">
-        <f t="shared" ref="G19:O19" si="24">SUM(G14:G18)</f>
+      <c r="G20" s="5">
+        <f t="shared" ref="G20:O20" si="23">SUM(G15:G19)</f>
         <v>-8.0000000000000018</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H20" s="5">
+        <f t="shared" si="23"/>
+        <v>0.39999999999999947</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="23"/>
+        <v>-2.6999999999999993</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="23"/>
+        <v>5.6</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="23"/>
+        <v>-8.5000000000000018</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="23"/>
+        <v>6.5</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" si="23"/>
+        <v>288.7</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="23"/>
+        <v>-38.100000000000009</v>
+      </c>
+      <c r="O20" s="5">
+        <f t="shared" si="23"/>
+        <v>13.999999999999998</v>
+      </c>
+      <c r="P20" s="5">
+        <f>SUM(P14:P19)</f>
+        <v>27.400000000000002</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" ref="Q20:R20" si="24">SUM(Q14:Q19)</f>
+        <v>16.86</v>
+      </c>
+      <c r="R20" s="5">
         <f t="shared" si="24"/>
-        <v>0.39999999999999947</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="24"/>
-        <v>-2.6999999999999993</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="24"/>
-        <v>5.6</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="24"/>
-        <v>-8.5000000000000018</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="24"/>
-        <v>6.5</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="24"/>
-        <v>288.7</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="24"/>
-        <v>-38.100000000000009</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="24"/>
-        <v>13.999999999999998</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" ref="P19:R19" si="25">SUM(P14:P18)</f>
-        <v>22.5</v>
-      </c>
-      <c r="Q19" s="5">
+        <v>12.18</v>
+      </c>
+      <c r="Y20" s="5">
+        <f>SUM(Y15:Y19)</f>
+        <v>-4.7000000000000028</v>
+      </c>
+      <c r="Z20" s="5">
+        <f>SUM(Z15:Z19)</f>
+        <v>248.60000000000002</v>
+      </c>
+      <c r="AA20" s="5">
+        <f t="shared" ref="AA20:AK20" si="25">SUM(AA14:AA19)</f>
+        <v>70.44</v>
+      </c>
+      <c r="AB20" s="5">
         <f t="shared" si="25"/>
-        <v>16.86</v>
-      </c>
-      <c r="R19" s="5">
+        <v>66.109000000000009</v>
+      </c>
+      <c r="AC20" s="5">
         <f t="shared" si="25"/>
-        <v>12.18</v>
-      </c>
-      <c r="Y19" s="5">
-        <f>SUM(Y14:Y18)</f>
-        <v>-4.7000000000000028</v>
-      </c>
-      <c r="Z19" s="5">
-        <f>SUM(Z14:Z18)</f>
-        <v>248.60000000000002</v>
-      </c>
-      <c r="AA19" s="5">
-        <f>SUM(AA14:AA18)</f>
-        <v>65.540000000000006</v>
-      </c>
-      <c r="AB19" s="5">
-        <f>SUM(AB14:AB18)</f>
-        <v>68.74199999999999</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AK19" si="26">SUM(AC14:AC18)</f>
-        <v>69.830699999999993</v>
-      </c>
-      <c r="AD19" s="5">
+        <v>66.841510000000014</v>
+      </c>
+      <c r="AD20" s="5">
+        <f t="shared" si="25"/>
+        <v>67.533457300000009</v>
+      </c>
+      <c r="AE20" s="5">
+        <f t="shared" si="25"/>
+        <v>68.180498119000021</v>
+      </c>
+      <c r="AF20" s="5">
+        <f t="shared" si="25"/>
+        <v>68.778002017570032</v>
+      </c>
+      <c r="AG20" s="5">
+        <f t="shared" si="25"/>
+        <v>69.321035480847129</v>
+      </c>
+      <c r="AH20" s="5">
+        <f t="shared" si="25"/>
+        <v>69.804344618160044</v>
+      </c>
+      <c r="AI20" s="5">
+        <f t="shared" si="25"/>
+        <v>70.222336933236718</v>
+      </c>
+      <c r="AJ20" s="5">
+        <f t="shared" si="25"/>
+        <v>70.569062116592292</v>
+      </c>
+      <c r="AK20" s="5">
+        <f t="shared" si="25"/>
+        <v>70.838191809216454</v>
+      </c>
+    </row>
+    <row r="21" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" ref="G21:O21" si="26">G13-G20</f>
+        <v>16.799999999999983</v>
+      </c>
+      <c r="H21" s="8">
         <f t="shared" si="26"/>
-        <v>70.903382999999991</v>
-      </c>
-      <c r="AE19" s="5">
+        <v>33.499999999999979</v>
+      </c>
+      <c r="I21" s="8">
         <f t="shared" si="26"/>
-        <v>71.95713459000001</v>
-      </c>
-      <c r="AF19" s="5">
+        <v>47.399999999999963</v>
+      </c>
+      <c r="J21" s="8">
         <f t="shared" si="26"/>
-        <v>72.988831232700008</v>
-      </c>
-      <c r="AG19" s="5">
+        <v>21.799999999999976</v>
+      </c>
+      <c r="K21" s="8">
         <f t="shared" si="26"/>
-        <v>73.995127904931024</v>
-      </c>
-      <c r="AH19" s="5">
+        <v>29.899999999999949</v>
+      </c>
+      <c r="L21" s="8">
         <f t="shared" si="26"/>
-        <v>74.97244506409146</v>
-      </c>
-      <c r="AI19" s="5">
+        <v>52.69999999999996</v>
+      </c>
+      <c r="M21" s="8">
         <f t="shared" si="26"/>
-        <v>75.916954904127337</v>
-      </c>
-      <c r="AJ19" s="5">
+        <v>-208.29999999999993</v>
+      </c>
+      <c r="N21" s="8">
         <f t="shared" si="26"/>
-        <v>76.824566863769931</v>
-      </c>
-      <c r="AK19" s="5">
+        <v>124.10000000000007</v>
+      </c>
+      <c r="O21" s="8">
         <f t="shared" si="26"/>
-        <v>77.690912347827734</v>
-      </c>
-    </row>
-    <row r="20" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="8">
-        <f t="shared" ref="G20:O20" si="27">G13-G19</f>
-        <v>16.799999999999983</v>
-      </c>
-      <c r="H20" s="8">
+        <v>11.400000000000007</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" ref="P21:R21" si="27">P13-P20</f>
+        <v>55.700000000000017</v>
+      </c>
+      <c r="Q21" s="8">
         <f t="shared" si="27"/>
-        <v>33.499999999999979</v>
-      </c>
-      <c r="I20" s="8">
+        <v>71.385159999999971</v>
+      </c>
+      <c r="R21" s="8">
         <f t="shared" si="27"/>
-        <v>47.399999999999963</v>
-      </c>
-      <c r="J20" s="8">
-        <f t="shared" si="27"/>
-        <v>21.799999999999976</v>
-      </c>
-      <c r="K20" s="8">
-        <f t="shared" si="27"/>
-        <v>29.899999999999949</v>
-      </c>
-      <c r="L20" s="8">
-        <f t="shared" si="27"/>
-        <v>52.69999999999996</v>
-      </c>
-      <c r="M20" s="8">
-        <f t="shared" si="27"/>
-        <v>-208.29999999999993</v>
-      </c>
-      <c r="N20" s="8">
-        <f t="shared" si="27"/>
-        <v>124.10000000000007</v>
-      </c>
-      <c r="O20" s="8">
-        <f t="shared" si="27"/>
-        <v>11.400000000000007</v>
-      </c>
-      <c r="P20" s="8">
-        <f t="shared" ref="P20:R20" si="28">P13-P19</f>
-        <v>51.787600000000026</v>
-      </c>
-      <c r="Q20" s="8">
+        <v>65.235599999999977</v>
+      </c>
+      <c r="Y21" s="8">
+        <f>Y13-Y20</f>
+        <v>119.49999999999984</v>
+      </c>
+      <c r="Z21" s="8">
+        <f>Z13-Z20</f>
+        <v>-1.5999999999996817</v>
+      </c>
+      <c r="AA21" s="8">
+        <f>AA13-AA20</f>
+        <v>203.72075999999998</v>
+      </c>
+      <c r="AB21" s="8">
+        <f>AB13-AB20</f>
+        <v>547.33953559999998</v>
+      </c>
+      <c r="AC21" s="8">
+        <f t="shared" ref="AC21:AK21" si="28">AC13-AC20</f>
+        <v>635.6327271020001</v>
+      </c>
+      <c r="AD21" s="8">
         <f t="shared" si="28"/>
-        <v>80.476759999999999</v>
-      </c>
-      <c r="R20" s="8">
+        <v>676.95720909710008</v>
+      </c>
+      <c r="AE21" s="8">
         <f t="shared" si="28"/>
-        <v>73.226600000000019</v>
-      </c>
-      <c r="Y20" s="8">
-        <f>Y13-Y19</f>
-        <v>119.49999999999984</v>
-      </c>
-      <c r="Z20" s="8">
-        <f>Z13-Z19</f>
-        <v>-1.5999999999996817</v>
-      </c>
-      <c r="AA20" s="8">
-        <f>AA13-AA19</f>
-        <v>216.89096000000001</v>
-      </c>
-      <c r="AB20" s="8">
-        <f>AB13-AB19</f>
-        <v>535.23387360000038</v>
-      </c>
-      <c r="AC20" s="8">
-        <f t="shared" ref="AC20:AK20" si="29">AC13-AC19</f>
-        <v>646.19589967200022</v>
-      </c>
-      <c r="AD20" s="8">
-        <f t="shared" si="29"/>
-        <v>729.12413248859991</v>
-      </c>
-      <c r="AE20" s="8">
-        <f t="shared" si="29"/>
-        <v>810.19905078446402</v>
-      </c>
-      <c r="AF20" s="8">
-        <f t="shared" si="29"/>
-        <v>887.26343604730778</v>
-      </c>
-      <c r="AG20" s="8">
-        <f t="shared" si="29"/>
-        <v>977.33308843195596</v>
-      </c>
-      <c r="AH20" s="8">
-        <f t="shared" si="29"/>
-        <v>1017.1654214228183</v>
-      </c>
-      <c r="AI20" s="8">
-        <f t="shared" si="29"/>
-        <v>1058.4402473105051</v>
-      </c>
-      <c r="AJ20" s="8">
-        <f t="shared" si="29"/>
-        <v>1101.2076551450789</v>
-      </c>
-      <c r="AK20" s="8">
-        <f t="shared" si="29"/>
-        <v>1145.5194661236196</v>
-      </c>
-    </row>
-    <row r="21" spans="2:146" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="H21" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="J21" s="5">
-        <v>2.6</v>
-      </c>
-      <c r="K21" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="L21" s="5">
-        <v>-1.8</v>
-      </c>
-      <c r="M21" s="5">
-        <v>-280.5</v>
-      </c>
-      <c r="N21" s="5">
-        <v>15.2</v>
-      </c>
-      <c r="O21" s="5">
-        <v>-8.1</v>
-      </c>
-      <c r="P21" s="5">
-        <f t="shared" ref="P21:R21" si="30">P20*0.15</f>
-        <v>7.7681400000000034</v>
-      </c>
-      <c r="Q21" s="5">
-        <f t="shared" si="30"/>
-        <v>12.071513999999999</v>
-      </c>
-      <c r="R21" s="5">
-        <f t="shared" si="30"/>
-        <v>10.983990000000002</v>
-      </c>
-      <c r="Y21" s="5">
-        <f>SUM(G21:J21)</f>
-        <v>-3.4</v>
-      </c>
-      <c r="Z21" s="5">
-        <f>SUM(K21:N21)</f>
-        <v>-265.7</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>SUM(O21:R21)</f>
-        <v>22.723644000000004</v>
-      </c>
-      <c r="AB21" s="5">
-        <f>AB20*0.15</f>
-        <v>80.285081040000051</v>
-      </c>
-      <c r="AC21" s="5">
-        <f t="shared" ref="AC21:AK21" si="31">AC20*0.15</f>
-        <v>96.929384950800028</v>
-      </c>
-      <c r="AD21" s="5">
-        <f t="shared" si="31"/>
-        <v>109.36861987328999</v>
-      </c>
-      <c r="AE21" s="5">
-        <f t="shared" si="31"/>
-        <v>121.52985761766959</v>
-      </c>
-      <c r="AF21" s="5">
-        <f t="shared" si="31"/>
-        <v>133.08951540709617</v>
-      </c>
-      <c r="AG21" s="5">
-        <f t="shared" si="31"/>
-        <v>146.59996326479339</v>
-      </c>
-      <c r="AH21" s="5">
-        <f t="shared" si="31"/>
-        <v>152.57481321342274</v>
-      </c>
-      <c r="AI21" s="5">
-        <f t="shared" si="31"/>
-        <v>158.76603709657576</v>
-      </c>
-      <c r="AJ21" s="5">
-        <f t="shared" si="31"/>
-        <v>165.18114827176183</v>
-      </c>
-      <c r="AK21" s="5">
-        <f t="shared" si="31"/>
-        <v>171.82791991854293</v>
+        <v>713.25822107158422</v>
+      </c>
+      <c r="AF21" s="8">
+        <f t="shared" si="28"/>
+        <v>743.48735767045969</v>
+      </c>
+      <c r="AG21" s="8">
+        <f t="shared" si="28"/>
+        <v>774.84343349798587</v>
+      </c>
+      <c r="AH21" s="8">
+        <f t="shared" si="28"/>
+        <v>807.36682990020404</v>
+      </c>
+      <c r="AI21" s="8">
+        <f t="shared" si="28"/>
+        <v>841.09937972024727</v>
+      </c>
+      <c r="AJ21" s="8">
+        <f t="shared" si="28"/>
+        <v>876.08442107405722</v>
+      </c>
+      <c r="AK21" s="8">
+        <f t="shared" si="28"/>
+        <v>912.36685321546418</v>
       </c>
     </row>
     <row r="22" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="5">
-        <v>5.6</v>
+        <v>-3.6</v>
       </c>
       <c r="H22" s="5">
-        <v>11.7</v>
+        <v>-3.3</v>
       </c>
       <c r="I22" s="5">
-        <v>13.9</v>
+        <v>0.9</v>
       </c>
       <c r="J22" s="5">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="K22" s="5">
-        <v>7.9</v>
+        <v>1.4</v>
       </c>
       <c r="L22" s="5">
-        <v>15.3</v>
+        <v>-1.8</v>
       </c>
       <c r="M22" s="5">
-        <v>18.399999999999999</v>
+        <v>-280.5</v>
       </c>
       <c r="N22" s="5">
-        <v>23.3</v>
+        <v>15.2</v>
       </c>
       <c r="O22" s="5">
-        <v>2.8</v>
+        <v>-8.1</v>
       </c>
       <c r="P22" s="5">
-        <f t="shared" ref="P22:R22" si="32">P20*0.2</f>
-        <v>10.357520000000006</v>
+        <v>14.6</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" si="32"/>
-        <v>16.095352000000002</v>
+        <f t="shared" ref="P22:R22" si="29">Q21*0.15</f>
+        <v>10.707773999999995</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="32"/>
-        <v>14.645320000000005</v>
+        <f t="shared" si="29"/>
+        <v>9.7853399999999962</v>
       </c>
       <c r="Y22" s="5">
         <f>SUM(G22:J22)</f>
-        <v>36.699999999999996</v>
+        <v>-3.4</v>
       </c>
       <c r="Z22" s="5">
         <f>SUM(K22:N22)</f>
-        <v>64.900000000000006</v>
+        <v>-265.7</v>
       </c>
       <c r="AA22" s="5">
         <f>SUM(O22:R22)</f>
-        <v>43.898192000000009</v>
+        <v>26.993113999999991</v>
       </c>
       <c r="AB22" s="5">
-        <f>AB20*0.18</f>
-        <v>96.342097248000059</v>
+        <f>AB21*0.15</f>
+        <v>82.100930339999991</v>
       </c>
       <c r="AC22" s="5">
-        <f t="shared" ref="AC22:AK22" si="33">AC20*0.18</f>
-        <v>116.31526194096004</v>
+        <f t="shared" ref="AC22:AK22" si="30">AC21*0.15</f>
+        <v>95.344909065300016</v>
       </c>
       <c r="AD22" s="5">
+        <f t="shared" si="30"/>
+        <v>101.54358136456501</v>
+      </c>
+      <c r="AE22" s="5">
+        <f t="shared" si="30"/>
+        <v>106.98873316073762</v>
+      </c>
+      <c r="AF22" s="5">
+        <f t="shared" si="30"/>
+        <v>111.52310365056896</v>
+      </c>
+      <c r="AG22" s="5">
+        <f t="shared" si="30"/>
+        <v>116.22651502469787</v>
+      </c>
+      <c r="AH22" s="5">
+        <f t="shared" si="30"/>
+        <v>121.1050244850306</v>
+      </c>
+      <c r="AI22" s="5">
+        <f t="shared" si="30"/>
+        <v>126.16490695803708</v>
+      </c>
+      <c r="AJ22" s="5">
+        <f t="shared" si="30"/>
+        <v>131.41266316110858</v>
+      </c>
+      <c r="AK22" s="5">
+        <f t="shared" si="30"/>
+        <v>136.85502798231963</v>
+      </c>
+    </row>
+    <row r="23" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="H23" s="5">
+        <v>11.7</v>
+      </c>
+      <c r="I23" s="5">
+        <v>13.9</v>
+      </c>
+      <c r="J23" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="K23" s="5">
+        <v>7.9</v>
+      </c>
+      <c r="L23" s="5">
+        <v>15.3</v>
+      </c>
+      <c r="M23" s="5">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="N23" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="O23" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="P23" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" ref="P23:R23" si="31">Q21*0.2</f>
+        <v>14.277031999999995</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="31"/>
+        <v>13.047119999999996</v>
+      </c>
+      <c r="Y23" s="5">
+        <f>SUM(G23:J23)</f>
+        <v>36.699999999999996</v>
+      </c>
+      <c r="Z23" s="5">
+        <f>SUM(K23:N23)</f>
+        <v>64.900000000000006</v>
+      </c>
+      <c r="AA23" s="5">
+        <f>SUM(O23:R23)</f>
+        <v>37.224151999999989</v>
+      </c>
+      <c r="AB23" s="5">
+        <f>AB21*0.18</f>
+        <v>98.521116407999997</v>
+      </c>
+      <c r="AC23" s="5">
+        <f t="shared" ref="AC23:AK23" si="32">AC21*0.18</f>
+        <v>114.41389087836002</v>
+      </c>
+      <c r="AD23" s="5">
+        <f t="shared" si="32"/>
+        <v>121.852297637478</v>
+      </c>
+      <c r="AE23" s="5">
+        <f t="shared" si="32"/>
+        <v>128.38647979288515</v>
+      </c>
+      <c r="AF23" s="5">
+        <f t="shared" si="32"/>
+        <v>133.82772438068275</v>
+      </c>
+      <c r="AG23" s="5">
+        <f t="shared" si="32"/>
+        <v>139.47181802963746</v>
+      </c>
+      <c r="AH23" s="5">
+        <f t="shared" si="32"/>
+        <v>145.32602938203672</v>
+      </c>
+      <c r="AI23" s="5">
+        <f t="shared" si="32"/>
+        <v>151.39788834964449</v>
+      </c>
+      <c r="AJ23" s="5">
+        <f t="shared" si="32"/>
+        <v>157.6951957933303</v>
+      </c>
+      <c r="AK23" s="5">
+        <f t="shared" si="32"/>
+        <v>164.22603357878356</v>
+      </c>
+    </row>
+    <row r="24" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" ref="G24:O24" si="33">G21-G22-G23</f>
+        <v>14.799999999999985</v>
+      </c>
+      <c r="H24" s="8">
         <f t="shared" si="33"/>
-        <v>131.24234384794798</v>
-      </c>
-      <c r="AE22" s="5">
+        <v>25.099999999999977</v>
+      </c>
+      <c r="I24" s="8">
         <f t="shared" si="33"/>
-        <v>145.8358291412035</v>
-      </c>
-      <c r="AF22" s="5">
+        <v>32.599999999999966</v>
+      </c>
+      <c r="J24" s="8">
         <f t="shared" si="33"/>
-        <v>159.7074184885154</v>
-      </c>
-      <c r="AG22" s="5">
+        <v>13.699999999999974</v>
+      </c>
+      <c r="K24" s="8">
         <f t="shared" si="33"/>
-        <v>175.91995591775208</v>
-      </c>
-      <c r="AH22" s="5">
+        <v>20.599999999999952</v>
+      </c>
+      <c r="L24" s="8">
         <f t="shared" si="33"/>
-        <v>183.08977585610728</v>
-      </c>
-      <c r="AI22" s="5">
+        <v>39.19999999999996</v>
+      </c>
+      <c r="M24" s="8">
         <f t="shared" si="33"/>
-        <v>190.5192445158909</v>
-      </c>
-      <c r="AJ22" s="5">
+        <v>53.800000000000075</v>
+      </c>
+      <c r="N24" s="8">
         <f t="shared" si="33"/>
-        <v>198.21737792611418</v>
-      </c>
-      <c r="AK22" s="5">
+        <v>85.600000000000065</v>
+      </c>
+      <c r="O24" s="8">
         <f t="shared" si="33"/>
-        <v>206.19350390225154</v>
-      </c>
-    </row>
-    <row r="23" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" ref="G23:O23" si="34">G20-G21-G22</f>
-        <v>14.799999999999985</v>
-      </c>
-      <c r="H23" s="8">
+        <v>16.700000000000006</v>
+      </c>
+      <c r="P24" s="8">
+        <f t="shared" ref="P24:R24" si="34">P21-P22-P23</f>
+        <v>34.000000000000014</v>
+      </c>
+      <c r="Q24" s="8">
         <f t="shared" si="34"/>
-        <v>25.099999999999977</v>
-      </c>
-      <c r="I23" s="8">
+        <v>46.400353999999979</v>
+      </c>
+      <c r="R24" s="8">
         <f t="shared" si="34"/>
-        <v>32.599999999999966</v>
-      </c>
-      <c r="J23" s="8">
-        <f t="shared" si="34"/>
-        <v>13.699999999999974</v>
-      </c>
-      <c r="K23" s="8">
-        <f t="shared" si="34"/>
-        <v>20.599999999999952</v>
-      </c>
-      <c r="L23" s="8">
-        <f t="shared" si="34"/>
-        <v>39.19999999999996</v>
-      </c>
-      <c r="M23" s="8">
-        <f t="shared" si="34"/>
-        <v>53.800000000000075</v>
-      </c>
-      <c r="N23" s="8">
-        <f t="shared" si="34"/>
-        <v>85.600000000000065</v>
-      </c>
-      <c r="O23" s="8">
-        <f t="shared" si="34"/>
-        <v>16.700000000000006</v>
-      </c>
-      <c r="P23" s="8">
-        <f t="shared" ref="P23:R23" si="35">P20-P21-P22</f>
-        <v>33.661940000000016</v>
-      </c>
-      <c r="Q23" s="8">
+        <v>42.403139999999979</v>
+      </c>
+      <c r="Y24" s="8">
+        <f>Y21-Y22-Y23</f>
+        <v>86.199999999999847</v>
+      </c>
+      <c r="Z24" s="8">
+        <f>Z21-Z22-Z23</f>
+        <v>199.2000000000003</v>
+      </c>
+      <c r="AA24" s="8">
+        <f>AA21-AA22-AA23</f>
+        <v>139.50349399999999</v>
+      </c>
+      <c r="AB24" s="8">
+        <f>AB21-AB22-AB23</f>
+        <v>366.71748885199997</v>
+      </c>
+      <c r="AC24" s="8">
+        <f t="shared" ref="AC24:AK24" si="35">AC21-AC22-AC23</f>
+        <v>425.87392715834005</v>
+      </c>
+      <c r="AD24" s="8">
         <f t="shared" si="35"/>
-        <v>52.309894</v>
-      </c>
-      <c r="R23" s="8">
+        <v>453.56133009505703</v>
+      </c>
+      <c r="AE24" s="8">
         <f t="shared" si="35"/>
-        <v>47.597290000000008</v>
-      </c>
-      <c r="Y23" s="8">
-        <f>Y20-Y21-Y22</f>
-        <v>86.199999999999847</v>
-      </c>
-      <c r="Z23" s="8">
-        <f>Z20-Z21-Z22</f>
-        <v>199.2000000000003</v>
-      </c>
-      <c r="AA23" s="8">
-        <f>AA20-AA21-AA22</f>
-        <v>150.26912399999998</v>
-      </c>
-      <c r="AB23" s="8">
-        <f>AB20-AB21-AB22</f>
-        <v>358.60669531200028</v>
-      </c>
-      <c r="AC23" s="8">
-        <f t="shared" ref="AC23:AK23" si="36">AC20-AC21-AC22</f>
-        <v>432.95125278024017</v>
-      </c>
-      <c r="AD23" s="8">
-        <f t="shared" si="36"/>
-        <v>488.513168767362</v>
-      </c>
-      <c r="AE23" s="8">
-        <f t="shared" si="36"/>
-        <v>542.83336402559098</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="36"/>
-        <v>594.4665021516962</v>
-      </c>
-      <c r="AG23" s="8">
-        <f t="shared" si="36"/>
-        <v>654.81316924941052</v>
-      </c>
-      <c r="AH23" s="8">
-        <f t="shared" si="36"/>
-        <v>681.50083235328827</v>
-      </c>
-      <c r="AI23" s="8">
-        <f t="shared" si="36"/>
-        <v>709.1549656980385</v>
-      </c>
-      <c r="AJ23" s="8">
-        <f t="shared" si="36"/>
-        <v>737.80912894720291</v>
-      </c>
-      <c r="AK23" s="8">
-        <f t="shared" si="36"/>
-        <v>767.49804230282518</v>
-      </c>
-      <c r="AL23" s="1">
-        <f>AK23*(1+$AO$29)</f>
-        <v>759.82306187979691</v>
-      </c>
-      <c r="AM23" s="1">
-        <f t="shared" ref="AM23:CX23" si="37">AL23*(1+$AO$29)</f>
-        <v>752.22483126099894</v>
-      </c>
-      <c r="AN23" s="1">
+        <v>477.88300811796142</v>
+      </c>
+      <c r="AF24" s="8">
+        <f t="shared" si="35"/>
+        <v>498.13652963920799</v>
+      </c>
+      <c r="AG24" s="8">
+        <f t="shared" si="35"/>
+        <v>519.14510044365056</v>
+      </c>
+      <c r="AH24" s="8">
+        <f t="shared" si="35"/>
+        <v>540.93577603313668</v>
+      </c>
+      <c r="AI24" s="8">
+        <f t="shared" si="35"/>
+        <v>563.53658441256562</v>
+      </c>
+      <c r="AJ24" s="8">
+        <f t="shared" si="35"/>
+        <v>586.97656211961828</v>
+      </c>
+      <c r="AK24" s="8">
+        <f t="shared" si="35"/>
+        <v>611.28579165436099</v>
+      </c>
+      <c r="AL24" s="1">
+        <f>AK24*(1+$AO$30)</f>
+        <v>605.1729337378174</v>
+      </c>
+      <c r="AM24" s="1">
+        <f t="shared" ref="AM24:CX24" si="36">AL24*(1+$AO$30)</f>
+        <v>599.12120440043918</v>
+      </c>
+      <c r="AN24" s="1">
+        <f t="shared" si="36"/>
+        <v>593.12999235643474</v>
+      </c>
+      <c r="AO24" s="1">
+        <f t="shared" si="36"/>
+        <v>587.19869243287042</v>
+      </c>
+      <c r="AP24" s="1">
+        <f t="shared" si="36"/>
+        <v>581.32670550854175</v>
+      </c>
+      <c r="AQ24" s="1">
+        <f t="shared" si="36"/>
+        <v>575.51343845345627</v>
+      </c>
+      <c r="AR24" s="1">
+        <f t="shared" si="36"/>
+        <v>569.75830406892169</v>
+      </c>
+      <c r="AS24" s="1">
+        <f t="shared" si="36"/>
+        <v>564.06072102823248</v>
+      </c>
+      <c r="AT24" s="1">
+        <f t="shared" si="36"/>
+        <v>558.4201138179501</v>
+      </c>
+      <c r="AU24" s="1">
+        <f t="shared" si="36"/>
+        <v>552.83591267977056</v>
+      </c>
+      <c r="AV24" s="1">
+        <f t="shared" si="36"/>
+        <v>547.30755355297288</v>
+      </c>
+      <c r="AW24" s="1">
+        <f t="shared" si="36"/>
+        <v>541.83447801744319</v>
+      </c>
+      <c r="AX24" s="1">
+        <f t="shared" si="36"/>
+        <v>536.4161332372687</v>
+      </c>
+      <c r="AY24" s="1">
+        <f t="shared" si="36"/>
+        <v>531.05197190489605</v>
+      </c>
+      <c r="AZ24" s="1">
+        <f t="shared" si="36"/>
+        <v>525.74145218584704</v>
+      </c>
+      <c r="BA24" s="1">
+        <f t="shared" si="36"/>
+        <v>520.4840376639886</v>
+      </c>
+      <c r="BB24" s="1">
+        <f t="shared" si="36"/>
+        <v>515.27919728734867</v>
+      </c>
+      <c r="BC24" s="1">
+        <f t="shared" si="36"/>
+        <v>510.12640531447516</v>
+      </c>
+      <c r="BD24" s="1">
+        <f t="shared" si="36"/>
+        <v>505.02514126133042</v>
+      </c>
+      <c r="BE24" s="1">
+        <f t="shared" si="36"/>
+        <v>499.97488984871711</v>
+      </c>
+      <c r="BF24" s="1">
+        <f t="shared" si="36"/>
+        <v>494.97514095022996</v>
+      </c>
+      <c r="BG24" s="1">
+        <f t="shared" si="36"/>
+        <v>490.02538954072764</v>
+      </c>
+      <c r="BH24" s="1">
+        <f t="shared" si="36"/>
+        <v>485.12513564532037</v>
+      </c>
+      <c r="BI24" s="1">
+        <f t="shared" si="36"/>
+        <v>480.27388428886718</v>
+      </c>
+      <c r="BJ24" s="1">
+        <f t="shared" si="36"/>
+        <v>475.47114544597849</v>
+      </c>
+      <c r="BK24" s="1">
+        <f t="shared" si="36"/>
+        <v>470.71643399151873</v>
+      </c>
+      <c r="BL24" s="1">
+        <f t="shared" si="36"/>
+        <v>466.00926965160352</v>
+      </c>
+      <c r="BM24" s="1">
+        <f t="shared" si="36"/>
+        <v>461.3491769550875</v>
+      </c>
+      <c r="BN24" s="1">
+        <f t="shared" si="36"/>
+        <v>456.73568518553662</v>
+      </c>
+      <c r="BO24" s="1">
+        <f t="shared" si="36"/>
+        <v>452.16832833368125</v>
+      </c>
+      <c r="BP24" s="1">
+        <f t="shared" si="36"/>
+        <v>447.64664505034443</v>
+      </c>
+      <c r="BQ24" s="1">
+        <f t="shared" si="36"/>
+        <v>443.17017859984099</v>
+      </c>
+      <c r="BR24" s="1">
+        <f t="shared" si="36"/>
+        <v>438.73847681384257</v>
+      </c>
+      <c r="BS24" s="1">
+        <f t="shared" si="36"/>
+        <v>434.35109204570415</v>
+      </c>
+      <c r="BT24" s="1">
+        <f t="shared" si="36"/>
+        <v>430.0075811252471</v>
+      </c>
+      <c r="BU24" s="1">
+        <f t="shared" si="36"/>
+        <v>425.7075053139946</v>
+      </c>
+      <c r="BV24" s="1">
+        <f t="shared" si="36"/>
+        <v>421.45043026085466</v>
+      </c>
+      <c r="BW24" s="1">
+        <f t="shared" si="36"/>
+        <v>417.23592595824613</v>
+      </c>
+      <c r="BX24" s="1">
+        <f t="shared" si="36"/>
+        <v>413.06356669866364</v>
+      </c>
+      <c r="BY24" s="1">
+        <f t="shared" si="36"/>
+        <v>408.93293103167701</v>
+      </c>
+      <c r="BZ24" s="1">
+        <f t="shared" si="36"/>
+        <v>404.84360172136024</v>
+      </c>
+      <c r="CA24" s="1">
+        <f t="shared" si="36"/>
+        <v>400.79516570414665</v>
+      </c>
+      <c r="CB24" s="1">
+        <f t="shared" si="36"/>
+        <v>396.78721404710518</v>
+      </c>
+      <c r="CC24" s="1">
+        <f t="shared" si="36"/>
+        <v>392.81934190663412</v>
+      </c>
+      <c r="CD24" s="1">
+        <f t="shared" si="36"/>
+        <v>388.89114848756776</v>
+      </c>
+      <c r="CE24" s="1">
+        <f t="shared" si="36"/>
+        <v>385.00223700269208</v>
+      </c>
+      <c r="CF24" s="1">
+        <f t="shared" si="36"/>
+        <v>381.15221463266516</v>
+      </c>
+      <c r="CG24" s="1">
+        <f t="shared" si="36"/>
+        <v>377.34069248633853</v>
+      </c>
+      <c r="CH24" s="1">
+        <f t="shared" si="36"/>
+        <v>373.56728556147516</v>
+      </c>
+      <c r="CI24" s="1">
+        <f t="shared" si="36"/>
+        <v>369.83161270586038</v>
+      </c>
+      <c r="CJ24" s="1">
+        <f t="shared" si="36"/>
+        <v>366.13329657880178</v>
+      </c>
+      <c r="CK24" s="1">
+        <f t="shared" si="36"/>
+        <v>362.47196361301377</v>
+      </c>
+      <c r="CL24" s="1">
+        <f t="shared" si="36"/>
+        <v>358.84724397688365</v>
+      </c>
+      <c r="CM24" s="1">
+        <f t="shared" si="36"/>
+        <v>355.2587715371148</v>
+      </c>
+      <c r="CN24" s="1">
+        <f t="shared" si="36"/>
+        <v>351.70618382174365</v>
+      </c>
+      <c r="CO24" s="1">
+        <f t="shared" si="36"/>
+        <v>348.18912198352621</v>
+      </c>
+      <c r="CP24" s="1">
+        <f t="shared" si="36"/>
+        <v>344.70723076369092</v>
+      </c>
+      <c r="CQ24" s="1">
+        <f t="shared" si="36"/>
+        <v>341.260158456054</v>
+      </c>
+      <c r="CR24" s="1">
+        <f t="shared" si="36"/>
+        <v>337.84755687149345</v>
+      </c>
+      <c r="CS24" s="1">
+        <f t="shared" si="36"/>
+        <v>334.46908130277853</v>
+      </c>
+      <c r="CT24" s="1">
+        <f t="shared" si="36"/>
+        <v>331.12439048975074</v>
+      </c>
+      <c r="CU24" s="1">
+        <f t="shared" si="36"/>
+        <v>327.8131465848532</v>
+      </c>
+      <c r="CV24" s="1">
+        <f t="shared" si="36"/>
+        <v>324.53501511900464</v>
+      </c>
+      <c r="CW24" s="1">
+        <f t="shared" si="36"/>
+        <v>321.28966496781459</v>
+      </c>
+      <c r="CX24" s="1">
+        <f t="shared" si="36"/>
+        <v>318.07676831813643</v>
+      </c>
+      <c r="CY24" s="1">
+        <f t="shared" ref="CY24:EP24" si="37">CX24*(1+$AO$30)</f>
+        <v>314.89600063495504</v>
+      </c>
+      <c r="CZ24" s="1">
         <f t="shared" si="37"/>
-        <v>744.70258294838891</v>
-      </c>
-      <c r="AO23" s="1">
+        <v>311.74704062860548</v>
+      </c>
+      <c r="DA24" s="1">
         <f t="shared" si="37"/>
-        <v>737.25555711890502</v>
-      </c>
-      <c r="AP23" s="1">
+        <v>308.62957022231944</v>
+      </c>
+      <c r="DB24" s="1">
         <f t="shared" si="37"/>
-        <v>729.88300154771593</v>
-      </c>
-      <c r="AQ23" s="1">
+        <v>305.54327452009625</v>
+      </c>
+      <c r="DC24" s="1">
         <f t="shared" si="37"/>
-        <v>722.58417153223877</v>
-      </c>
-      <c r="AR23" s="1">
+        <v>302.48784177489529</v>
+      </c>
+      <c r="DD24" s="1">
         <f t="shared" si="37"/>
-        <v>715.35832981691635</v>
-      </c>
-      <c r="AS23" s="1">
+        <v>299.46296335714635</v>
+      </c>
+      <c r="DE24" s="1">
         <f t="shared" si="37"/>
-        <v>708.20474651874713</v>
-      </c>
-      <c r="AT23" s="1">
+        <v>296.46833372357486</v>
+      </c>
+      <c r="DF24" s="1">
         <f t="shared" si="37"/>
-        <v>701.1226990535597</v>
-      </c>
-      <c r="AU23" s="1">
+        <v>293.50365038633913</v>
+      </c>
+      <c r="DG24" s="1">
         <f t="shared" si="37"/>
-        <v>694.11147206302405</v>
-      </c>
-      <c r="AV23" s="1">
+        <v>290.56861388247574</v>
+      </c>
+      <c r="DH24" s="1">
         <f t="shared" si="37"/>
-        <v>687.1703573423938</v>
-      </c>
-      <c r="AW23" s="1">
+        <v>287.66292774365098</v>
+      </c>
+      <c r="DI24" s="1">
         <f t="shared" si="37"/>
-        <v>680.29865376896987</v>
-      </c>
-      <c r="AX23" s="1">
+        <v>284.78629846621448</v>
+      </c>
+      <c r="DJ24" s="1">
         <f t="shared" si="37"/>
-        <v>673.49566723128021</v>
-      </c>
-      <c r="AY23" s="1">
+        <v>281.93843548155235</v>
+      </c>
+      <c r="DK24" s="1">
         <f t="shared" si="37"/>
-        <v>666.76071055896739</v>
-      </c>
-      <c r="AZ23" s="1">
+        <v>279.11905112673679</v>
+      </c>
+      <c r="DL24" s="1">
         <f t="shared" si="37"/>
-        <v>660.09310345337769</v>
-      </c>
-      <c r="BA23" s="1">
+        <v>276.32786061546943</v>
+      </c>
+      <c r="DM24" s="1">
         <f t="shared" si="37"/>
-        <v>653.49217241884389</v>
-      </c>
-      <c r="BB23" s="1">
+        <v>273.56458200931473</v>
+      </c>
+      <c r="DN24" s="1">
         <f t="shared" si="37"/>
-        <v>646.9572506946555</v>
-      </c>
-      <c r="BC23" s="1">
+        <v>270.82893618922157</v>
+      </c>
+      <c r="DO24" s="1">
         <f t="shared" si="37"/>
-        <v>640.48767818770898</v>
-      </c>
-      <c r="BD23" s="1">
+        <v>268.12064682732932</v>
+      </c>
+      <c r="DP24" s="1">
         <f t="shared" si="37"/>
-        <v>634.0828014058319</v>
-      </c>
-      <c r="BE23" s="1">
+        <v>265.43944035905605</v>
+      </c>
+      <c r="DQ24" s="1">
         <f t="shared" si="37"/>
-        <v>627.74197339177363</v>
-      </c>
-      <c r="BF23" s="1">
+        <v>262.78504595546548</v>
+      </c>
+      <c r="DR24" s="1">
         <f t="shared" si="37"/>
-        <v>621.46455365785584</v>
-      </c>
-      <c r="BG23" s="1">
+        <v>260.1571954959108</v>
+      </c>
+      <c r="DS24" s="1">
         <f t="shared" si="37"/>
-        <v>615.24990812127726</v>
-      </c>
-      <c r="BH23" s="1">
+        <v>257.55562354095167</v>
+      </c>
+      <c r="DT24" s="1">
         <f t="shared" si="37"/>
-        <v>609.09740904006446</v>
-      </c>
-      <c r="BI23" s="1">
+        <v>254.98006730554215</v>
+      </c>
+      <c r="DU24" s="1">
         <f t="shared" si="37"/>
-        <v>603.0064349496638</v>
-      </c>
-      <c r="BJ23" s="1">
+        <v>252.43026663248673</v>
+      </c>
+      <c r="DV24" s="1">
         <f t="shared" si="37"/>
-        <v>596.97637060016712</v>
-      </c>
-      <c r="BK23" s="1">
+        <v>249.90596396616186</v>
+      </c>
+      <c r="DW24" s="1">
         <f t="shared" si="37"/>
-        <v>591.00660689416543</v>
-      </c>
-      <c r="BL23" s="1">
+        <v>247.40690432650024</v>
+      </c>
+      <c r="DX24" s="1">
         <f t="shared" si="37"/>
-        <v>585.09654082522377</v>
-      </c>
-      <c r="BM23" s="1">
+        <v>244.93283528323522</v>
+      </c>
+      <c r="DY24" s="1">
         <f t="shared" si="37"/>
-        <v>579.24557541697152</v>
-      </c>
-      <c r="BN23" s="1">
+        <v>242.48350693040285</v>
+      </c>
+      <c r="DZ24" s="1">
         <f t="shared" si="37"/>
-        <v>573.45311966280178</v>
-      </c>
-      <c r="BO23" s="1">
+        <v>240.05867186109882</v>
+      </c>
+      <c r="EA24" s="1">
         <f t="shared" si="37"/>
-        <v>567.71858846617374</v>
-      </c>
-      <c r="BP23" s="1">
+        <v>237.65808514248783</v>
+      </c>
+      <c r="EB24" s="1">
         <f t="shared" si="37"/>
-        <v>562.04140258151199</v>
-      </c>
-      <c r="BQ23" s="1">
+        <v>235.28150429106296</v>
+      </c>
+      <c r="EC24" s="1">
         <f t="shared" si="37"/>
-        <v>556.42098855569691</v>
-      </c>
-      <c r="BR23" s="1">
+        <v>232.92868924815232</v>
+      </c>
+      <c r="ED24" s="1">
         <f t="shared" si="37"/>
-        <v>550.85677867013999</v>
-      </c>
-      <c r="BS23" s="1">
+        <v>230.5994023556708</v>
+      </c>
+      <c r="EE24" s="1">
         <f t="shared" si="37"/>
-        <v>545.34821088343858</v>
-      </c>
-      <c r="BT23" s="1">
+        <v>228.2934083321141</v>
+      </c>
+      <c r="EF24" s="1">
         <f t="shared" si="37"/>
-        <v>539.89472877460423</v>
-      </c>
-      <c r="BU23" s="1">
+        <v>226.01047424879295</v>
+      </c>
+      <c r="EG24" s="1">
         <f t="shared" si="37"/>
-        <v>534.49578148685816</v>
-      </c>
-      <c r="BV23" s="1">
+        <v>223.75036950630502</v>
+      </c>
+      <c r="EH24" s="1">
         <f t="shared" si="37"/>
-        <v>529.15082367198954</v>
-      </c>
-      <c r="BW23" s="1">
+        <v>221.51286581124197</v>
+      </c>
+      <c r="EI24" s="1">
         <f t="shared" si="37"/>
-        <v>523.85931543526965</v>
-      </c>
-      <c r="BX23" s="1">
+        <v>219.29773715312953</v>
+      </c>
+      <c r="EJ24" s="1">
         <f t="shared" si="37"/>
-        <v>518.62072228091699</v>
-      </c>
-      <c r="BY23" s="1">
+        <v>217.10475978159823</v>
+      </c>
+      <c r="EK24" s="1">
         <f t="shared" si="37"/>
-        <v>513.43451505810776</v>
-      </c>
-      <c r="BZ23" s="1">
+        <v>214.93371218378226</v>
+      </c>
+      <c r="EL24" s="1">
         <f t="shared" si="37"/>
-        <v>508.30016990752671</v>
-      </c>
-      <c r="CA23" s="1">
+        <v>212.78437506194444</v>
+      </c>
+      <c r="EM24" s="1">
         <f t="shared" si="37"/>
-        <v>503.21716820845143</v>
-      </c>
-      <c r="CB23" s="1">
+        <v>210.65653131132501</v>
+      </c>
+      <c r="EN24" s="1">
         <f t="shared" si="37"/>
-        <v>498.18499652636689</v>
-      </c>
-      <c r="CC23" s="1">
+        <v>208.54996599821175</v>
+      </c>
+      <c r="EO24" s="1">
         <f t="shared" si="37"/>
-        <v>493.20314656110321</v>
-      </c>
-      <c r="CD23" s="1">
+        <v>206.46446633822961</v>
+      </c>
+      <c r="EP24" s="1">
         <f t="shared" si="37"/>
-        <v>488.27111509549218</v>
-      </c>
-      <c r="CE23" s="1">
-        <f t="shared" si="37"/>
-        <v>483.38840394453723</v>
-      </c>
-      <c r="CF23" s="1">
-        <f t="shared" si="37"/>
-        <v>478.55451990509187</v>
-      </c>
-      <c r="CG23" s="1">
-        <f t="shared" si="37"/>
-        <v>473.76897470604092</v>
-      </c>
-      <c r="CH23" s="1">
-        <f t="shared" si="37"/>
-        <v>469.03128495898051</v>
-      </c>
-      <c r="CI23" s="1">
-        <f t="shared" si="37"/>
-        <v>464.34097210939069</v>
-      </c>
-      <c r="CJ23" s="1">
-        <f t="shared" si="37"/>
-        <v>459.69756238829677</v>
-      </c>
-      <c r="CK23" s="1">
-        <f t="shared" si="37"/>
-        <v>455.10058676441378</v>
-      </c>
-      <c r="CL23" s="1">
-        <f t="shared" si="37"/>
-        <v>450.54958089676961</v>
-      </c>
-      <c r="CM23" s="1">
-        <f t="shared" si="37"/>
-        <v>446.04408508780193</v>
-      </c>
-      <c r="CN23" s="1">
-        <f t="shared" si="37"/>
-        <v>441.58364423692393</v>
-      </c>
-      <c r="CO23" s="1">
-        <f t="shared" si="37"/>
-        <v>437.16780779455468</v>
-      </c>
-      <c r="CP23" s="1">
-        <f t="shared" si="37"/>
-        <v>432.79612971660913</v>
-      </c>
-      <c r="CQ23" s="1">
-        <f t="shared" si="37"/>
-        <v>428.46816841944303</v>
-      </c>
-      <c r="CR23" s="1">
-        <f t="shared" si="37"/>
-        <v>424.18348673524861</v>
-      </c>
-      <c r="CS23" s="1">
-        <f t="shared" si="37"/>
-        <v>419.9416518678961</v>
-      </c>
-      <c r="CT23" s="1">
-        <f t="shared" si="37"/>
-        <v>415.74223534921714</v>
-      </c>
-      <c r="CU23" s="1">
-        <f t="shared" si="37"/>
-        <v>411.58481299572497</v>
-      </c>
-      <c r="CV23" s="1">
-        <f t="shared" si="37"/>
-        <v>407.4689648657677</v>
-      </c>
-      <c r="CW23" s="1">
-        <f t="shared" si="37"/>
-        <v>403.39427521711002</v>
-      </c>
-      <c r="CX23" s="1">
-        <f t="shared" si="37"/>
-        <v>399.36033246493889</v>
-      </c>
-      <c r="CY23" s="1">
-        <f t="shared" ref="CY23:EP23" si="38">CX23*(1+$AO$29)</f>
-        <v>395.36672914028952</v>
-      </c>
-      <c r="CZ23" s="1">
-        <f t="shared" si="38"/>
-        <v>391.41306184888663</v>
-      </c>
-      <c r="DA23" s="1">
-        <f t="shared" si="38"/>
-        <v>387.49893123039777</v>
-      </c>
-      <c r="DB23" s="1">
-        <f t="shared" si="38"/>
-        <v>383.62394191809381</v>
-      </c>
-      <c r="DC23" s="1">
-        <f t="shared" si="38"/>
-        <v>379.78770249891284</v>
-      </c>
-      <c r="DD23" s="1">
-        <f t="shared" si="38"/>
-        <v>375.9898254739237</v>
-      </c>
-      <c r="DE23" s="1">
-        <f t="shared" si="38"/>
-        <v>372.22992721918445</v>
-      </c>
-      <c r="DF23" s="1">
-        <f t="shared" si="38"/>
-        <v>368.50762794699261</v>
-      </c>
-      <c r="DG23" s="1">
-        <f t="shared" si="38"/>
-        <v>364.8225516675227</v>
-      </c>
-      <c r="DH23" s="1">
-        <f t="shared" si="38"/>
-        <v>361.17432615084749</v>
-      </c>
-      <c r="DI23" s="1">
-        <f t="shared" si="38"/>
-        <v>357.56258288933901</v>
-      </c>
-      <c r="DJ23" s="1">
-        <f t="shared" si="38"/>
-        <v>353.9869570604456</v>
-      </c>
-      <c r="DK23" s="1">
-        <f t="shared" si="38"/>
-        <v>350.44708748984112</v>
-      </c>
-      <c r="DL23" s="1">
-        <f t="shared" si="38"/>
-        <v>346.94261661494272</v>
-      </c>
-      <c r="DM23" s="1">
-        <f t="shared" si="38"/>
-        <v>343.47319044879328</v>
-      </c>
-      <c r="DN23" s="1">
-        <f t="shared" si="38"/>
-        <v>340.03845854430534</v>
-      </c>
-      <c r="DO23" s="1">
-        <f t="shared" si="38"/>
-        <v>336.63807395886226</v>
-      </c>
-      <c r="DP23" s="1">
-        <f t="shared" si="38"/>
-        <v>333.27169321927363</v>
-      </c>
-      <c r="DQ23" s="1">
-        <f t="shared" si="38"/>
-        <v>329.93897628708089</v>
-      </c>
-      <c r="DR23" s="1">
-        <f t="shared" si="38"/>
-        <v>326.63958652421007</v>
-      </c>
-      <c r="DS23" s="1">
-        <f t="shared" si="38"/>
-        <v>323.37319065896799</v>
-      </c>
-      <c r="DT23" s="1">
-        <f t="shared" si="38"/>
-        <v>320.13945875237829</v>
-      </c>
-      <c r="DU23" s="1">
-        <f t="shared" si="38"/>
-        <v>316.9380641648545</v>
-      </c>
-      <c r="DV23" s="1">
-        <f t="shared" si="38"/>
-        <v>313.76868352320594</v>
-      </c>
-      <c r="DW23" s="1">
-        <f t="shared" si="38"/>
-        <v>310.63099668797389</v>
-      </c>
-      <c r="DX23" s="1">
-        <f t="shared" si="38"/>
-        <v>307.52468672109416</v>
-      </c>
-      <c r="DY23" s="1">
-        <f t="shared" si="38"/>
-        <v>304.44943985388323</v>
-      </c>
-      <c r="DZ23" s="1">
-        <f t="shared" si="38"/>
-        <v>301.40494545534438</v>
-      </c>
-      <c r="EA23" s="1">
-        <f t="shared" si="38"/>
-        <v>298.39089600079092</v>
-      </c>
-      <c r="EB23" s="1">
-        <f t="shared" si="38"/>
-        <v>295.40698704078301</v>
-      </c>
-      <c r="EC23" s="1">
-        <f t="shared" si="38"/>
-        <v>292.4529171703752</v>
-      </c>
-      <c r="ED23" s="1">
-        <f t="shared" si="38"/>
-        <v>289.52838799867146</v>
-      </c>
-      <c r="EE23" s="1">
-        <f t="shared" si="38"/>
-        <v>286.63310411868474</v>
-      </c>
-      <c r="EF23" s="1">
-        <f t="shared" si="38"/>
-        <v>283.76677307749787</v>
-      </c>
-      <c r="EG23" s="1">
-        <f t="shared" si="38"/>
-        <v>280.92910534672291</v>
-      </c>
-      <c r="EH23" s="1">
-        <f t="shared" si="38"/>
-        <v>278.11981429325567</v>
-      </c>
-      <c r="EI23" s="1">
-        <f t="shared" si="38"/>
-        <v>275.33861615032311</v>
-      </c>
-      <c r="EJ23" s="1">
-        <f t="shared" si="38"/>
-        <v>272.58522998881989</v>
-      </c>
-      <c r="EK23" s="1">
-        <f t="shared" si="38"/>
-        <v>269.85937768893172</v>
-      </c>
-      <c r="EL23" s="1">
-        <f t="shared" si="38"/>
-        <v>267.1607839120424</v>
-      </c>
-      <c r="EM23" s="1">
-        <f t="shared" si="38"/>
-        <v>264.48917607292196</v>
-      </c>
-      <c r="EN23" s="1">
-        <f t="shared" si="38"/>
-        <v>261.84428431219277</v>
-      </c>
-      <c r="EO23" s="1">
-        <f t="shared" si="38"/>
-        <v>259.22584146907082</v>
-      </c>
-      <c r="EP23" s="1">
-        <f t="shared" si="38"/>
-        <v>256.6335830543801</v>
-      </c>
-    </row>
-    <row r="24" spans="2:146" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="5">
-        <f t="shared" ref="G24:O24" si="39">67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="H24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="J24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="K24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="L24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="M24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="N24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="O24" s="5">
-        <f t="shared" si="39"/>
-        <v>89.1</v>
-      </c>
-      <c r="P24" s="5">
-        <f t="shared" ref="P24:R24" si="40">67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="Q24" s="5">
-        <f t="shared" si="40"/>
-        <v>89.1</v>
-      </c>
-      <c r="R24" s="5">
-        <f t="shared" si="40"/>
-        <v>89.1</v>
-      </c>
-      <c r="Y24" s="5">
-        <f>67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="Z24" s="5">
-        <f>67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="AA24" s="5">
-        <f>67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="AB24" s="5">
-        <f>67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="AC24" s="5">
-        <f t="shared" ref="AC24:AK24" si="41">67.8+19.8+1.5</f>
-        <v>89.1</v>
-      </c>
-      <c r="AD24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AE24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AF24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AG24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AH24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AI24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AJ24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
-      </c>
-      <c r="AK24" s="5">
-        <f t="shared" si="41"/>
-        <v>89.1</v>
+        <v>204.39982167484732</v>
       </c>
     </row>
     <row r="25" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" ref="G25:O25" si="38">67.8+19.8+1.5</f>
+        <v>89.1</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="M25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="N25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="O25" s="5">
+        <f t="shared" si="38"/>
+        <v>89.1</v>
+      </c>
+      <c r="P25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="Q25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="R25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="Y25" s="5">
+        <f>67.8+19.8+1.5</f>
+        <v>89.1</v>
+      </c>
+      <c r="Z25" s="5">
+        <f>67.8+19.8+1.5</f>
+        <v>89.1</v>
+      </c>
+      <c r="AA25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AB25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AC25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AD25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AE25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AF25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AG25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AH25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AI25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AJ25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+      <c r="AK25" s="5">
+        <f>67.3+19.8+1.3</f>
+        <v>88.399999999999991</v>
+      </c>
+    </row>
+    <row r="26" spans="2:146" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="7">
-        <f t="shared" ref="G25:O25" si="42">G23/G24</f>
+      <c r="G26" s="7">
+        <f t="shared" ref="G26:O26" si="39">G24/G25</f>
         <v>0.1661054994388326</v>
       </c>
-      <c r="H25" s="7">
-        <f t="shared" si="42"/>
+      <c r="H26" s="7">
+        <f t="shared" si="39"/>
         <v>0.28170594837261481</v>
       </c>
-      <c r="I25" s="7">
-        <f t="shared" si="42"/>
+      <c r="I26" s="7">
+        <f t="shared" si="39"/>
         <v>0.36588103254769888</v>
       </c>
-      <c r="J25" s="7">
-        <f t="shared" si="42"/>
+      <c r="J26" s="7">
+        <f t="shared" si="39"/>
         <v>0.15375982042648681</v>
       </c>
-      <c r="K25" s="7">
-        <f t="shared" si="42"/>
+      <c r="K26" s="7">
+        <f t="shared" si="39"/>
         <v>0.23120089786756401</v>
       </c>
-      <c r="L25" s="7">
-        <f t="shared" si="42"/>
+      <c r="L26" s="7">
+        <f t="shared" si="39"/>
         <v>0.4399551066217729</v>
       </c>
-      <c r="M25" s="7">
-        <f t="shared" si="42"/>
+      <c r="M26" s="7">
+        <f t="shared" si="39"/>
         <v>0.6038159371492714</v>
       </c>
-      <c r="N25" s="7">
-        <f t="shared" si="42"/>
+      <c r="N26" s="7">
+        <f t="shared" si="39"/>
         <v>0.96071829405162823</v>
       </c>
-      <c r="O25" s="7">
-        <f t="shared" si="42"/>
+      <c r="O26" s="7">
+        <f t="shared" si="39"/>
         <v>0.18742985409652085</v>
       </c>
-      <c r="P25" s="7">
-        <f t="shared" ref="P25:R25" si="43">P23/P24</f>
-        <v>0.37779955106621793</v>
-      </c>
-      <c r="Q25" s="7">
-        <f t="shared" si="43"/>
-        <v>0.5870919640852974</v>
-      </c>
-      <c r="R25" s="7">
-        <f t="shared" si="43"/>
-        <v>0.5342007856341191</v>
-      </c>
-      <c r="Y25" s="7">
-        <f>Y23/Y24</f>
+      <c r="P26" s="7">
+        <f t="shared" ref="P26:R26" si="40">P24/P25</f>
+        <v>0.3846153846153848</v>
+      </c>
+      <c r="Q26" s="7">
+        <f t="shared" si="40"/>
+        <v>0.52489088235294101</v>
+      </c>
+      <c r="R26" s="7">
+        <f t="shared" si="40"/>
+        <v>0.4796735294117645</v>
+      </c>
+      <c r="Y26" s="7">
+        <f>Y24/Y25</f>
         <v>0.96745230078563249</v>
       </c>
-      <c r="Z25" s="7">
-        <f>Z23/Z24</f>
+      <c r="Z26" s="7">
+        <f>Z24/Z25</f>
         <v>2.2356902356902393</v>
       </c>
-      <c r="AA25" s="7">
-        <f>AA23/AA24</f>
-        <v>1.6865221548821547</v>
-      </c>
-      <c r="AB25" s="7">
-        <f>AB23/AB24</f>
-        <v>4.0247665018181848</v>
-      </c>
-      <c r="AC25" s="7">
-        <f t="shared" ref="AC25:AK25" si="44">AC23/AC24</f>
-        <v>4.8591610861979824</v>
-      </c>
-      <c r="AD25" s="7">
-        <f t="shared" si="44"/>
-        <v>5.48275161355064</v>
-      </c>
-      <c r="AE25" s="7">
-        <f t="shared" si="44"/>
-        <v>6.0924058813197641</v>
-      </c>
-      <c r="AF25" s="7">
-        <f t="shared" si="44"/>
-        <v>6.6719023810515852</v>
-      </c>
-      <c r="AG25" s="7">
-        <f t="shared" si="44"/>
-        <v>7.3491938187363699</v>
-      </c>
-      <c r="AH25" s="7">
-        <f t="shared" si="44"/>
-        <v>7.6487186571637293</v>
-      </c>
-      <c r="AI25" s="7">
-        <f t="shared" si="44"/>
-        <v>7.9590905241081771</v>
-      </c>
-      <c r="AJ25" s="7">
-        <f t="shared" si="44"/>
-        <v>8.2806860712368451</v>
-      </c>
-      <c r="AK25" s="7">
-        <f t="shared" si="44"/>
-        <v>8.6138949753403509</v>
-      </c>
-    </row>
-    <row r="27" spans="2:146" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9">
-        <f t="shared" ref="K27:M27" si="45">K3/G3-1</f>
-        <v>0.29323583180987201</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" si="45"/>
-        <v>0.29827315541601251</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="45"/>
-        <v>0.34616523541604982</v>
-      </c>
-      <c r="N27" s="9">
-        <f>N3/J3-1</f>
-        <v>0.25744258576694068</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" ref="O27:R27" si="46">O3/K3-1</f>
-        <v>0.19918009612666099</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="R27" s="9">
-        <f t="shared" si="46"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9">
-        <f>Z3/Y3-1</f>
-        <v>0.29858078602620086</v>
-      </c>
-      <c r="AA27" s="9">
-        <f t="shared" ref="AA27:AK27" si="47">AA3/Z3-1</f>
-        <v>0.16044556536359789</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="47"/>
-        <v>0.1100000000000001</v>
-      </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="47"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="47"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AK27" s="9">
-        <f t="shared" si="47"/>
-        <v>3.0000000000000027E-2</v>
+      <c r="AA26" s="7">
+        <f>AA24/AA25</f>
+        <v>1.5780938235294117</v>
+      </c>
+      <c r="AB26" s="7">
+        <f>AB24/AB25</f>
+        <v>4.1483878829411767</v>
+      </c>
+      <c r="AC26" s="7">
+        <f t="shared" ref="AC26:AK26" si="41">AC24/AC25</f>
+        <v>4.8175783615196845</v>
+      </c>
+      <c r="AD26" s="7">
+        <f t="shared" si="41"/>
+        <v>5.1307842770934062</v>
+      </c>
+      <c r="AE26" s="7">
+        <f t="shared" si="41"/>
+        <v>5.4059163814249036</v>
+      </c>
+      <c r="AF26" s="7">
+        <f t="shared" si="41"/>
+        <v>5.6350286158281451</v>
+      </c>
+      <c r="AG26" s="7">
+        <f t="shared" si="41"/>
+        <v>5.8726821317155045</v>
+      </c>
+      <c r="AH26" s="7">
+        <f t="shared" si="41"/>
+        <v>6.1191829868001895</v>
+      </c>
+      <c r="AI26" s="7">
+        <f t="shared" si="41"/>
+        <v>6.3748482399611497</v>
+      </c>
+      <c r="AJ26" s="7">
+        <f t="shared" si="41"/>
+        <v>6.6400063588192122</v>
+      </c>
+      <c r="AK26" s="7">
+        <f t="shared" si="41"/>
+        <v>6.9149976431488804</v>
       </c>
     </row>
     <row r="28" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="9">
-        <f t="shared" ref="G28:M28" si="48">G5/G3</f>
-        <v>0.26581352833638022</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.26200941915227627</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.26695291679005029</v>
-      </c>
-      <c r="J28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.27672242699177768</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.26547921967769289</v>
+        <f t="shared" ref="K28:M28" si="42">K3/G3-1</f>
+        <v>0.29323583180987201</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.28029020556227324</v>
+        <f t="shared" si="42"/>
+        <v>0.29827315541601251</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="48"/>
-        <v>0.29399472063352405</v>
+        <f t="shared" si="42"/>
+        <v>0.34616523541604982</v>
       </c>
       <c r="N28" s="9">
-        <f>N5/N3</f>
-        <v>0.32266065388951526</v>
+        <f>N3/J3-1</f>
+        <v>0.25744258576694068</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="49">O5/O3</f>
-        <v>0.30295885889425911</v>
+        <f t="shared" ref="O28:R28" si="43">O3/K3-1</f>
+        <v>0.19918009612666099</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="49"/>
-        <v>0.32</v>
+        <f t="shared" si="43"/>
+        <v>0.1683192261185007</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="43"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="49"/>
-        <v>0.34</v>
-      </c>
-      <c r="Y28" s="9">
-        <f>Y5/Y3</f>
-        <v>0.26816905801621954</v>
-      </c>
+        <f t="shared" si="43"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="Y28" s="9"/>
       <c r="Z28" s="9">
-        <f>Z5/Z3</f>
-        <v>0.29216957905482505</v>
+        <f>Z3/Y3-1</f>
+        <v>0.29858078602620086</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AK28" si="50">AA5/AA3</f>
-        <v>0.32424343722347854</v>
+        <f t="shared" ref="AA28:AK28" si="44">AA3/Z3-1</f>
+        <v>0.16499429532216414</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.34</v>
+        <f t="shared" si="44"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.36</v>
+        <f t="shared" si="44"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.37</v>
+        <f t="shared" si="44"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.38</v>
+        <f t="shared" si="44"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.39</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.4</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.39999999999999997</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.4</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.39999999999999997</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="50"/>
-        <v>0.4</v>
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="29" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="G29" s="9">
+        <f t="shared" ref="G29:M29" si="45">G5/G3</f>
+        <v>0.26581352833638022</v>
+      </c>
+      <c r="H29" s="9">
+        <f t="shared" si="45"/>
+        <v>0.26200941915227627</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="45"/>
+        <v>0.26695291679005029</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="45"/>
+        <v>0.27672242699177768</v>
+      </c>
       <c r="K29" s="9">
-        <f t="shared" ref="K29:M29" si="51">K6/G6-1</f>
-        <v>0.24970828471411899</v>
+        <f t="shared" si="45"/>
+        <v>0.26547921967769289</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="51"/>
-        <v>0.34104750304506704</v>
+        <f t="shared" si="45"/>
+        <v>0.28029020556227324</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="51"/>
-        <v>0.54914809960681521</v>
+        <f t="shared" si="45"/>
+        <v>0.29399472063352405</v>
       </c>
       <c r="N29" s="9">
-        <f>N6/J6-1</f>
-        <v>0.45657276995305152</v>
+        <f>N5/N3</f>
+        <v>0.32266065388951526</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="52">O6/K6-1</f>
-        <v>0.43790849673202614</v>
+        <f t="shared" ref="O29:R29" si="46">O5/O3</f>
+        <v>0.30295885889425911</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="52"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="46"/>
+        <v>0.30273235354998962</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="52"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="46"/>
+        <v>0.31</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="52"/>
-        <v>0.29999999999999982</v>
-      </c>
-      <c r="Y29" s="9"/>
+        <f t="shared" si="46"/>
+        <v>0.32</v>
+      </c>
+      <c r="Y29" s="9">
+        <f>Y5/Y3</f>
+        <v>0.26816905801621954</v>
+      </c>
       <c r="Z29" s="9">
-        <f>Z6/Y6-1</f>
-        <v>0.39538414819313683</v>
+        <f>Z5/Z3</f>
+        <v>0.29216957905482505</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AK29" si="53">AA6/Z6-1</f>
-        <v>0.33214363438520111</v>
+        <f t="shared" ref="AA29:AK29" si="47">AA5/AA3</f>
+        <v>0.3092797921719117</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="47"/>
+        <v>0.32</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="53"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="53"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="53"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="53"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO29" s="9">
-        <v>-0.01</v>
+        <f t="shared" si="47"/>
+        <v>0.33</v>
       </c>
     </row>
     <row r="30" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="9">
-        <f t="shared" ref="G30:M30" si="54">G9/G3</f>
-        <v>1.1151736745886653E-2</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" si="54"/>
-        <v>8.4772370486656205E-3</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" si="54"/>
-        <v>8.4394432928634883E-3</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" si="54"/>
-        <v>2.2540402608449108E-2</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
       <c r="K30" s="9">
-        <f t="shared" si="54"/>
-        <v>1.1309018942606729E-2</v>
+        <f t="shared" ref="K30:M30" si="48">K6/G6-1</f>
+        <v>0.24970828471411899</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="54"/>
-        <v>1.4026602176541716E-2</v>
+        <f t="shared" si="48"/>
+        <v>0.34104750304506704</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="54"/>
-        <v>1.0338759348878134E-2</v>
+        <f t="shared" si="48"/>
+        <v>0.54914809960681521</v>
       </c>
       <c r="N30" s="9">
-        <f>N9/N3</f>
-        <v>1.3979706877113867E-2</v>
+        <f>N6/J6-1</f>
+        <v>0.45657276995305152</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="55">O9/O3</f>
-        <v>2.1926205351880234E-2</v>
+        <f t="shared" ref="O30:R30" si="49">O6/K6-1</f>
+        <v>0.43790849673202614</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="55"/>
-        <v>1.9557331370590403E-2</v>
+        <f t="shared" si="49"/>
+        <v>0.18437783832879218</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="55"/>
-        <v>1.7789169647468392E-2</v>
+        <f t="shared" si="49"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="55"/>
-        <v>1.8234400274496351E-2</v>
-      </c>
-      <c r="Y30" s="9">
-        <f>Y9/Y3</f>
-        <v>1.290548970679975E-2</v>
-      </c>
+        <f t="shared" si="49"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="Y30" s="9"/>
       <c r="Z30" s="9">
-        <f>Z9/Z3</f>
-        <v>1.2430192758061608E-2</v>
+        <f>Z6/Y6-1</f>
+        <v>0.39538414819313683</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30:AK30" si="56">AA9/AA3</f>
-        <v>1.9249776195478376E-2</v>
+        <f t="shared" ref="AA30:AK30" si="50">AA6/Z6-1</f>
+        <v>0.25170837867247009</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="56"/>
-        <v>0.02</v>
+        <f t="shared" si="50"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AO30" s="9">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="31" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:M31" si="57">G10/G3</f>
-        <v>4.570383912248629E-3</v>
+        <f t="shared" ref="G31:M31" si="51">G9/G3</f>
+        <v>1.1151736745886653E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="57"/>
-        <v>6.2794348508634227E-3</v>
+        <f t="shared" si="51"/>
+        <v>8.4772370486656205E-3</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="57"/>
-        <v>6.9588392063962105E-3</v>
+        <f t="shared" si="51"/>
+        <v>8.4394432928634883E-3</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="57"/>
-        <v>5.5287779982988372E-3</v>
+        <f t="shared" si="51"/>
+        <v>2.2540402608449108E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="57"/>
-        <v>6.2199604184337018E-3</v>
+        <f t="shared" si="51"/>
+        <v>1.1309018942606729E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="57"/>
-        <v>4.7158403869407492E-3</v>
+        <f t="shared" si="51"/>
+        <v>1.4026602176541716E-2</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="57"/>
-        <v>6.8191816981962167E-3</v>
+        <f t="shared" si="51"/>
+        <v>1.0338759348878134E-2</v>
       </c>
       <c r="N31" s="9">
-        <f>N10/N3</f>
-        <v>8.1172491544532141E-3</v>
+        <f>N9/N3</f>
+        <v>1.3979706877113867E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="58">O10/O3</f>
-        <v>7.8981492396557832E-3</v>
+        <f t="shared" ref="O31:R31" si="52">O9/O3</f>
+        <v>2.1926205351880234E-2</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="58"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="52"/>
+        <v>1.5731732560546469E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="58"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="52"/>
+        <v>1.7789169647468392E-2</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="58"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="52"/>
+        <v>1.8234400274496351E-2</v>
       </c>
       <c r="Y31" s="9">
-        <f>Y10/Y3</f>
-        <v>5.8873986275732992E-3</v>
+        <f>Y9/Y3</f>
+        <v>1.290548970679975E-2</v>
       </c>
       <c r="Z31" s="9">
-        <f>Z10/Z3</f>
-        <v>6.5153425809163501E-3</v>
+        <f>Z9/Z3</f>
+        <v>1.2430192758061608E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31:AK31" si="59">AA10/AA3</f>
-        <v>7.9776454211923486E-3</v>
+        <f t="shared" ref="AA31:AK31" si="53">AA9/AA3</f>
+        <v>1.8298355982918096E-2</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="59"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.02</v>
       </c>
       <c r="AN31" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO31" s="5">
-        <f>NPV(AO30,AA23:EP23)</f>
-        <v>6407.6652977204085</v>
+        <v>57</v>
+      </c>
+      <c r="AO31" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="32" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" ref="G32:M32" si="60">G13/G3</f>
-        <v>1.6087751371115143E-2</v>
+        <f t="shared" ref="G32:M32" si="54">G10/G3</f>
+        <v>4.570383912248629E-3</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="60"/>
-        <v>5.3218210361067469E-2</v>
+        <f t="shared" si="54"/>
+        <v>6.2794348508634227E-3</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="60"/>
-        <v>6.6183002665087295E-2</v>
+        <f t="shared" si="54"/>
+        <v>6.9588392063962105E-3</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="60"/>
-        <v>3.8843209526509749E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.5287779982988372E-3</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="60"/>
-        <v>3.025162567147293E-2</v>
+        <f t="shared" si="54"/>
+        <v>6.2199604184337018E-3</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="60"/>
-        <v>7.1584038694074925E-2</v>
+        <f t="shared" si="54"/>
+        <v>4.7158403869407492E-3</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="60"/>
-        <v>8.8429388473383261E-2</v>
+        <f t="shared" si="54"/>
+        <v>6.8191816981962167E-3</v>
       </c>
       <c r="N32" s="9">
-        <f>N13/N3</f>
-        <v>9.6956031567080103E-2</v>
+        <f>N10/N3</f>
+        <v>8.1172491544532141E-3</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="61">O13/O3</f>
-        <v>2.9942237416008495E-2</v>
+        <f t="shared" ref="O32:R32" si="55">O10/O3</f>
+        <v>7.8981492396557832E-3</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="61"/>
-        <v>7.8111140318595271E-2</v>
+        <f t="shared" si="55"/>
+        <v>7.3483750776236799E-3</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="61"/>
-        <v>9.309355572983416E-2</v>
+        <f t="shared" si="55"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="61"/>
-        <v>8.372785647762368E-2</v>
+        <f t="shared" si="55"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="Y32" s="9">
-        <f>Y13/Y3</f>
-        <v>4.4759825327510855E-2</v>
+        <f>Y10/Y3</f>
+        <v>5.8873986275732992E-3</v>
       </c>
       <c r="Z32" s="9">
-        <f>Z13/Z3</f>
-        <v>7.4160811865729995E-2</v>
+        <f>Z10/Z3</f>
+        <v>6.5153425809163501E-3</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" ref="AA32:AK32" si="62">AA13/AA3</f>
-        <v>7.3074365197232607E-2</v>
+        <f t="shared" ref="AA32:AK32" si="56">AA10/AA3</f>
+        <v>7.8154701002285994E-3</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.14078272297622468</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.1559822385736889</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.16598223857368882</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.17598223857368886</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.1859822385736889</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.19769114887879871</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.19938346782172292</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.20105935648364798</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.20271897438186498</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" si="62"/>
-        <v>0.20436247948495367</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="AN32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AO32" s="5">
-        <f>Main!D8</f>
-        <v>-1676.2</v>
+        <f>NPV(AO31,AA24:EP24)</f>
+        <v>5339.3770819335095</v>
       </c>
     </row>
     <row r="33" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:M33" si="63">G21/G20</f>
-        <v>-0.2142857142857145</v>
+        <f t="shared" ref="G33:M33" si="57">G13/G3</f>
+        <v>1.6087751371115143E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="63"/>
-        <v>-9.8507462686567224E-2</v>
+        <f t="shared" si="57"/>
+        <v>5.3218210361067469E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="63"/>
-        <v>1.8987341772151913E-2</v>
+        <f t="shared" si="57"/>
+        <v>6.6183002665087295E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="63"/>
-        <v>0.11926605504587169</v>
+        <f t="shared" si="57"/>
+        <v>3.8843209526509749E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="63"/>
-        <v>4.6822742474916468E-2</v>
+        <f t="shared" si="57"/>
+        <v>3.025162567147293E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="63"/>
-        <v>-3.4155597722960181E-2</v>
+        <f t="shared" si="57"/>
+        <v>7.1584038694074925E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="63"/>
-        <v>1.3466154584733563</v>
+        <f t="shared" si="57"/>
+        <v>8.8429388473383261E-2</v>
       </c>
       <c r="N33" s="9">
-        <f>N21/N20</f>
-        <v>0.12248186946011275</v>
+        <f>N13/N3</f>
+        <v>9.6956031567080103E-2</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" ref="O33:R33" si="64">O21/O20</f>
-        <v>-0.71052631578947323</v>
+        <f t="shared" ref="O33:R33" si="58">O13/O3</f>
+        <v>2.9942237416008495E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="64"/>
-        <v>0.15</v>
+        <f t="shared" si="58"/>
+        <v>8.600703788035606E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="64"/>
-        <v>0.15</v>
+        <f t="shared" si="58"/>
+        <v>8.4398286118709212E-2</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="64"/>
-        <v>0.15</v>
+        <f t="shared" si="58"/>
+        <v>7.5893926768295664E-2</v>
       </c>
       <c r="Y33" s="9">
-        <f>Y21/Y20</f>
-        <v>-2.845188284518832E-2</v>
+        <f>Y13/Y3</f>
+        <v>4.4759825327510855E-2</v>
       </c>
       <c r="Z33" s="9">
-        <f>Z21/Z20</f>
-        <v>166.06250000003303</v>
+        <f>Z13/Z3</f>
+        <v>7.4160811865729995E-2</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" ref="AA33:AK33" si="65">AA21/AA20</f>
-        <v>0.10476989912350429</v>
+        <f t="shared" ref="AA33:AK33" si="59">AA13/AA3</f>
+        <v>7.0657622296160169E-2</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.14243242839244519</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.1524324283924452</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.15385688145537429</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.15528133451830339</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.15670578758123249</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.15811641100277388</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.15951333905129067</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.16089670469156939</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.16226663959747653</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="65"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.16362327416449132</v>
       </c>
       <c r="AN33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AO33" s="5">
-        <f>AO31+AO32</f>
-        <v>4731.4652977204087</v>
+        <f>Main!D8</f>
+        <v>-702.49999999999955</v>
       </c>
     </row>
     <row r="34" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:M34" si="66">G22/G20</f>
-        <v>0.33333333333333365</v>
+        <f t="shared" ref="G34:M34" si="60">G22/G21</f>
+        <v>-0.2142857142857145</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="66"/>
-        <v>0.3492537313432838</v>
+        <f t="shared" si="60"/>
+        <v>-9.8507462686567224E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="66"/>
-        <v>0.29324894514767957</v>
+        <f t="shared" si="60"/>
+        <v>1.8987341772151913E-2</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="66"/>
-        <v>0.25229357798165164</v>
+        <f t="shared" si="60"/>
+        <v>0.11926605504587169</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="66"/>
-        <v>0.26421404682274297</v>
+        <f t="shared" si="60"/>
+        <v>4.6822742474916468E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="66"/>
-        <v>0.29032258064516153</v>
+        <f t="shared" si="60"/>
+        <v>-3.4155597722960181E-2</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="66"/>
-        <v>-8.8334133461353839E-2</v>
+        <f t="shared" si="60"/>
+        <v>1.3466154584733563</v>
       </c>
       <c r="N34" s="9">
-        <f>N22/N20</f>
-        <v>0.18775181305398864</v>
+        <f>N22/N21</f>
+        <v>0.12248186946011275</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" ref="O34:R34" si="67">O22/O20</f>
-        <v>0.24561403508771912</v>
+        <f t="shared" ref="O34:R34" si="61">O22/O21</f>
+        <v>-0.71052631578947323</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="67"/>
-        <v>0.2</v>
+        <f t="shared" si="61"/>
+        <v>0.26211849192100528</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="67"/>
-        <v>0.20000000000000004</v>
+        <f t="shared" si="61"/>
+        <v>0.15</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="67"/>
-        <v>0.2</v>
+        <f t="shared" si="61"/>
+        <v>0.15</v>
       </c>
       <c r="Y34" s="9">
-        <f>Y22/Y20</f>
-        <v>0.30711297071129745</v>
+        <f>Y22/Y21</f>
+        <v>-2.845188284518832E-2</v>
       </c>
       <c r="Z34" s="9">
-        <f>Z22/Z20</f>
-        <v>-40.562500000008072</v>
+        <f>Z22/Z21</f>
+        <v>166.06250000003303</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" ref="AA34:AK34" si="68">AA22/AA20</f>
-        <v>0.20239751808927403</v>
+        <f t="shared" ref="AA34:AK34" si="62">AA22/AA21</f>
+        <v>0.13250055615343273</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.17999999999999997</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AJ34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AK34" s="9">
-        <f t="shared" si="68"/>
-        <v>0.18</v>
+        <f t="shared" si="62"/>
+        <v>0.15</v>
       </c>
       <c r="AN34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO34" s="4">
-        <f>AO33/AK24</f>
-        <v>53.102865294280683</v>
+        <v>60</v>
+      </c>
+      <c r="AO34" s="5">
+        <f>AO32+AO33</f>
+        <v>4636.8770819335095</v>
       </c>
     </row>
     <row r="35" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:M35" si="69">G23/G3</f>
-        <v>2.7056672760511855E-2</v>
+        <f t="shared" ref="G35:M35" si="63">G23/G21</f>
+        <v>0.33333333333333365</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="69"/>
-        <v>3.9403453689167936E-2</v>
+        <f t="shared" si="63"/>
+        <v>0.3492537313432838</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="69"/>
-        <v>4.8267693218833237E-2</v>
+        <f t="shared" si="63"/>
+        <v>0.29324894514767957</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="69"/>
-        <v>1.9421604763254854E-2</v>
+        <f t="shared" si="63"/>
+        <v>0.25229357798165164</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="69"/>
-        <v>2.9120723777212261E-2</v>
+        <f t="shared" si="63"/>
+        <v>0.26421404682274297</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="69"/>
-        <v>4.740024183796851E-2</v>
+        <f t="shared" si="63"/>
+        <v>0.29032258064516153</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="69"/>
-        <v>5.9172899252089829E-2</v>
+        <f t="shared" si="63"/>
+        <v>-8.8334133461353839E-2</v>
       </c>
       <c r="N35" s="9">
-        <f>N23/N3</f>
-        <v>9.6505073280721609E-2</v>
+        <f>N23/N21</f>
+        <v>0.18775181305398864</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" ref="O35:R35" si="70">O23/O3</f>
-        <v>1.9686431686903226E-2</v>
+        <f t="shared" ref="O35:R35" si="64">O23/O21</f>
+        <v>0.24561403508771912</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="70"/>
-        <v>3.5394500814888825E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.12746858168761216</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="70"/>
-        <v>5.0029547236940267E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.2</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="70"/>
-        <v>4.6661722464585081E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.2</v>
       </c>
       <c r="Y35" s="9">
-        <f>Y23/Y3</f>
-        <v>3.3608858390517714E-2</v>
+        <f>Y23/Y21</f>
+        <v>0.30711297071129745</v>
       </c>
       <c r="Z35" s="9">
-        <f>Z23/Z3</f>
-        <v>5.9809043415600879E-2</v>
+        <f>Z23/Z21</f>
+        <v>-40.562500000008072</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" ref="AA35:AK35" si="71">AA23/AA3</f>
-        <v>3.8879664060357359E-2</v>
+        <f t="shared" ref="AA35:AK35" si="65">AA23/AA21</f>
+        <v>0.18272144674897145</v>
       </c>
       <c r="AB35" s="9">
-        <f t="shared" si="71"/>
-        <v>8.3588814140222178E-2</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="71"/>
-        <v>9.431591735960719E-2</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AD35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.10135215071348183</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.10829038231269533</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AF35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.11513663085682041</v>
+        <f t="shared" si="65"/>
+        <v>0.18000000000000002</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.1231306890829249</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AH35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.12441652601523259</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.12569430579015534</v>
+        <f t="shared" si="65"/>
+        <v>0.17999999999999997</v>
       </c>
       <c r="AJ35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.1269641925877904</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AK35" s="9">
-        <f t="shared" si="71"/>
-        <v>0.12822635066328816</v>
+        <f t="shared" si="65"/>
+        <v>0.18</v>
       </c>
       <c r="AN35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO35" s="4">
-        <f>Main!D3</f>
-        <v>90.43</v>
+        <f>AO34/AK25</f>
+        <v>52.453360655356448</v>
       </c>
     </row>
     <row r="36" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="AN36" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AO36" s="10">
-        <f>AO34/AO35-1</f>
-        <v>-0.41277379968726446</v>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="9">
+        <f t="shared" ref="G36:M36" si="66">G24/G3</f>
+        <v>2.7056672760511855E-2</v>
+      </c>
+      <c r="H36" s="9">
+        <f t="shared" si="66"/>
+        <v>3.9403453689167936E-2</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="66"/>
+        <v>4.8267693218833237E-2</v>
+      </c>
+      <c r="J36" s="9">
+        <f t="shared" si="66"/>
+        <v>1.9421604763254854E-2</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="shared" si="66"/>
+        <v>2.9120723777212261E-2</v>
+      </c>
+      <c r="L36" s="9">
+        <f t="shared" si="66"/>
+        <v>4.740024183796851E-2</v>
+      </c>
+      <c r="M36" s="9">
+        <f t="shared" si="66"/>
+        <v>5.9172899252089829E-2</v>
+      </c>
+      <c r="N36" s="9">
+        <f>N24/N3</f>
+        <v>9.6505073280721609E-2</v>
+      </c>
+      <c r="O36" s="9">
+        <f t="shared" ref="O36:R36" si="67">O24/O3</f>
+        <v>1.9686431686903226E-2</v>
+      </c>
+      <c r="P36" s="9">
+        <f t="shared" si="67"/>
+        <v>3.518940178016975E-2</v>
+      </c>
+      <c r="Q36" s="9">
+        <f t="shared" si="67"/>
+        <v>4.4377621989709043E-2</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" si="67"/>
+        <v>4.1569668153521866E-2</v>
+      </c>
+      <c r="Y36" s="9">
+        <f>Y24/Y3</f>
+        <v>3.3608858390517714E-2</v>
+      </c>
+      <c r="Z36" s="9">
+        <f>Z24/Z3</f>
+        <v>5.9809043415600879E-2</v>
+      </c>
+      <c r="AA36" s="9">
+        <f t="shared" ref="AA36:AK36" si="68">AA24/AA3</f>
+        <v>3.5953304141871534E-2</v>
+      </c>
+      <c r="AB36" s="9">
+        <f t="shared" si="68"/>
+        <v>8.5145630708992448E-2</v>
+      </c>
+      <c r="AC36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.2411925558413141E-2</v>
+      </c>
+      <c r="AD36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.3733252741620796E-2</v>
+      </c>
+      <c r="AE36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.4961139526131111E-2</v>
+      </c>
+      <c r="AF36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.6102679092550769E-2</v>
+      </c>
+      <c r="AG36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.7238586896604889E-2</v>
+      </c>
+      <c r="AH36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.8369023463094105E-2</v>
+      </c>
+      <c r="AI36" s="9">
+        <f t="shared" si="68"/>
+        <v>9.9494149813616858E-2</v>
+      </c>
+      <c r="AJ36" s="9">
+        <f t="shared" si="68"/>
+        <v>0.10061412750165508</v>
+      </c>
+      <c r="AK36" s="9">
+        <f t="shared" si="68"/>
+        <v>0.10172911864809328</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO36" s="4">
+        <f>Main!D3</f>
+        <v>86.88</v>
       </c>
     </row>
     <row r="37" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="AN37" t="s">
+      <c r="AN37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO37" s="10">
+        <f>AO35/AO36-1</f>
+        <v>-0.39625505691348473</v>
+      </c>
+    </row>
+    <row r="38" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="AN38" t="s">
         <v>64</v>
       </c>
-      <c r="AO37" s="6" t="s">
+      <c r="AO38" s="6" t="s">
         <v>65</v>
       </c>
     </row>

--- a/Financial Analysis/FOUR.xlsx
+++ b/Financial Analysis/FOUR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB4335F-B45E-445C-AE42-7D724302729A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0958405B-A554-45DD-996B-543D26445E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9FA048E8-CD64-4FE4-A115-46129781B051}"/>
   </bookViews>
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -305,8 +305,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,14 +749,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>86.88</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="E3" s="3">
-        <v>45875</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45875</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45966</v>
@@ -782,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>7680.1919999999991</v>
+        <v>6992.4399999999987</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +822,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>8382.6919999999991</v>
+        <v>7694.9399999999987</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +1981,7 @@
       </c>
     </row>
     <row r="14" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+      <c r="B14" t="s">
         <v>66</v>
       </c>
       <c r="G14" s="8"/>
@@ -1995,15 +1993,15 @@
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="12">
+      <c r="P14" s="5">
         <v>3.1</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
-      <c r="AA14" s="12">
-        <f>SUM(O14:R14)</f>
+      <c r="AA14" s="5">
+        <f t="shared" ref="AA14:AA19" si="20">SUM(O14:R14)</f>
         <v>3.1</v>
       </c>
       <c r="AB14" s="8"/>
@@ -2052,11 +2050,11 @@
         <v>-19.2</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" ref="Q15:R15" si="20">M15*1.2</f>
+        <f t="shared" ref="Q15:R15" si="21">M15*1.2</f>
         <v>-11.639999999999999</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-16.32</v>
       </c>
       <c r="Y15" s="5">
@@ -2068,7 +2066,7 @@
         <v>-33.700000000000003</v>
       </c>
       <c r="AA15" s="5">
-        <f>SUM(O15:R15)</f>
+        <f t="shared" si="20"/>
         <v>-59.56</v>
       </c>
       <c r="AB15" s="5">
@@ -2076,39 +2074,39 @@
         <v>-62.538000000000004</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" ref="AC15:AK15" si="21">AB15*1.05</f>
+        <f t="shared" ref="AC15:AK15" si="22">AB15*1.05</f>
         <v>-65.664900000000003</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-68.948145000000011</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-72.395552250000009</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-76.01532986250001</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-79.816096355625021</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-83.806901173406274</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-87.997246232076591</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-92.397108543680432</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-97.016963970864452</v>
       </c>
     </row>
@@ -2161,7 +2159,7 @@
         <v>-1.7999999999999998</v>
       </c>
       <c r="AA16" s="5">
-        <f>SUM(O16:R16)</f>
+        <f t="shared" si="20"/>
         <v>4.2</v>
       </c>
       <c r="AB16" s="5">
@@ -2244,7 +2242,7 @@
         <v>-66.7</v>
       </c>
       <c r="AA17" s="5">
-        <f>SUM(O17:R17)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AB17" s="5">
@@ -2327,7 +2325,7 @@
         <v>289</v>
       </c>
       <c r="AA18" s="5">
-        <f>SUM(O18:R18)</f>
+        <f t="shared" si="20"/>
         <v>-2.2000000000000002</v>
       </c>
       <c r="AB18" s="5">
@@ -2410,7 +2408,7 @@
         <v>61.8</v>
       </c>
       <c r="AA19" s="5">
-        <f>SUM(O19:R19)</f>
+        <f t="shared" si="20"/>
         <v>124.9</v>
       </c>
       <c r="AB19" s="5">
@@ -2418,39 +2416,39 @@
         <v>128.64700000000002</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AK19" si="22">AB19*1.03</f>
+        <f t="shared" ref="AC19:AK19" si="23">AB19*1.03</f>
         <v>132.50641000000002</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>136.48160230000002</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>140.57605036900003</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>144.79333188007004</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>149.13713183647215</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>153.61124579156632</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>158.21958316531331</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>162.96617066027272</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>167.85515578008091</v>
       </c>
     </row>
@@ -2459,39 +2457,39 @@
         <v>30</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" ref="G20:O20" si="23">SUM(G15:G19)</f>
+        <f t="shared" ref="G20:O20" si="24">SUM(G15:G19)</f>
         <v>-8.0000000000000018</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.39999999999999947</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-2.6999999999999993</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.6</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-8.5000000000000018</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.5</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>288.7</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-38.100000000000009</v>
       </c>
       <c r="O20" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13.999999999999998</v>
       </c>
       <c r="P20" s="5">
@@ -2499,11 +2497,11 @@
         <v>27.400000000000002</v>
       </c>
       <c r="Q20" s="5">
-        <f t="shared" ref="Q20:R20" si="24">SUM(Q14:Q19)</f>
+        <f t="shared" ref="Q20:R20" si="25">SUM(Q14:Q19)</f>
         <v>16.86</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>12.18</v>
       </c>
       <c r="Y20" s="5">
@@ -2515,47 +2513,47 @@
         <v>248.60000000000002</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" ref="AA20:AK20" si="25">SUM(AA14:AA19)</f>
+        <f t="shared" ref="AA20:AK20" si="26">SUM(AA14:AA19)</f>
         <v>70.44</v>
       </c>
       <c r="AB20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>66.109000000000009</v>
       </c>
       <c r="AC20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>66.841510000000014</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>67.533457300000009</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>68.180498119000021</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>68.778002017570032</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>69.321035480847129</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>69.804344618160044</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>70.222336933236718</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>70.569062116592292</v>
       </c>
       <c r="AK20" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>70.838191809216454</v>
       </c>
     </row>
@@ -2564,51 +2562,51 @@
         <v>25</v>
       </c>
       <c r="G21" s="8">
-        <f t="shared" ref="G21:O21" si="26">G13-G20</f>
+        <f t="shared" ref="G21:O21" si="27">G13-G20</f>
         <v>16.799999999999983</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>33.499999999999979</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>47.399999999999963</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21.799999999999976</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29.899999999999949</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>52.69999999999996</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-208.29999999999993</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>124.10000000000007</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.400000000000007</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21:R21" si="27">P13-P20</f>
+        <f t="shared" ref="P21:R21" si="28">P13-P20</f>
         <v>55.700000000000017</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>71.385159999999971</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>65.235599999999977</v>
       </c>
       <c r="Y21" s="8">
@@ -2628,39 +2626,39 @@
         <v>547.33953559999998</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" ref="AC21:AK21" si="28">AC13-AC20</f>
+        <f t="shared" ref="AC21:AK21" si="29">AC13-AC20</f>
         <v>635.6327271020001</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>676.95720909710008</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>713.25822107158422</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>743.48735767045969</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>774.84343349798587</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>807.36682990020404</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>841.09937972024727</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>876.08442107405722</v>
       </c>
       <c r="AK21" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>912.36685321546418</v>
       </c>
     </row>
@@ -2699,11 +2697,11 @@
         <v>14.6</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" ref="P22:R22" si="29">Q21*0.15</f>
+        <f t="shared" ref="Q22:R22" si="30">Q21*0.15</f>
         <v>10.707773999999995</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>9.7853399999999962</v>
       </c>
       <c r="Y22" s="5">
@@ -2723,39 +2721,39 @@
         <v>82.100930339999991</v>
       </c>
       <c r="AC22" s="5">
-        <f t="shared" ref="AC22:AK22" si="30">AC21*0.15</f>
+        <f t="shared" ref="AC22:AK22" si="31">AC21*0.15</f>
         <v>95.344909065300016</v>
       </c>
       <c r="AD22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>101.54358136456501</v>
       </c>
       <c r="AE22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>106.98873316073762</v>
       </c>
       <c r="AF22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>111.52310365056896</v>
       </c>
       <c r="AG22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>116.22651502469787</v>
       </c>
       <c r="AH22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>121.1050244850306</v>
       </c>
       <c r="AI22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>126.16490695803708</v>
       </c>
       <c r="AJ22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>131.41266316110858</v>
       </c>
       <c r="AK22" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>136.85502798231963</v>
       </c>
     </row>
@@ -2794,11 +2792,11 @@
         <v>7.1</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" ref="P23:R23" si="31">Q21*0.2</f>
+        <f t="shared" ref="Q23:R23" si="32">Q21*0.2</f>
         <v>14.277031999999995</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13.047119999999996</v>
       </c>
       <c r="Y23" s="5">
@@ -2818,39 +2816,39 @@
         <v>98.521116407999997</v>
       </c>
       <c r="AC23" s="5">
-        <f t="shared" ref="AC23:AK23" si="32">AC21*0.18</f>
+        <f t="shared" ref="AC23:AK23" si="33">AC21*0.18</f>
         <v>114.41389087836002</v>
       </c>
       <c r="AD23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>121.852297637478</v>
       </c>
       <c r="AE23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>128.38647979288515</v>
       </c>
       <c r="AF23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>133.82772438068275</v>
       </c>
       <c r="AG23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>139.47181802963746</v>
       </c>
       <c r="AH23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>145.32602938203672</v>
       </c>
       <c r="AI23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>151.39788834964449</v>
       </c>
       <c r="AJ23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>157.6951957933303</v>
       </c>
       <c r="AK23" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>164.22603357878356</v>
       </c>
     </row>
@@ -2859,51 +2857,51 @@
         <v>28</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" ref="G24:O24" si="33">G21-G22-G23</f>
+        <f t="shared" ref="G24:O24" si="34">G21-G22-G23</f>
         <v>14.799999999999985</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>25.099999999999977</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>32.599999999999966</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13.699999999999974</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20.599999999999952</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>39.19999999999996</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>53.800000000000075</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>85.600000000000065</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>16.700000000000006</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24:R24" si="34">P21-P22-P23</f>
+        <f t="shared" ref="P24:R24" si="35">P21-P22-P23</f>
         <v>34.000000000000014</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>46.400353999999979</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>42.403139999999979</v>
       </c>
       <c r="Y24" s="8">
@@ -2923,39 +2921,39 @@
         <v>366.71748885199997</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" ref="AC24:AK24" si="35">AC21-AC22-AC23</f>
+        <f t="shared" ref="AC24:AK24" si="36">AC21-AC22-AC23</f>
         <v>425.87392715834005</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>453.56133009505703</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>477.88300811796142</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>498.13652963920799</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>519.14510044365056</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>540.93577603313668</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>563.53658441256562</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>586.97656211961828</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>611.28579165436099</v>
       </c>
       <c r="AL24" s="1">
@@ -2963,435 +2961,435 @@
         <v>605.1729337378174</v>
       </c>
       <c r="AM24" s="1">
-        <f t="shared" ref="AM24:CX24" si="36">AL24*(1+$AO$30)</f>
+        <f t="shared" ref="AM24:CX24" si="37">AL24*(1+$AO$30)</f>
         <v>599.12120440043918</v>
       </c>
       <c r="AN24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>593.12999235643474</v>
       </c>
       <c r="AO24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>587.19869243287042</v>
       </c>
       <c r="AP24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>581.32670550854175</v>
       </c>
       <c r="AQ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>575.51343845345627</v>
       </c>
       <c r="AR24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>569.75830406892169</v>
       </c>
       <c r="AS24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>564.06072102823248</v>
       </c>
       <c r="AT24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>558.4201138179501</v>
       </c>
       <c r="AU24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>552.83591267977056</v>
       </c>
       <c r="AV24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>547.30755355297288</v>
       </c>
       <c r="AW24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>541.83447801744319</v>
       </c>
       <c r="AX24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>536.4161332372687</v>
       </c>
       <c r="AY24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>531.05197190489605</v>
       </c>
       <c r="AZ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>525.74145218584704</v>
       </c>
       <c r="BA24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>520.4840376639886</v>
       </c>
       <c r="BB24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>515.27919728734867</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>510.12640531447516</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>505.02514126133042</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>499.97488984871711</v>
       </c>
       <c r="BF24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>494.97514095022996</v>
       </c>
       <c r="BG24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>490.02538954072764</v>
       </c>
       <c r="BH24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>485.12513564532037</v>
       </c>
       <c r="BI24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>480.27388428886718</v>
       </c>
       <c r="BJ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>475.47114544597849</v>
       </c>
       <c r="BK24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>470.71643399151873</v>
       </c>
       <c r="BL24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>466.00926965160352</v>
       </c>
       <c r="BM24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>461.3491769550875</v>
       </c>
       <c r="BN24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>456.73568518553662</v>
       </c>
       <c r="BO24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>452.16832833368125</v>
       </c>
       <c r="BP24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>447.64664505034443</v>
       </c>
       <c r="BQ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>443.17017859984099</v>
       </c>
       <c r="BR24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>438.73847681384257</v>
       </c>
       <c r="BS24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>434.35109204570415</v>
       </c>
       <c r="BT24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>430.0075811252471</v>
       </c>
       <c r="BU24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>425.7075053139946</v>
       </c>
       <c r="BV24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>421.45043026085466</v>
       </c>
       <c r="BW24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>417.23592595824613</v>
       </c>
       <c r="BX24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>413.06356669866364</v>
       </c>
       <c r="BY24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>408.93293103167701</v>
       </c>
       <c r="BZ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>404.84360172136024</v>
       </c>
       <c r="CA24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>400.79516570414665</v>
       </c>
       <c r="CB24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>396.78721404710518</v>
       </c>
       <c r="CC24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>392.81934190663412</v>
       </c>
       <c r="CD24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>388.89114848756776</v>
       </c>
       <c r="CE24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>385.00223700269208</v>
       </c>
       <c r="CF24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>381.15221463266516</v>
       </c>
       <c r="CG24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>377.34069248633853</v>
       </c>
       <c r="CH24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>373.56728556147516</v>
       </c>
       <c r="CI24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>369.83161270586038</v>
       </c>
       <c r="CJ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>366.13329657880178</v>
       </c>
       <c r="CK24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>362.47196361301377</v>
       </c>
       <c r="CL24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>358.84724397688365</v>
       </c>
       <c r="CM24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>355.2587715371148</v>
       </c>
       <c r="CN24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>351.70618382174365</v>
       </c>
       <c r="CO24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>348.18912198352621</v>
       </c>
       <c r="CP24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>344.70723076369092</v>
       </c>
       <c r="CQ24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>341.260158456054</v>
       </c>
       <c r="CR24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>337.84755687149345</v>
       </c>
       <c r="CS24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>334.46908130277853</v>
       </c>
       <c r="CT24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>331.12439048975074</v>
       </c>
       <c r="CU24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>327.8131465848532</v>
       </c>
       <c r="CV24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>324.53501511900464</v>
       </c>
       <c r="CW24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>321.28966496781459</v>
       </c>
       <c r="CX24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>318.07676831813643</v>
       </c>
       <c r="CY24" s="1">
-        <f t="shared" ref="CY24:EP24" si="37">CX24*(1+$AO$30)</f>
+        <f t="shared" ref="CY24:EP24" si="38">CX24*(1+$AO$30)</f>
         <v>314.89600063495504</v>
       </c>
       <c r="CZ24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>311.74704062860548</v>
       </c>
       <c r="DA24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>308.62957022231944</v>
       </c>
       <c r="DB24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>305.54327452009625</v>
       </c>
       <c r="DC24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>302.48784177489529</v>
       </c>
       <c r="DD24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>299.46296335714635</v>
       </c>
       <c r="DE24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>296.46833372357486</v>
       </c>
       <c r="DF24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>293.50365038633913</v>
       </c>
       <c r="DG24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>290.56861388247574</v>
       </c>
       <c r="DH24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>287.66292774365098</v>
       </c>
       <c r="DI24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>284.78629846621448</v>
       </c>
       <c r="DJ24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>281.93843548155235</v>
       </c>
       <c r="DK24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>279.11905112673679</v>
       </c>
       <c r="DL24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>276.32786061546943</v>
       </c>
       <c r="DM24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>273.56458200931473</v>
       </c>
       <c r="DN24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>270.82893618922157</v>
       </c>
       <c r="DO24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>268.12064682732932</v>
       </c>
       <c r="DP24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>265.43944035905605</v>
       </c>
       <c r="DQ24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>262.78504595546548</v>
       </c>
       <c r="DR24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>260.1571954959108</v>
       </c>
       <c r="DS24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>257.55562354095167</v>
       </c>
       <c r="DT24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>254.98006730554215</v>
       </c>
       <c r="DU24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>252.43026663248673</v>
       </c>
       <c r="DV24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>249.90596396616186</v>
       </c>
       <c r="DW24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>247.40690432650024</v>
       </c>
       <c r="DX24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>244.93283528323522</v>
       </c>
       <c r="DY24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>242.48350693040285</v>
       </c>
       <c r="DZ24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>240.05867186109882</v>
       </c>
       <c r="EA24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>237.65808514248783</v>
       </c>
       <c r="EB24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>235.28150429106296</v>
       </c>
       <c r="EC24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>232.92868924815232</v>
       </c>
       <c r="ED24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>230.5994023556708</v>
       </c>
       <c r="EE24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>228.2934083321141</v>
       </c>
       <c r="EF24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>226.01047424879295</v>
       </c>
       <c r="EG24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>223.75036950630502</v>
       </c>
       <c r="EH24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>221.51286581124197</v>
       </c>
       <c r="EI24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>219.29773715312953</v>
       </c>
       <c r="EJ24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>217.10475978159823</v>
       </c>
       <c r="EK24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>214.93371218378226</v>
       </c>
       <c r="EL24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>212.78437506194444</v>
       </c>
       <c r="EM24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>210.65653131132501</v>
       </c>
       <c r="EN24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>208.54996599821175</v>
       </c>
       <c r="EO24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>206.46446633822961</v>
       </c>
       <c r="EP24" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>204.39982167484732</v>
       </c>
     </row>
@@ -3400,39 +3398,39 @@
         <v>2</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" ref="G25:O25" si="38">67.8+19.8+1.5</f>
+        <f t="shared" ref="G25:O25" si="39">67.8+19.8+1.5</f>
         <v>89.1</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>89.1</v>
       </c>
       <c r="P25" s="5">
@@ -3456,47 +3454,47 @@
         <v>89.1</v>
       </c>
       <c r="AA25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" ref="AA25:AK25" si="40">67.3+19.8+1.3</f>
         <v>88.399999999999991</v>
       </c>
       <c r="AB25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AC25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AD25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AE25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AF25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AG25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AH25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AI25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AJ25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
       <c r="AK25" s="5">
-        <f>67.3+19.8+1.3</f>
+        <f t="shared" si="40"/>
         <v>88.399999999999991</v>
       </c>
     </row>
@@ -3505,51 +3503,51 @@
         <v>29</v>
       </c>
       <c r="G26" s="7">
-        <f t="shared" ref="G26:O26" si="39">G24/G25</f>
+        <f t="shared" ref="G26:O26" si="41">G24/G25</f>
         <v>0.1661054994388326</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.28170594837261481</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.36588103254769888</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.15375982042648681</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.23120089786756401</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.4399551066217729</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.6038159371492714</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.96071829405162823</v>
       </c>
       <c r="O26" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.18742985409652085</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" ref="P26:R26" si="40">P24/P25</f>
+        <f t="shared" ref="P26:R26" si="42">P24/P25</f>
         <v>0.3846153846153848</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.52489088235294101</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.4796735294117645</v>
       </c>
       <c r="Y26" s="7">
@@ -3569,39 +3567,39 @@
         <v>4.1483878829411767</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" ref="AC26:AK26" si="41">AC24/AC25</f>
+        <f t="shared" ref="AC26:AK26" si="43">AC24/AC25</f>
         <v>4.8175783615196845</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5.1307842770934062</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5.4059163814249036</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5.6350286158281451</v>
       </c>
       <c r="AG26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>5.8726821317155045</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.1191829868001895</v>
       </c>
       <c r="AI26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.3748482399611497</v>
       </c>
       <c r="AJ26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.6400063588192122</v>
       </c>
       <c r="AK26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.9149976431488804</v>
       </c>
     </row>
@@ -3614,15 +3612,15 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" ref="K28:M28" si="42">K3/G3-1</f>
+        <f t="shared" ref="K28:M28" si="44">K3/G3-1</f>
         <v>0.29323583180987201</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.29827315541601251</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.34616523541604982</v>
       </c>
       <c r="N28" s="9">
@@ -3630,19 +3628,19 @@
         <v>0.25744258576694068</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="43">O3/K3-1</f>
+        <f t="shared" ref="O28:R28" si="45">O3/K3-1</f>
         <v>0.19918009612666099</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.1683192261185007</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="Y28" s="9"/>
@@ -3651,47 +3649,47 @@
         <v>0.29858078602620086</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AK28" si="44">AA3/Z3-1</f>
+        <f t="shared" ref="AA28:AK28" si="46">AA3/Z3-1</f>
         <v>0.16499429532216414</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3700,31 +3698,31 @@
         <v>50</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:M29" si="45">G5/G3</f>
+        <f t="shared" ref="G29:M29" si="47">G5/G3</f>
         <v>0.26581352833638022</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.26200941915227627</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.26695291679005029</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.27672242699177768</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.26547921967769289</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.28029020556227324</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.29399472063352405</v>
       </c>
       <c r="N29" s="9">
@@ -3732,19 +3730,19 @@
         <v>0.32266065388951526</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="46">O5/O3</f>
+        <f t="shared" ref="O29:R29" si="48">O5/O3</f>
         <v>0.30295885889425911</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.30273235354998962</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.31</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.32</v>
       </c>
       <c r="Y29" s="9">
@@ -3756,47 +3754,47 @@
         <v>0.29216957905482505</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AK29" si="47">AA5/AA3</f>
+        <f t="shared" ref="AA29:AK29" si="49">AA5/AA3</f>
         <v>0.3092797921719117</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.32</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.33</v>
       </c>
     </row>
@@ -3809,15 +3807,15 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9">
-        <f t="shared" ref="K30:M30" si="48">K6/G6-1</f>
+        <f t="shared" ref="K30:M30" si="50">K6/G6-1</f>
         <v>0.24970828471411899</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.34104750304506704</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.54914809960681521</v>
       </c>
       <c r="N30" s="9">
@@ -3825,19 +3823,19 @@
         <v>0.45657276995305152</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="49">O6/K6-1</f>
+        <f t="shared" ref="O30:R30" si="51">O6/K6-1</f>
         <v>0.43790849673202614</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.18437783832879218</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="Y30" s="9"/>
@@ -3846,47 +3844,47 @@
         <v>0.39538414819313683</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30:AK30" si="50">AA6/Z6-1</f>
+        <f t="shared" ref="AA30:AK30" si="52">AA6/Z6-1</f>
         <v>0.25170837867247009</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN30" t="s">
@@ -3901,31 +3899,31 @@
         <v>52</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:M31" si="51">G9/G3</f>
+        <f t="shared" ref="G31:M31" si="53">G9/G3</f>
         <v>1.1151736745886653E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>8.4772370486656205E-3</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>8.4394432928634883E-3</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>2.2540402608449108E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.1309018942606729E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.4026602176541716E-2</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.0338759348878134E-2</v>
       </c>
       <c r="N31" s="9">
@@ -3933,19 +3931,19 @@
         <v>1.3979706877113867E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="52">O9/O3</f>
+        <f t="shared" ref="O31:R31" si="54">O9/O3</f>
         <v>2.1926205351880234E-2</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.5731732560546469E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.7789169647468392E-2</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.8234400274496351E-2</v>
       </c>
       <c r="Y31" s="9">
@@ -3957,47 +3955,47 @@
         <v>1.2430192758061608E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31:AK31" si="53">AA9/AA3</f>
+        <f t="shared" ref="AA31:AK31" si="55">AA9/AA3</f>
         <v>1.8298355982918096E-2</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.02</v>
       </c>
       <c r="AN31" t="s">
@@ -4012,31 +4010,31 @@
         <v>53</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" ref="G32:M32" si="54">G10/G3</f>
+        <f t="shared" ref="G32:M32" si="56">G10/G3</f>
         <v>4.570383912248629E-3</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>6.2794348508634227E-3</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>6.9588392063962105E-3</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>5.5287779982988372E-3</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>6.2199604184337018E-3</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>4.7158403869407492E-3</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>6.8191816981962167E-3</v>
       </c>
       <c r="N32" s="9">
@@ -4044,19 +4042,19 @@
         <v>8.1172491544532141E-3</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="55">O10/O3</f>
+        <f t="shared" ref="O32:R32" si="57">O10/O3</f>
         <v>7.8981492396557832E-3</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>7.3483750776236799E-3</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="Y32" s="9">
@@ -4068,47 +4066,47 @@
         <v>6.5153425809163501E-3</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" ref="AA32:AK32" si="56">AA10/AA3</f>
+        <f t="shared" ref="AA32:AK32" si="58">AA10/AA3</f>
         <v>7.8154701002285994E-3</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AN32" t="s">
@@ -4124,31 +4122,31 @@
         <v>54</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:M33" si="57">G13/G3</f>
+        <f t="shared" ref="G33:M33" si="59">G13/G3</f>
         <v>1.6087751371115143E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>5.3218210361067469E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>6.6183002665087295E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>3.8843209526509749E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>3.025162567147293E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>7.1584038694074925E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>8.8429388473383261E-2</v>
       </c>
       <c r="N33" s="9">
@@ -4156,19 +4154,19 @@
         <v>9.6956031567080103E-2</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" ref="O33:R33" si="58">O13/O3</f>
+        <f t="shared" ref="O33:R33" si="60">O13/O3</f>
         <v>2.9942237416008495E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>8.600703788035606E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>8.4398286118709212E-2</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>7.5893926768295664E-2</v>
       </c>
       <c r="Y33" s="9">
@@ -4180,47 +4178,47 @@
         <v>7.4160811865729995E-2</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" ref="AA33:AK33" si="59">AA13/AA3</f>
+        <f t="shared" ref="AA33:AK33" si="61">AA13/AA3</f>
         <v>7.0657622296160169E-2</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.14243242839244519</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.1524324283924452</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.15385688145537429</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.15528133451830339</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.15670578758123249</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.15811641100277388</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.15951333905129067</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.16089670469156939</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.16226663959747653</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.16362327416449132</v>
       </c>
       <c r="AN33" t="s">
@@ -4236,31 +4234,31 @@
         <v>26</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:M34" si="60">G22/G21</f>
+        <f t="shared" ref="G34:M34" si="62">G22/G21</f>
         <v>-0.2142857142857145</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-9.8507462686567224E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.8987341772151913E-2</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.11926605504587169</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>4.6822742474916468E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-3.4155597722960181E-2</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.3466154584733563</v>
       </c>
       <c r="N34" s="9">
@@ -4268,19 +4266,19 @@
         <v>0.12248186946011275</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" ref="O34:R34" si="61">O22/O21</f>
+        <f t="shared" ref="O34:R34" si="63">O22/O21</f>
         <v>-0.71052631578947323</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.26211849192100528</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.15</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.15</v>
       </c>
       <c r="Y34" s="9">
@@ -4292,47 +4290,47 @@
         <v>166.06250000003303</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" ref="AA34:AK34" si="62">AA22/AA21</f>
+        <f t="shared" ref="AA34:AK34" si="64">AA22/AA21</f>
         <v>0.13250055615343273</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AJ34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AK34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.15</v>
       </c>
       <c r="AN34" t="s">
@@ -4348,31 +4346,31 @@
         <v>27</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:M35" si="63">G23/G21</f>
+        <f t="shared" ref="G35:M35" si="65">G23/G21</f>
         <v>0.33333333333333365</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.3492537313432838</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.29324894514767957</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.25229357798165164</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.26421404682274297</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.29032258064516153</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-8.8334133461353839E-2</v>
       </c>
       <c r="N35" s="9">
@@ -4380,19 +4378,19 @@
         <v>0.18775181305398864</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" ref="O35:R35" si="64">O23/O21</f>
+        <f t="shared" ref="O35:R35" si="66">O23/O21</f>
         <v>0.24561403508771912</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.12746858168761216</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.2</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.2</v>
       </c>
       <c r="Y35" s="9">
@@ -4404,47 +4402,47 @@
         <v>-40.562500000008072</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" ref="AA35:AK35" si="65">AA23/AA21</f>
+        <f t="shared" ref="AA35:AK35" si="67">AA23/AA21</f>
         <v>0.18272144674897145</v>
       </c>
       <c r="AB35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AD35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AF35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AH35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="AJ35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AK35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.18</v>
       </c>
       <c r="AN35" t="s">
@@ -4460,31 +4458,31 @@
         <v>55</v>
       </c>
       <c r="G36" s="9">
-        <f t="shared" ref="G36:M36" si="66">G24/G3</f>
+        <f t="shared" ref="G36:M36" si="68">G24/G3</f>
         <v>2.7056672760511855E-2</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3.9403453689167936E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>4.8267693218833237E-2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1.9421604763254854E-2</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2.9120723777212261E-2</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>4.740024183796851E-2</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>5.9172899252089829E-2</v>
       </c>
       <c r="N36" s="9">
@@ -4492,19 +4490,19 @@
         <v>9.6505073280721609E-2</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" ref="O36:R36" si="67">O24/O3</f>
+        <f t="shared" ref="O36:R36" si="69">O24/O3</f>
         <v>1.9686431686903226E-2</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>3.518940178016975E-2</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>4.4377621989709043E-2</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>4.1569668153521866E-2</v>
       </c>
       <c r="Y36" s="9">
@@ -4516,47 +4514,47 @@
         <v>5.9809043415600879E-2</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" ref="AA36:AK36" si="68">AA24/AA3</f>
+        <f t="shared" ref="AA36:AK36" si="70">AA24/AA3</f>
         <v>3.5953304141871534E-2</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>8.5145630708992448E-2</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.2411925558413141E-2</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.3733252741620796E-2</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.4961139526131111E-2</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.6102679092550769E-2</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.7238586896604889E-2</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.8369023463094105E-2</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>9.9494149813616858E-2</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.10061412750165508</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.10172911864809328</v>
       </c>
       <c r="AN36" t="s">
@@ -4564,7 +4562,7 @@
       </c>
       <c r="AO36" s="4">
         <f>Main!D3</f>
-        <v>86.88</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="37" spans="2:41" x14ac:dyDescent="0.3">
@@ -4573,7 +4571,7 @@
       </c>
       <c r="AO37" s="10">
         <f>AO35/AO36-1</f>
-        <v>-0.39625505691348473</v>
+        <v>-0.33687281093101828</v>
       </c>
     </row>
     <row r="38" spans="2:41" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FOUR.xlsx
+++ b/Financial Analysis/FOUR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0958405B-A554-45DD-996B-543D26445E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CE40EF-8523-43C1-BC4B-135982255413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9FA048E8-CD64-4FE4-A115-46129781B051}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>FOUR</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Debt expense</t>
+  </si>
+  <si>
+    <t>Q325 dilu</t>
   </si>
 </sst>
 </file>
@@ -287,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -305,6 +308,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,17 +753,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>79.099999999999994</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>46001</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46001</v>
       </c>
       <c r="G3" s="3">
-        <v>45966</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -767,11 +771,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>67.3+19.8+1.3</f>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -780,7 +784,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>6992.4399999999987</v>
+        <v>6067.8300000000008</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -788,11 +792,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="5">
-        <f>3029.3</f>
-        <v>3029.3</v>
+        <f>1511.5</f>
+        <v>1511.5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -800,11 +804,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="5">
-        <f>688.6+3043.2</f>
-        <v>3731.7999999999997</v>
+        <f>699.4+4019.8</f>
+        <v>4719.2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -813,7 +817,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-702.49999999999955</v>
+        <v>-3207.7</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,7 +826,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>7694.9399999999987</v>
+        <v>9275.5300000000007</v>
       </c>
     </row>
   </sheetData>
@@ -976,12 +980,11 @@
         <v>966.2</v>
       </c>
       <c r="Q3" s="8">
-        <f t="shared" ref="Q3:R3" si="0">M3*1.15</f>
-        <v>1045.58</v>
+        <v>1176.9000000000001</v>
       </c>
       <c r="R3" s="8">
-        <f t="shared" si="0"/>
-        <v>1020.05</v>
+        <f>N3*1.35</f>
+        <v>1197.45</v>
       </c>
       <c r="Y3" s="8">
         <f>SUM(G3:J3)</f>
@@ -993,47 +996,47 @@
       </c>
       <c r="AA3" s="8">
         <f>SUM(O3:R3)</f>
-        <v>3880.13</v>
+        <v>4188.8500000000004</v>
       </c>
       <c r="AB3" s="8">
-        <f>AA3*1.11</f>
-        <v>4306.9443000000001</v>
+        <f>AA3*1.15</f>
+        <v>4817.1774999999998</v>
       </c>
       <c r="AC3" s="8">
-        <f>AB3*1.07</f>
-        <v>4608.4304010000005</v>
+        <f>AB3*1.06</f>
+        <v>5106.2081500000004</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.05</f>
-        <v>4838.8519210500008</v>
+        <v>5361.5185575000005</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.04</f>
-        <v>5032.4059978920013</v>
+        <v>5575.9792998000003</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.03</f>
-        <v>5183.3781778287612</v>
+        <v>5743.2586787940008</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.03</f>
-        <v>5338.8795231636241</v>
+        <v>5915.5564391578209</v>
       </c>
       <c r="AH3" s="8">
-        <f t="shared" ref="AH3:AK3" si="1">AG3*1.03</f>
-        <v>5499.045908858533</v>
+        <f t="shared" ref="AH3:AK3" si="0">AG3*1.03</f>
+        <v>6093.0231323325561</v>
       </c>
       <c r="AI3" s="8">
-        <f t="shared" si="1"/>
-        <v>5664.0172861242891</v>
+        <f t="shared" si="0"/>
+        <v>6275.813826302533</v>
       </c>
       <c r="AJ3" s="8">
-        <f t="shared" si="1"/>
-        <v>5833.9378047080181</v>
+        <f t="shared" si="0"/>
+        <v>6464.0882410916092</v>
       </c>
       <c r="AK3" s="8">
-        <f t="shared" si="1"/>
-        <v>6008.9559388492589</v>
+        <f t="shared" si="0"/>
+        <v>6658.0108883243574</v>
       </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.3">
@@ -1071,12 +1074,11 @@
         <v>673.7</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" ref="Q4:R4" si="2">Q3-Q5</f>
-        <v>721.4502</v>
+        <v>747.9</v>
       </c>
       <c r="R4" s="5">
-        <f t="shared" si="2"/>
-        <v>693.63400000000001</v>
+        <f t="shared" ref="Q4:R4" si="1">R3-R5</f>
+        <v>790.31700000000001</v>
       </c>
       <c r="Y4" s="5">
         <f>SUM(G4:J4)</f>
@@ -1088,47 +1090,47 @@
       </c>
       <c r="AA4" s="5">
         <f>SUM(O4:R4)</f>
-        <v>2680.0842000000002</v>
+        <v>2803.2170000000001</v>
       </c>
       <c r="AB4" s="5">
         <f>AB3-AB5</f>
-        <v>2928.7221239999999</v>
+        <v>3179.3371499999998</v>
       </c>
       <c r="AC4" s="5">
-        <f t="shared" ref="AC4:AK4" si="3">AC3-AC5</f>
-        <v>3087.6483686700003</v>
+        <f t="shared" ref="AC4:AK4" si="2">AC3-AC5</f>
+        <v>3319.0352975000005</v>
       </c>
       <c r="AD4" s="5">
-        <f t="shared" si="3"/>
-        <v>3242.0307871035002</v>
+        <f t="shared" si="2"/>
+        <v>3431.3718768000003</v>
       </c>
       <c r="AE4" s="5">
-        <f t="shared" si="3"/>
-        <v>3371.7120185876411</v>
+        <f t="shared" si="2"/>
+        <v>3568.6267518720006</v>
       </c>
       <c r="AF4" s="5">
-        <f t="shared" si="3"/>
-        <v>3472.8633791452698</v>
+        <f t="shared" si="2"/>
+        <v>3675.6855544281607</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" si="3"/>
-        <v>3577.0492805196282</v>
+        <f t="shared" si="2"/>
+        <v>3785.9561210610054</v>
       </c>
       <c r="AH4" s="5">
-        <f t="shared" si="3"/>
-        <v>3684.3607589352168</v>
+        <f t="shared" si="2"/>
+        <v>3899.5348046928361</v>
       </c>
       <c r="AI4" s="5">
-        <f t="shared" si="3"/>
-        <v>3794.8915817032739</v>
+        <f t="shared" si="2"/>
+        <v>4016.5208488336211</v>
       </c>
       <c r="AJ4" s="5">
-        <f t="shared" si="3"/>
-        <v>3908.738329154372</v>
+        <f t="shared" si="2"/>
+        <v>4137.0164742986299</v>
       </c>
       <c r="AK4" s="5">
-        <f t="shared" si="3"/>
-        <v>4026.0004790290031</v>
+        <f t="shared" si="2"/>
+        <v>4261.1269685275893</v>
       </c>
     </row>
     <row r="5" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1136,52 +1138,52 @@
         <v>13</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:P5" si="4">G3-G4</f>
+        <f t="shared" ref="G5:Q5" si="3">G3-G4</f>
         <v>145.39999999999998</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>166.89999999999998</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>180.29999999999995</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>195.2</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>187.79999999999995</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>231.79999999999995</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>267.30000000000007</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>286.20000000000005</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>257</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>292.5</v>
       </c>
       <c r="Q5" s="8">
-        <f>Q3*0.31</f>
-        <v>324.12979999999999</v>
+        <f t="shared" si="3"/>
+        <v>429.00000000000011</v>
       </c>
       <c r="R5" s="8">
-        <f>R3*0.32</f>
-        <v>326.416</v>
+        <f>R3*0.34</f>
+        <v>407.13300000000004</v>
       </c>
       <c r="Y5" s="8">
         <f>Y3-Y4</f>
@@ -1193,47 +1195,47 @@
       </c>
       <c r="AA5" s="8">
         <f>AA3-AA4</f>
-        <v>1200.0457999999999</v>
+        <v>1385.6330000000003</v>
       </c>
       <c r="AB5" s="8">
-        <f>AB3*0.32</f>
-        <v>1378.222176</v>
+        <f>AB3*0.34</f>
+        <v>1637.8403499999999</v>
       </c>
       <c r="AC5" s="8">
-        <f>AC3*0.33</f>
-        <v>1520.7820323300002</v>
+        <f>AC3*0.35</f>
+        <v>1787.1728525000001</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" ref="AD5:AK5" si="5">AD3*0.33</f>
-        <v>1596.8211339465004</v>
+        <f>AD3*0.36</f>
+        <v>1930.1466807000002</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="5"/>
-        <v>1660.6939793043605</v>
+        <f t="shared" ref="AE5:AK5" si="4">AE3*0.36</f>
+        <v>2007.3525479279999</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="5"/>
-        <v>1710.5147986834913</v>
+        <f t="shared" si="4"/>
+        <v>2067.5731243658402</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="5"/>
-        <v>1761.8302426439959</v>
+        <f t="shared" si="4"/>
+        <v>2129.6003180968155</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="5"/>
-        <v>1814.685149923316</v>
+        <f t="shared" si="4"/>
+        <v>2193.48832763972</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="5"/>
-        <v>1869.1257044210154</v>
+        <f t="shared" si="4"/>
+        <v>2259.2929774689119</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="5"/>
-        <v>1925.1994755536462</v>
+        <f t="shared" si="4"/>
+        <v>2327.0717667929794</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="5"/>
-        <v>1982.9554598202556</v>
+        <f t="shared" si="4"/>
+        <v>2396.8839197967686</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.3">
@@ -1271,64 +1273,62 @@
         <v>130.4</v>
       </c>
       <c r="Q6" s="5">
-        <f>M6*1.2</f>
-        <v>141.84</v>
+        <v>188.4</v>
       </c>
       <c r="R6" s="5">
-        <f>N6*1.2</f>
-        <v>148.91999999999999</v>
+        <v>193</v>
       </c>
       <c r="Y6" s="5">
-        <f t="shared" ref="Y6:Y11" si="6">SUM(G6:J6)</f>
+        <f t="shared" ref="Y6:Y11" si="5">SUM(G6:J6)</f>
         <v>329.3</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" ref="Z6:Z11" si="7">SUM(K6:N6)</f>
+        <f t="shared" ref="Z6:Z11" si="6">SUM(K6:N6)</f>
         <v>459.5</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" ref="AA6:AA11" si="8">SUM(O6:R6)</f>
-        <v>575.16</v>
+        <f t="shared" ref="AA6:AA11" si="7">SUM(O6:R6)</f>
+        <v>665.8</v>
       </c>
       <c r="AB6" s="5">
         <f>AA6*1.12</f>
-        <v>644.17920000000004</v>
+        <v>745.69600000000003</v>
       </c>
       <c r="AC6" s="5">
         <f>AB6*1.07</f>
-        <v>689.27174400000013</v>
+        <v>797.89472000000012</v>
       </c>
       <c r="AD6" s="5">
         <f>AC6*1.04</f>
-        <v>716.84261376000018</v>
+        <v>829.81050880000021</v>
       </c>
       <c r="AE6" s="5">
         <f>AD6*1.03</f>
-        <v>738.34789217280024</v>
+        <v>854.70482406400026</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6*1.02</f>
-        <v>753.11485001625624</v>
+        <v>871.79892054528034</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.02</f>
-        <v>768.17714701658133</v>
+        <v>889.23489895618593</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH6:AK6" si="9">AG6*1.02</f>
-        <v>783.54068995691296</v>
+        <f t="shared" ref="AH6:AK6" si="8">AG6*1.02</f>
+        <v>907.01959693530966</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="9"/>
-        <v>799.21150375605123</v>
+        <f t="shared" si="8"/>
+        <v>925.15998887401588</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="9"/>
-        <v>815.19573383117222</v>
+        <f t="shared" si="8"/>
+        <v>943.66318865149617</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="9"/>
-        <v>831.49964850779565</v>
+        <f t="shared" si="8"/>
+        <v>962.53645242452615</v>
       </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.3">
@@ -1366,22 +1366,22 @@
         <v>-0.9</v>
       </c>
       <c r="Q7" s="5">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="R7" s="5">
         <v>0</v>
       </c>
       <c r="Y7" s="5">
+        <f t="shared" si="5"/>
+        <v>23.1</v>
+      </c>
+      <c r="Z7" s="5">
         <f t="shared" si="6"/>
-        <v>23.1</v>
-      </c>
-      <c r="Z7" s="5">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="5">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="AA7" s="5">
-        <f t="shared" si="8"/>
-        <v>-4.6000000000000005</v>
+        <v>-7.4</v>
       </c>
       <c r="AB7" s="5">
         <v>0</v>
@@ -1449,24 +1449,22 @@
         <v>57.6</v>
       </c>
       <c r="Q8" s="5">
-        <f t="shared" ref="Q8:R8" si="10">M8*1.3</f>
-        <v>67.08</v>
+        <v>85.8</v>
       </c>
       <c r="R8" s="5">
-        <f t="shared" si="10"/>
-        <v>73.320000000000007</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="5">
+        <f t="shared" si="5"/>
+        <v>153.79999999999998</v>
+      </c>
+      <c r="Z8" s="5">
         <f t="shared" si="6"/>
-        <v>153.79999999999998</v>
-      </c>
-      <c r="Z8" s="5">
+        <v>199.5</v>
+      </c>
+      <c r="AA8" s="5">
         <f t="shared" si="7"/>
-        <v>199.5</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="8"/>
-        <v>254</v>
+        <v>289.39999999999998</v>
       </c>
       <c r="AB8" s="5">
         <v>0</v>
@@ -1534,62 +1532,62 @@
         <v>15.2</v>
       </c>
       <c r="Q9" s="5">
-        <v>18.600000000000001</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="R9" s="5">
-        <v>18.600000000000001</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="5">
+        <f t="shared" si="5"/>
+        <v>33.1</v>
+      </c>
+      <c r="Z9" s="5">
         <f t="shared" si="6"/>
-        <v>33.1</v>
-      </c>
-      <c r="Z9" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="AA9" s="5">
         <f t="shared" si="7"/>
-        <v>41.4</v>
-      </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="8"/>
-        <v>71</v>
+        <v>105.1</v>
       </c>
       <c r="AB9" s="5">
         <f>AB3*0.02</f>
-        <v>86.138885999999999</v>
+        <v>96.343549999999993</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" ref="AC9:AK9" si="11">AC3*0.02</f>
-        <v>92.168608020000008</v>
+        <f t="shared" ref="AC9:AK9" si="9">AC3*0.02</f>
+        <v>102.12416300000001</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="11"/>
-        <v>96.777038421000015</v>
+        <f t="shared" si="9"/>
+        <v>107.23037115000001</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" si="11"/>
-        <v>100.64811995784002</v>
+        <f t="shared" si="9"/>
+        <v>111.519585996</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="11"/>
-        <v>103.66756355657523</v>
+        <f t="shared" si="9"/>
+        <v>114.86517357588002</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="11"/>
-        <v>106.77759046327249</v>
+        <f t="shared" si="9"/>
+        <v>118.31112878315642</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="11"/>
-        <v>109.98091817717066</v>
+        <f t="shared" si="9"/>
+        <v>121.86046264665113</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="11"/>
-        <v>113.28034572248578</v>
+        <f t="shared" si="9"/>
+        <v>125.51627652605066</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="11"/>
-        <v>116.67875609416036</v>
+        <f t="shared" si="9"/>
+        <v>129.28176482183218</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="11"/>
-        <v>120.17911877698518</v>
+        <f t="shared" si="9"/>
+        <v>133.16021776648716</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.3">
@@ -1627,64 +1625,63 @@
         <v>7.1</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ref="Q10:R10" si="12">Q3*0.008</f>
-        <v>8.3646399999999996</v>
+        <v>7.7</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="12"/>
-        <v>8.1603999999999992</v>
+        <f t="shared" ref="Q10:R10" si="10">R3*0.008</f>
+        <v>9.579600000000001</v>
       </c>
       <c r="Y10" s="5">
+        <f t="shared" si="5"/>
+        <v>15.1</v>
+      </c>
+      <c r="Z10" s="5">
         <f t="shared" si="6"/>
-        <v>15.1</v>
-      </c>
-      <c r="Z10" s="5">
+        <v>21.7</v>
+      </c>
+      <c r="AA10" s="5">
         <f t="shared" si="7"/>
-        <v>21.7</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="8"/>
-        <v>30.325039999999998</v>
+        <v>31.079599999999999</v>
       </c>
       <c r="AB10" s="5">
         <f>AB3*0.008</f>
-        <v>34.455554400000004</v>
+        <v>38.537419999999997</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" ref="AC10:AK10" si="13">AC3*0.008</f>
-        <v>36.867443208000005</v>
+        <f t="shared" ref="AC10:AK10" si="11">AC3*0.008</f>
+        <v>40.849665200000004</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="13"/>
-        <v>38.710815368400006</v>
+        <f t="shared" si="11"/>
+        <v>42.892148460000001</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="13"/>
-        <v>40.259247983136014</v>
+        <f t="shared" si="11"/>
+        <v>44.607834398400001</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="13"/>
-        <v>41.467025422630087</v>
+        <f t="shared" si="11"/>
+        <v>45.946069430352004</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="13"/>
-        <v>42.711036185308991</v>
+        <f t="shared" si="11"/>
+        <v>47.324451513262566</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="13"/>
-        <v>43.992367270868264</v>
+        <f t="shared" si="11"/>
+        <v>48.744185058660449</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="13"/>
-        <v>45.312138288994312</v>
+        <f t="shared" si="11"/>
+        <v>50.206510610420267</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="13"/>
-        <v>46.671502437664145</v>
+        <f t="shared" si="11"/>
+        <v>51.712705928732873</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="13"/>
-        <v>48.071647510794072</v>
+        <f t="shared" si="11"/>
+        <v>53.264087106594857</v>
       </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.3">
@@ -1728,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="Y11" s="5">
+        <f t="shared" si="5"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="Z11" s="5">
         <f t="shared" si="6"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB11" s="5">
@@ -1775,52 +1772,52 @@
         <v>47</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" ref="G12:N12" si="14">SUM(G6:G11)</f>
+        <f t="shared" ref="G12:N12" si="12">SUM(G6:G11)</f>
         <v>136.6</v>
       </c>
       <c r="H12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>133</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>135.6</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>167.8</v>
       </c>
       <c r="K12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>166.4</v>
       </c>
       <c r="L12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>172.6</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>186.9</v>
       </c>
       <c r="N12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>200.2</v>
       </c>
       <c r="O12" s="5">
-        <f t="shared" ref="O12:R12" si="15">SUM(O6:O11)</f>
+        <f t="shared" ref="O12:R12" si="13">SUM(O6:O11)</f>
         <v>231.6</v>
       </c>
       <c r="P12" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>209.39999999999998</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="15"/>
-        <v>235.88464000000002</v>
+        <f t="shared" si="13"/>
+        <v>314.39999999999998</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" si="15"/>
-        <v>249.00040000000001</v>
+        <f t="shared" si="13"/>
+        <v>328.57960000000003</v>
       </c>
       <c r="Y12" s="5">
         <f>SUM(Y6:Y11)</f>
@@ -1832,47 +1829,47 @@
       </c>
       <c r="AA12" s="5">
         <f>SUM(AA6:AA11)</f>
-        <v>925.88503999999989</v>
+        <v>1083.9795999999999</v>
       </c>
       <c r="AB12" s="5">
         <f>SUM(AB6:AB11)</f>
-        <v>764.77364039999998</v>
+        <v>880.57696999999996</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" ref="AC12:AK12" si="16">SUM(AC6:AC11)</f>
-        <v>818.30779522800015</v>
+        <f t="shared" ref="AC12:AK12" si="14">SUM(AC6:AC11)</f>
+        <v>940.86854820000019</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="16"/>
-        <v>852.33046754940028</v>
+        <f t="shared" si="14"/>
+        <v>979.93302841000025</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="16"/>
-        <v>879.25526011377622</v>
+        <f t="shared" si="14"/>
+        <v>1010.8322444584003</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="16"/>
-        <v>898.24943899546156</v>
+        <f t="shared" si="14"/>
+        <v>1032.6101635515124</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="16"/>
-        <v>917.66577366516287</v>
+        <f t="shared" si="14"/>
+        <v>1054.8704792526048</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="16"/>
-        <v>937.51397540495191</v>
+        <f t="shared" si="14"/>
+        <v>1077.6242446406211</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="16"/>
-        <v>957.80398776753134</v>
+        <f t="shared" si="14"/>
+        <v>1100.8827760104869</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="16"/>
-        <v>978.54599236299669</v>
+        <f t="shared" si="14"/>
+        <v>1124.6576594020612</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="16"/>
-        <v>999.7504147955749</v>
+        <f t="shared" si="14"/>
+        <v>1148.9607572976081</v>
       </c>
     </row>
     <row r="13" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1880,52 +1877,52 @@
         <v>20</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" ref="G13:N13" si="17">G5-G12</f>
+        <f t="shared" ref="G13:N13" si="15">G5-G12</f>
         <v>8.7999999999999829</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>33.899999999999977</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>44.69999999999996</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>27.399999999999977</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>21.399999999999949</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>59.19999999999996</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>80.400000000000063</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>86.000000000000057</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" ref="O13:R13" si="18">O5-O12</f>
+        <f t="shared" ref="O13:R13" si="16">O5-O12</f>
         <v>25.400000000000006</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>83.100000000000023</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="18"/>
-        <v>88.24515999999997</v>
+        <f t="shared" si="16"/>
+        <v>114.60000000000014</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="18"/>
-        <v>77.415599999999984</v>
+        <f t="shared" si="16"/>
+        <v>78.553400000000011</v>
       </c>
       <c r="Y13" s="8">
         <f>Y5-Y12</f>
@@ -1937,47 +1934,47 @@
       </c>
       <c r="AA13" s="8">
         <f>AA5-AA12</f>
-        <v>274.16075999999998</v>
+        <v>301.65340000000037</v>
       </c>
       <c r="AB13" s="8">
         <f>AB5-AB12</f>
-        <v>613.44853560000001</v>
+        <v>757.26337999999998</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" ref="AC13:AK13" si="19">AC5-AC12</f>
-        <v>702.47423710200007</v>
+        <f t="shared" ref="AC13:AK13" si="17">AC5-AC12</f>
+        <v>846.3043042999999</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="19"/>
-        <v>744.49066639710009</v>
+        <f t="shared" si="17"/>
+        <v>950.21365228999991</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="19"/>
-        <v>781.43871919058427</v>
+        <f t="shared" si="17"/>
+        <v>996.52030346959964</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="19"/>
-        <v>812.26535968802978</v>
+        <f t="shared" si="17"/>
+        <v>1034.9629608143277</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="19"/>
-        <v>844.16446897883304</v>
+        <f t="shared" si="17"/>
+        <v>1074.7298388442107</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="19"/>
-        <v>877.17117451836407</v>
+        <f t="shared" si="17"/>
+        <v>1115.8640829990989</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="19"/>
-        <v>911.32171665348403</v>
+        <f t="shared" si="17"/>
+        <v>1158.410201458425</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="19"/>
-        <v>946.65348319064947</v>
+        <f t="shared" si="17"/>
+        <v>1202.4141073909182</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="19"/>
-        <v>983.20504502468066</v>
+        <f t="shared" si="17"/>
+        <v>1247.9231624991605</v>
       </c>
     </row>
     <row r="14" spans="2:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1996,13 +1993,15 @@
       <c r="P14" s="5">
         <v>3.1</v>
       </c>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
+      <c r="Q14" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="R14" s="11"/>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="5">
-        <f t="shared" ref="AA14:AA19" si="20">SUM(O14:R14)</f>
-        <v>3.1</v>
+        <f t="shared" ref="AA14:AA19" si="18">SUM(O14:R14)</f>
+        <v>12.299999999999999</v>
       </c>
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
@@ -2050,11 +2049,10 @@
         <v>-19.2</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" ref="Q15:R15" si="21">M15*1.2</f>
-        <v>-11.639999999999999</v>
+        <v>-17.5</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="Q15:R15" si="19">N15*1.2</f>
         <v>-16.32</v>
       </c>
       <c r="Y15" s="5">
@@ -2066,48 +2064,48 @@
         <v>-33.700000000000003</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" si="20"/>
-        <v>-59.56</v>
+        <f t="shared" si="18"/>
+        <v>-65.42</v>
       </c>
       <c r="AB15" s="5">
         <f>AA15*1.05</f>
-        <v>-62.538000000000004</v>
+        <v>-68.691000000000003</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" ref="AC15:AK15" si="22">AB15*1.05</f>
-        <v>-65.664900000000003</v>
+        <f t="shared" ref="AC15:AK15" si="20">AB15*1.05</f>
+        <v>-72.125550000000004</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="22"/>
-        <v>-68.948145000000011</v>
+        <f t="shared" si="20"/>
+        <v>-75.731827500000009</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="22"/>
-        <v>-72.395552250000009</v>
+        <f t="shared" si="20"/>
+        <v>-79.518418875000009</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="22"/>
-        <v>-76.01532986250001</v>
+        <f t="shared" si="20"/>
+        <v>-83.494339818750007</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="22"/>
-        <v>-79.816096355625021</v>
+        <f t="shared" si="20"/>
+        <v>-87.669056809687504</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="22"/>
-        <v>-83.806901173406274</v>
+        <f t="shared" si="20"/>
+        <v>-92.052509650171885</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="22"/>
-        <v>-87.997246232076591</v>
+        <f t="shared" si="20"/>
+        <v>-96.655135132680485</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="22"/>
-        <v>-92.397108543680432</v>
+        <f t="shared" si="20"/>
+        <v>-101.48789188931451</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="22"/>
-        <v>-97.016963970864452</v>
+        <f t="shared" si="20"/>
+        <v>-106.56228648378024</v>
       </c>
     </row>
     <row r="16" spans="2:37" x14ac:dyDescent="0.3">
@@ -2145,7 +2143,7 @@
         <v>3</v>
       </c>
       <c r="Q16" s="5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R16" s="5">
         <v>0</v>
@@ -2159,8 +2157,8 @@
         <v>-1.7999999999999998</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" si="20"/>
-        <v>4.2</v>
+        <f t="shared" si="18"/>
+        <v>5.6</v>
       </c>
       <c r="AB16" s="5">
         <v>0</v>
@@ -2242,7 +2240,7 @@
         <v>-66.7</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AB17" s="5">
@@ -2311,7 +2309,7 @@
         <v>0.8</v>
       </c>
       <c r="Q18" s="5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R18" s="5">
         <v>0</v>
@@ -2325,8 +2323,8 @@
         <v>289</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" si="20"/>
-        <v>-2.2000000000000002</v>
+        <f t="shared" si="18"/>
+        <v>-2</v>
       </c>
       <c r="AB18" s="5">
         <v>0</v>
@@ -2394,10 +2392,10 @@
         <v>39.4</v>
       </c>
       <c r="Q19" s="5">
-        <v>28.5</v>
+        <v>60.8</v>
       </c>
       <c r="R19" s="5">
-        <v>28.5</v>
+        <v>60.8</v>
       </c>
       <c r="Y19" s="5">
         <f>SUM(G19:J19)</f>
@@ -2408,48 +2406,48 @@
         <v>61.8</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" si="20"/>
-        <v>124.9</v>
+        <f t="shared" si="18"/>
+        <v>189.5</v>
       </c>
       <c r="AB19" s="5">
         <f>AA19*1.03</f>
-        <v>128.64700000000002</v>
+        <v>195.185</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AK19" si="23">AB19*1.03</f>
-        <v>132.50641000000002</v>
+        <f t="shared" ref="AC19:AK19" si="21">AB19*1.03</f>
+        <v>201.04055</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="23"/>
-        <v>136.48160230000002</v>
+        <f t="shared" si="21"/>
+        <v>207.0717665</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="23"/>
-        <v>140.57605036900003</v>
+        <f t="shared" si="21"/>
+        <v>213.28391949499999</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="23"/>
-        <v>144.79333188007004</v>
+        <f t="shared" si="21"/>
+        <v>219.68243707984999</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="23"/>
-        <v>149.13713183647215</v>
+        <f t="shared" si="21"/>
+        <v>226.27291019224549</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="23"/>
-        <v>153.61124579156632</v>
+        <f t="shared" si="21"/>
+        <v>233.06109749801286</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="23"/>
-        <v>158.21958316531331</v>
+        <f t="shared" si="21"/>
+        <v>240.05293042295324</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="23"/>
-        <v>162.96617066027272</v>
+        <f t="shared" si="21"/>
+        <v>247.25451833564185</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="23"/>
-        <v>167.85515578008091</v>
+        <f t="shared" si="21"/>
+        <v>254.67215388571111</v>
       </c>
     </row>
     <row r="20" spans="2:146" x14ac:dyDescent="0.3">
@@ -2457,39 +2455,39 @@
         <v>30</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" ref="G20:O20" si="24">SUM(G15:G19)</f>
+        <f t="shared" ref="G20:O20" si="22">SUM(G15:G19)</f>
         <v>-8.0000000000000018</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>0.39999999999999947</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>-2.6999999999999993</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>5.6</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>-8.5000000000000018</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>6.5</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>288.7</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>-38.100000000000009</v>
       </c>
       <c r="O20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>13.999999999999998</v>
       </c>
       <c r="P20" s="5">
@@ -2497,12 +2495,12 @@
         <v>27.400000000000002</v>
       </c>
       <c r="Q20" s="5">
-        <f t="shared" ref="Q20:R20" si="25">SUM(Q14:Q19)</f>
-        <v>16.86</v>
+        <f t="shared" ref="Q20:R20" si="23">SUM(Q14:Q19)</f>
+        <v>54.099999999999994</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" si="25"/>
-        <v>12.18</v>
+        <f t="shared" si="23"/>
+        <v>44.48</v>
       </c>
       <c r="Y20" s="5">
         <f>SUM(Y15:Y19)</f>
@@ -2513,48 +2511,48 @@
         <v>248.60000000000002</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" ref="AA20:AK20" si="26">SUM(AA14:AA19)</f>
-        <v>70.44</v>
+        <f t="shared" ref="AA20:AK20" si="24">SUM(AA14:AA19)</f>
+        <v>139.97999999999999</v>
       </c>
       <c r="AB20" s="5">
-        <f t="shared" si="26"/>
-        <v>66.109000000000009</v>
+        <f t="shared" si="24"/>
+        <v>126.494</v>
       </c>
       <c r="AC20" s="5">
-        <f t="shared" si="26"/>
-        <v>66.841510000000014</v>
+        <f t="shared" si="24"/>
+        <v>128.91499999999999</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="26"/>
-        <v>67.533457300000009</v>
+        <f t="shared" si="24"/>
+        <v>131.33993899999999</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" si="26"/>
-        <v>68.180498119000021</v>
+        <f t="shared" si="24"/>
+        <v>133.76550061999998</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="26"/>
-        <v>68.778002017570032</v>
+        <f t="shared" si="24"/>
+        <v>136.18809726109998</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="26"/>
-        <v>69.321035480847129</v>
+        <f t="shared" si="24"/>
+        <v>138.60385338255799</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="26"/>
-        <v>69.804344618160044</v>
+        <f t="shared" si="24"/>
+        <v>141.00858784784097</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="26"/>
-        <v>70.222336933236718</v>
+        <f t="shared" si="24"/>
+        <v>143.39779529027277</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="26"/>
-        <v>70.569062116592292</v>
+        <f t="shared" si="24"/>
+        <v>145.76662644632734</v>
       </c>
       <c r="AK20" s="5">
-        <f t="shared" si="26"/>
-        <v>70.838191809216454</v>
+        <f t="shared" si="24"/>
+        <v>148.10986740193087</v>
       </c>
     </row>
     <row r="21" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2562,52 +2560,52 @@
         <v>25</v>
       </c>
       <c r="G21" s="8">
-        <f t="shared" ref="G21:O21" si="27">G13-G20</f>
+        <f t="shared" ref="G21:O21" si="25">G13-G20</f>
         <v>16.799999999999983</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>33.499999999999979</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>47.399999999999963</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>21.799999999999976</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>29.899999999999949</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>52.69999999999996</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-208.29999999999993</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>124.10000000000007</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>11.400000000000007</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21:R21" si="28">P13-P20</f>
+        <f t="shared" ref="P21:R21" si="26">P13-P20</f>
         <v>55.700000000000017</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" si="28"/>
-        <v>71.385159999999971</v>
+        <f t="shared" si="26"/>
+        <v>60.500000000000142</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" si="28"/>
-        <v>65.235599999999977</v>
+        <f t="shared" si="26"/>
+        <v>34.073400000000014</v>
       </c>
       <c r="Y21" s="8">
         <f>Y13-Y20</f>
@@ -2619,47 +2617,47 @@
       </c>
       <c r="AA21" s="8">
         <f>AA13-AA20</f>
-        <v>203.72075999999998</v>
+        <v>161.67340000000038</v>
       </c>
       <c r="AB21" s="8">
         <f>AB13-AB20</f>
-        <v>547.33953559999998</v>
+        <v>630.76937999999996</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" ref="AC21:AK21" si="29">AC13-AC20</f>
-        <v>635.6327271020001</v>
+        <f t="shared" ref="AC21:AK21" si="27">AC13-AC20</f>
+        <v>717.38930429999994</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="29"/>
-        <v>676.95720909710008</v>
+        <f t="shared" si="27"/>
+        <v>818.87371328999996</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="29"/>
-        <v>713.25822107158422</v>
+        <f t="shared" si="27"/>
+        <v>862.75480284959963</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="29"/>
-        <v>743.48735767045969</v>
+        <f t="shared" si="27"/>
+        <v>898.77486355322776</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="29"/>
-        <v>774.84343349798587</v>
+        <f t="shared" si="27"/>
+        <v>936.1259854616527</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="29"/>
-        <v>807.36682990020404</v>
+        <f t="shared" si="27"/>
+        <v>974.85549515125786</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="29"/>
-        <v>841.09937972024727</v>
+        <f t="shared" si="27"/>
+        <v>1015.0124061681522</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="29"/>
-        <v>876.08442107405722</v>
+        <f t="shared" si="27"/>
+        <v>1056.6474809445908</v>
       </c>
       <c r="AK21" s="8">
-        <f t="shared" si="29"/>
-        <v>912.36685321546418</v>
+        <f t="shared" si="27"/>
+        <v>1099.8132950972297</v>
       </c>
     </row>
     <row r="22" spans="2:146" x14ac:dyDescent="0.3">
@@ -2697,12 +2695,11 @@
         <v>14.6</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" ref="Q22:R22" si="30">Q21*0.15</f>
-        <v>10.707773999999995</v>
+        <v>27.1</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="30"/>
-        <v>9.7853399999999962</v>
+        <f t="shared" ref="Q22:R22" si="28">R21*0.15</f>
+        <v>5.1110100000000021</v>
       </c>
       <c r="Y22" s="5">
         <f>SUM(G22:J22)</f>
@@ -2714,47 +2711,47 @@
       </c>
       <c r="AA22" s="5">
         <f>SUM(O22:R22)</f>
-        <v>26.993113999999991</v>
+        <v>38.711010000000002</v>
       </c>
       <c r="AB22" s="5">
         <f>AB21*0.15</f>
-        <v>82.100930339999991</v>
+        <v>94.61540699999999</v>
       </c>
       <c r="AC22" s="5">
-        <f t="shared" ref="AC22:AK22" si="31">AC21*0.15</f>
-        <v>95.344909065300016</v>
+        <f t="shared" ref="AC22:AK22" si="29">AC21*0.15</f>
+        <v>107.60839564499999</v>
       </c>
       <c r="AD22" s="5">
-        <f t="shared" si="31"/>
-        <v>101.54358136456501</v>
+        <f t="shared" si="29"/>
+        <v>122.83105699349998</v>
       </c>
       <c r="AE22" s="5">
-        <f t="shared" si="31"/>
-        <v>106.98873316073762</v>
+        <f t="shared" si="29"/>
+        <v>129.41322042743994</v>
       </c>
       <c r="AF22" s="5">
-        <f t="shared" si="31"/>
-        <v>111.52310365056896</v>
+        <f t="shared" si="29"/>
+        <v>134.81622953298415</v>
       </c>
       <c r="AG22" s="5">
-        <f t="shared" si="31"/>
-        <v>116.22651502469787</v>
+        <f t="shared" si="29"/>
+        <v>140.41889781924789</v>
       </c>
       <c r="AH22" s="5">
-        <f t="shared" si="31"/>
-        <v>121.1050244850306</v>
+        <f t="shared" si="29"/>
+        <v>146.22832427268867</v>
       </c>
       <c r="AI22" s="5">
-        <f t="shared" si="31"/>
-        <v>126.16490695803708</v>
+        <f t="shared" si="29"/>
+        <v>152.25186092522281</v>
       </c>
       <c r="AJ22" s="5">
-        <f t="shared" si="31"/>
-        <v>131.41266316110858</v>
+        <f t="shared" si="29"/>
+        <v>158.49712214168861</v>
       </c>
       <c r="AK22" s="5">
-        <f t="shared" si="31"/>
-        <v>136.85502798231963</v>
+        <f t="shared" si="29"/>
+        <v>164.97199426458445</v>
       </c>
     </row>
     <row r="23" spans="2:146" x14ac:dyDescent="0.3">
@@ -2792,12 +2789,12 @@
         <v>7.1</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" ref="Q23:R23" si="32">Q21*0.2</f>
-        <v>14.277031999999995</v>
+        <f>5.3+15.1</f>
+        <v>20.399999999999999</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="32"/>
-        <v>13.047119999999996</v>
+        <f>5.3+15.1</f>
+        <v>20.399999999999999</v>
       </c>
       <c r="Y23" s="5">
         <f>SUM(G23:J23)</f>
@@ -2809,47 +2806,47 @@
       </c>
       <c r="AA23" s="5">
         <f>SUM(O23:R23)</f>
-        <v>37.224151999999989</v>
+        <v>50.699999999999996</v>
       </c>
       <c r="AB23" s="5">
         <f>AB21*0.18</f>
-        <v>98.521116407999997</v>
+        <v>113.53848839999999</v>
       </c>
       <c r="AC23" s="5">
-        <f t="shared" ref="AC23:AK23" si="33">AC21*0.18</f>
-        <v>114.41389087836002</v>
+        <f t="shared" ref="AC23:AK23" si="30">AC21*0.18</f>
+        <v>129.13007477399998</v>
       </c>
       <c r="AD23" s="5">
-        <f t="shared" si="33"/>
-        <v>121.852297637478</v>
+        <f t="shared" si="30"/>
+        <v>147.39726839219998</v>
       </c>
       <c r="AE23" s="5">
-        <f t="shared" si="33"/>
-        <v>128.38647979288515</v>
+        <f t="shared" si="30"/>
+        <v>155.29586451292792</v>
       </c>
       <c r="AF23" s="5">
-        <f t="shared" si="33"/>
-        <v>133.82772438068275</v>
+        <f t="shared" si="30"/>
+        <v>161.77947543958098</v>
       </c>
       <c r="AG23" s="5">
-        <f t="shared" si="33"/>
-        <v>139.47181802963746</v>
+        <f t="shared" si="30"/>
+        <v>168.50267738309748</v>
       </c>
       <c r="AH23" s="5">
-        <f t="shared" si="33"/>
-        <v>145.32602938203672</v>
+        <f t="shared" si="30"/>
+        <v>175.47398912722642</v>
       </c>
       <c r="AI23" s="5">
-        <f t="shared" si="33"/>
-        <v>151.39788834964449</v>
+        <f t="shared" si="30"/>
+        <v>182.7022331102674</v>
       </c>
       <c r="AJ23" s="5">
-        <f t="shared" si="33"/>
-        <v>157.6951957933303</v>
+        <f t="shared" si="30"/>
+        <v>190.19654657002633</v>
       </c>
       <c r="AK23" s="5">
-        <f t="shared" si="33"/>
-        <v>164.22603357878356</v>
+        <f t="shared" si="30"/>
+        <v>197.96639311750133</v>
       </c>
     </row>
     <row r="24" spans="2:146" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2857,52 +2854,52 @@
         <v>28</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" ref="G24:O24" si="34">G21-G22-G23</f>
+        <f t="shared" ref="G24:O24" si="31">G21-G22-G23</f>
         <v>14.799999999999985</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>25.099999999999977</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>32.599999999999966</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>13.699999999999974</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>20.599999999999952</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>39.19999999999996</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>53.800000000000075</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>85.600000000000065</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>16.700000000000006</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24:R24" si="35">P21-P22-P23</f>
+        <f t="shared" ref="P24:R24" si="32">P21-P22-P23</f>
         <v>34.000000000000014</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="35"/>
-        <v>46.400353999999979</v>
+        <f t="shared" si="32"/>
+        <v>13.000000000000142</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="35"/>
-        <v>42.403139999999979</v>
+        <f t="shared" si="32"/>
+        <v>8.5623900000000148</v>
       </c>
       <c r="Y24" s="8">
         <f>Y21-Y22-Y23</f>
@@ -2914,483 +2911,483 @@
       </c>
       <c r="AA24" s="8">
         <f>AA21-AA22-AA23</f>
-        <v>139.50349399999999</v>
+        <v>72.26239000000038</v>
       </c>
       <c r="AB24" s="8">
         <f>AB21-AB22-AB23</f>
-        <v>366.71748885199997</v>
+        <v>422.61548459999995</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" ref="AC24:AK24" si="36">AC21-AC22-AC23</f>
-        <v>425.87392715834005</v>
+        <f t="shared" ref="AC24:AK24" si="33">AC21-AC22-AC23</f>
+        <v>480.65083388099998</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="36"/>
-        <v>453.56133009505703</v>
+        <f t="shared" si="33"/>
+        <v>548.64538790430004</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="36"/>
-        <v>477.88300811796142</v>
+        <f t="shared" si="33"/>
+        <v>578.04571790923183</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="36"/>
-        <v>498.13652963920799</v>
+        <f t="shared" si="33"/>
+        <v>602.1791585806626</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="36"/>
-        <v>519.14510044365056</v>
+        <f t="shared" si="33"/>
+        <v>627.20441025930722</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="36"/>
-        <v>540.93577603313668</v>
+        <f t="shared" si="33"/>
+        <v>653.15318175134269</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" si="36"/>
-        <v>563.53658441256562</v>
+        <f t="shared" si="33"/>
+        <v>680.05831213266197</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" si="36"/>
-        <v>586.97656211961828</v>
+        <f t="shared" si="33"/>
+        <v>707.95381223287586</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" si="36"/>
-        <v>611.28579165436099</v>
+        <f t="shared" si="33"/>
+        <v>736.87490771514388</v>
       </c>
       <c r="AL24" s="1">
         <f>AK24*(1+$AO$30)</f>
-        <v>605.1729337378174</v>
+        <v>729.50615863799248</v>
       </c>
       <c r="AM24" s="1">
-        <f t="shared" ref="AM24:CX24" si="37">AL24*(1+$AO$30)</f>
-        <v>599.12120440043918</v>
+        <f t="shared" ref="AM24:CX24" si="34">AL24*(1+$AO$30)</f>
+        <v>722.21109705161257</v>
       </c>
       <c r="AN24" s="1">
-        <f t="shared" si="37"/>
-        <v>593.12999235643474</v>
+        <f t="shared" si="34"/>
+        <v>714.98898608109641</v>
       </c>
       <c r="AO24" s="1">
-        <f t="shared" si="37"/>
-        <v>587.19869243287042</v>
+        <f t="shared" si="34"/>
+        <v>707.83909622028546</v>
       </c>
       <c r="AP24" s="1">
-        <f t="shared" si="37"/>
-        <v>581.32670550854175</v>
+        <f t="shared" si="34"/>
+        <v>700.76070525808257</v>
       </c>
       <c r="AQ24" s="1">
-        <f t="shared" si="37"/>
-        <v>575.51343845345627</v>
+        <f t="shared" si="34"/>
+        <v>693.75309820550171</v>
       </c>
       <c r="AR24" s="1">
-        <f t="shared" si="37"/>
-        <v>569.75830406892169</v>
+        <f t="shared" si="34"/>
+        <v>686.81556722344669</v>
       </c>
       <c r="AS24" s="1">
-        <f t="shared" si="37"/>
-        <v>564.06072102823248</v>
+        <f t="shared" si="34"/>
+        <v>679.94741155121221</v>
       </c>
       <c r="AT24" s="1">
-        <f t="shared" si="37"/>
-        <v>558.4201138179501</v>
+        <f t="shared" si="34"/>
+        <v>673.1479374357001</v>
       </c>
       <c r="AU24" s="1">
-        <f t="shared" si="37"/>
-        <v>552.83591267977056</v>
+        <f t="shared" si="34"/>
+        <v>666.41645806134306</v>
       </c>
       <c r="AV24" s="1">
-        <f t="shared" si="37"/>
-        <v>547.30755355297288</v>
+        <f t="shared" si="34"/>
+        <v>659.75229348072958</v>
       </c>
       <c r="AW24" s="1">
-        <f t="shared" si="37"/>
-        <v>541.83447801744319</v>
+        <f t="shared" si="34"/>
+        <v>653.15477054592225</v>
       </c>
       <c r="AX24" s="1">
-        <f t="shared" si="37"/>
-        <v>536.4161332372687</v>
+        <f t="shared" si="34"/>
+        <v>646.62322284046297</v>
       </c>
       <c r="AY24" s="1">
-        <f t="shared" si="37"/>
-        <v>531.05197190489605</v>
+        <f t="shared" si="34"/>
+        <v>640.15699061205828</v>
       </c>
       <c r="AZ24" s="1">
-        <f t="shared" si="37"/>
-        <v>525.74145218584704</v>
+        <f t="shared" si="34"/>
+        <v>633.75542070593769</v>
       </c>
       <c r="BA24" s="1">
-        <f t="shared" si="37"/>
-        <v>520.4840376639886</v>
+        <f t="shared" si="34"/>
+        <v>627.41786649887831</v>
       </c>
       <c r="BB24" s="1">
-        <f t="shared" si="37"/>
-        <v>515.27919728734867</v>
+        <f t="shared" si="34"/>
+        <v>621.14368783388954</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" si="37"/>
-        <v>510.12640531447516</v>
+        <f t="shared" si="34"/>
+        <v>614.93225095555067</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="37"/>
-        <v>505.02514126133042</v>
+        <f t="shared" si="34"/>
+        <v>608.78292844599514</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="37"/>
-        <v>499.97488984871711</v>
+        <f t="shared" si="34"/>
+        <v>602.69509916153515</v>
       </c>
       <c r="BF24" s="1">
-        <f t="shared" si="37"/>
-        <v>494.97514095022996</v>
+        <f t="shared" si="34"/>
+        <v>596.66814816991985</v>
       </c>
       <c r="BG24" s="1">
-        <f t="shared" si="37"/>
-        <v>490.02538954072764</v>
+        <f t="shared" si="34"/>
+        <v>590.70146668822065</v>
       </c>
       <c r="BH24" s="1">
-        <f t="shared" si="37"/>
-        <v>485.12513564532037</v>
+        <f t="shared" si="34"/>
+        <v>584.79445202133843</v>
       </c>
       <c r="BI24" s="1">
-        <f t="shared" si="37"/>
-        <v>480.27388428886718</v>
+        <f t="shared" si="34"/>
+        <v>578.94650750112498</v>
       </c>
       <c r="BJ24" s="1">
-        <f t="shared" si="37"/>
-        <v>475.47114544597849</v>
+        <f t="shared" si="34"/>
+        <v>573.15704242611378</v>
       </c>
       <c r="BK24" s="1">
-        <f t="shared" si="37"/>
-        <v>470.71643399151873</v>
+        <f t="shared" si="34"/>
+        <v>567.42547200185265</v>
       </c>
       <c r="BL24" s="1">
-        <f t="shared" si="37"/>
-        <v>466.00926965160352</v>
+        <f t="shared" si="34"/>
+        <v>561.7512172818341</v>
       </c>
       <c r="BM24" s="1">
-        <f t="shared" si="37"/>
-        <v>461.3491769550875</v>
+        <f t="shared" si="34"/>
+        <v>556.13370510901575</v>
       </c>
       <c r="BN24" s="1">
-        <f t="shared" si="37"/>
-        <v>456.73568518553662</v>
+        <f t="shared" si="34"/>
+        <v>550.57236805792559</v>
       </c>
       <c r="BO24" s="1">
-        <f t="shared" si="37"/>
-        <v>452.16832833368125</v>
+        <f t="shared" si="34"/>
+        <v>545.06664437734628</v>
       </c>
       <c r="BP24" s="1">
-        <f t="shared" si="37"/>
-        <v>447.64664505034443</v>
+        <f t="shared" si="34"/>
+        <v>539.61597793357282</v>
       </c>
       <c r="BQ24" s="1">
-        <f t="shared" si="37"/>
-        <v>443.17017859984099</v>
+        <f t="shared" si="34"/>
+        <v>534.21981815423703</v>
       </c>
       <c r="BR24" s="1">
-        <f t="shared" si="37"/>
-        <v>438.73847681384257</v>
+        <f t="shared" si="34"/>
+        <v>528.87761997269467</v>
       </c>
       <c r="BS24" s="1">
-        <f t="shared" si="37"/>
-        <v>434.35109204570415</v>
+        <f t="shared" si="34"/>
+        <v>523.58884377296772</v>
       </c>
       <c r="BT24" s="1">
-        <f t="shared" si="37"/>
-        <v>430.0075811252471</v>
+        <f t="shared" si="34"/>
+        <v>518.35295533523799</v>
       </c>
       <c r="BU24" s="1">
-        <f t="shared" si="37"/>
-        <v>425.7075053139946</v>
+        <f t="shared" si="34"/>
+        <v>513.16942578188559</v>
       </c>
       <c r="BV24" s="1">
-        <f t="shared" si="37"/>
-        <v>421.45043026085466</v>
+        <f t="shared" si="34"/>
+        <v>508.03773152406671</v>
       </c>
       <c r="BW24" s="1">
-        <f t="shared" si="37"/>
-        <v>417.23592595824613</v>
+        <f t="shared" si="34"/>
+        <v>502.95735420882602</v>
       </c>
       <c r="BX24" s="1">
-        <f t="shared" si="37"/>
-        <v>413.06356669866364</v>
+        <f t="shared" si="34"/>
+        <v>497.92778066673776</v>
       </c>
       <c r="BY24" s="1">
-        <f t="shared" si="37"/>
-        <v>408.93293103167701</v>
+        <f t="shared" si="34"/>
+        <v>492.94850286007039</v>
       </c>
       <c r="BZ24" s="1">
-        <f t="shared" si="37"/>
-        <v>404.84360172136024</v>
+        <f t="shared" si="34"/>
+        <v>488.01901783146968</v>
       </c>
       <c r="CA24" s="1">
-        <f t="shared" si="37"/>
-        <v>400.79516570414665</v>
+        <f t="shared" si="34"/>
+        <v>483.13882765315498</v>
       </c>
       <c r="CB24" s="1">
-        <f t="shared" si="37"/>
-        <v>396.78721404710518</v>
+        <f t="shared" si="34"/>
+        <v>478.30743937662345</v>
       </c>
       <c r="CC24" s="1">
-        <f t="shared" si="37"/>
-        <v>392.81934190663412</v>
+        <f t="shared" si="34"/>
+        <v>473.52436498285721</v>
       </c>
       <c r="CD24" s="1">
-        <f t="shared" si="37"/>
-        <v>388.89114848756776</v>
+        <f t="shared" si="34"/>
+        <v>468.78912133302862</v>
       </c>
       <c r="CE24" s="1">
-        <f t="shared" si="37"/>
-        <v>385.00223700269208</v>
+        <f t="shared" si="34"/>
+        <v>464.1012301196983</v>
       </c>
       <c r="CF24" s="1">
-        <f t="shared" si="37"/>
-        <v>381.15221463266516</v>
+        <f t="shared" si="34"/>
+        <v>459.46021781850129</v>
       </c>
       <c r="CG24" s="1">
-        <f t="shared" si="37"/>
-        <v>377.34069248633853</v>
+        <f t="shared" si="34"/>
+        <v>454.86561564031626</v>
       </c>
       <c r="CH24" s="1">
-        <f t="shared" si="37"/>
-        <v>373.56728556147516</v>
+        <f t="shared" si="34"/>
+        <v>450.31695948391308</v>
       </c>
       <c r="CI24" s="1">
-        <f t="shared" si="37"/>
-        <v>369.83161270586038</v>
+        <f t="shared" si="34"/>
+        <v>445.81378988907397</v>
       </c>
       <c r="CJ24" s="1">
-        <f t="shared" si="37"/>
-        <v>366.13329657880178</v>
+        <f t="shared" si="34"/>
+        <v>441.35565199018322</v>
       </c>
       <c r="CK24" s="1">
-        <f t="shared" si="37"/>
-        <v>362.47196361301377</v>
+        <f t="shared" si="34"/>
+        <v>436.9420954702814</v>
       </c>
       <c r="CL24" s="1">
-        <f t="shared" si="37"/>
-        <v>358.84724397688365</v>
+        <f t="shared" si="34"/>
+        <v>432.57267451557857</v>
       </c>
       <c r="CM24" s="1">
-        <f t="shared" si="37"/>
-        <v>355.2587715371148</v>
+        <f t="shared" si="34"/>
+        <v>428.24694777042276</v>
       </c>
       <c r="CN24" s="1">
-        <f t="shared" si="37"/>
-        <v>351.70618382174365</v>
+        <f t="shared" si="34"/>
+        <v>423.96447829271852</v>
       </c>
       <c r="CO24" s="1">
-        <f t="shared" si="37"/>
-        <v>348.18912198352621</v>
+        <f t="shared" si="34"/>
+        <v>419.72483350979132</v>
       </c>
       <c r="CP24" s="1">
-        <f t="shared" si="37"/>
-        <v>344.70723076369092</v>
+        <f t="shared" si="34"/>
+        <v>415.5275851746934</v>
       </c>
       <c r="CQ24" s="1">
-        <f t="shared" si="37"/>
-        <v>341.260158456054</v>
+        <f t="shared" si="34"/>
+        <v>411.37230932294648</v>
       </c>
       <c r="CR24" s="1">
-        <f t="shared" si="37"/>
-        <v>337.84755687149345</v>
+        <f t="shared" si="34"/>
+        <v>407.25858622971703</v>
       </c>
       <c r="CS24" s="1">
-        <f t="shared" si="37"/>
-        <v>334.46908130277853</v>
+        <f t="shared" si="34"/>
+        <v>403.18600036741987</v>
       </c>
       <c r="CT24" s="1">
-        <f t="shared" si="37"/>
-        <v>331.12439048975074</v>
+        <f t="shared" si="34"/>
+        <v>399.15414036374568</v>
       </c>
       <c r="CU24" s="1">
-        <f t="shared" si="37"/>
-        <v>327.8131465848532</v>
+        <f t="shared" si="34"/>
+        <v>395.1625989601082</v>
       </c>
       <c r="CV24" s="1">
-        <f t="shared" si="37"/>
-        <v>324.53501511900464</v>
+        <f t="shared" si="34"/>
+        <v>391.2109729705071</v>
       </c>
       <c r="CW24" s="1">
-        <f t="shared" si="37"/>
-        <v>321.28966496781459</v>
+        <f t="shared" si="34"/>
+        <v>387.29886324080201</v>
       </c>
       <c r="CX24" s="1">
-        <f t="shared" si="37"/>
-        <v>318.07676831813643</v>
+        <f t="shared" si="34"/>
+        <v>383.425874608394</v>
       </c>
       <c r="CY24" s="1">
-        <f t="shared" ref="CY24:EP24" si="38">CX24*(1+$AO$30)</f>
-        <v>314.89600063495504</v>
+        <f t="shared" ref="CY24:EP24" si="35">CX24*(1+$AO$30)</f>
+        <v>379.59161586231005</v>
       </c>
       <c r="CZ24" s="1">
-        <f t="shared" si="38"/>
-        <v>311.74704062860548</v>
+        <f t="shared" si="35"/>
+        <v>375.79569970368692</v>
       </c>
       <c r="DA24" s="1">
-        <f t="shared" si="38"/>
-        <v>308.62957022231944</v>
+        <f t="shared" si="35"/>
+        <v>372.03774270665002</v>
       </c>
       <c r="DB24" s="1">
-        <f t="shared" si="38"/>
-        <v>305.54327452009625</v>
+        <f t="shared" si="35"/>
+        <v>368.3173652795835</v>
       </c>
       <c r="DC24" s="1">
-        <f t="shared" si="38"/>
-        <v>302.48784177489529</v>
+        <f t="shared" si="35"/>
+        <v>364.63419162678764</v>
       </c>
       <c r="DD24" s="1">
-        <f t="shared" si="38"/>
-        <v>299.46296335714635</v>
+        <f t="shared" si="35"/>
+        <v>360.98784971051975</v>
       </c>
       <c r="DE24" s="1">
-        <f t="shared" si="38"/>
-        <v>296.46833372357486</v>
+        <f t="shared" si="35"/>
+        <v>357.37797121341453</v>
       </c>
       <c r="DF24" s="1">
-        <f t="shared" si="38"/>
-        <v>293.50365038633913</v>
+        <f t="shared" si="35"/>
+        <v>353.8041915012804</v>
       </c>
       <c r="DG24" s="1">
-        <f t="shared" si="38"/>
-        <v>290.56861388247574</v>
+        <f t="shared" si="35"/>
+        <v>350.2661495862676</v>
       </c>
       <c r="DH24" s="1">
-        <f t="shared" si="38"/>
-        <v>287.66292774365098</v>
+        <f t="shared" si="35"/>
+        <v>346.76348809040491</v>
       </c>
       <c r="DI24" s="1">
-        <f t="shared" si="38"/>
-        <v>284.78629846621448</v>
+        <f t="shared" si="35"/>
+        <v>343.29585320950088</v>
       </c>
       <c r="DJ24" s="1">
-        <f t="shared" si="38"/>
-        <v>281.93843548155235</v>
+        <f t="shared" si="35"/>
+        <v>339.86289467740585</v>
       </c>
       <c r="DK24" s="1">
-        <f t="shared" si="38"/>
-        <v>279.11905112673679</v>
+        <f t="shared" si="35"/>
+        <v>336.46426573063178</v>
       </c>
       <c r="DL24" s="1">
-        <f t="shared" si="38"/>
-        <v>276.32786061546943</v>
+        <f t="shared" si="35"/>
+        <v>333.09962307332546</v>
       </c>
       <c r="DM24" s="1">
-        <f t="shared" si="38"/>
-        <v>273.56458200931473</v>
+        <f t="shared" si="35"/>
+        <v>329.7686268425922</v>
       </c>
       <c r="DN24" s="1">
-        <f t="shared" si="38"/>
-        <v>270.82893618922157</v>
+        <f t="shared" si="35"/>
+        <v>326.47094057416626</v>
       </c>
       <c r="DO24" s="1">
-        <f t="shared" si="38"/>
-        <v>268.12064682732932</v>
+        <f t="shared" si="35"/>
+        <v>323.20623116842461</v>
       </c>
       <c r="DP24" s="1">
-        <f t="shared" si="38"/>
-        <v>265.43944035905605</v>
+        <f t="shared" si="35"/>
+        <v>319.97416885674033</v>
       </c>
       <c r="DQ24" s="1">
-        <f t="shared" si="38"/>
-        <v>262.78504595546548</v>
+        <f t="shared" si="35"/>
+        <v>316.77442716817291</v>
       </c>
       <c r="DR24" s="1">
-        <f t="shared" si="38"/>
-        <v>260.1571954959108</v>
+        <f t="shared" si="35"/>
+        <v>313.60668289649118</v>
       </c>
       <c r="DS24" s="1">
-        <f t="shared" si="38"/>
-        <v>257.55562354095167</v>
+        <f t="shared" si="35"/>
+        <v>310.47061606752624</v>
       </c>
       <c r="DT24" s="1">
-        <f t="shared" si="38"/>
-        <v>254.98006730554215</v>
+        <f t="shared" si="35"/>
+        <v>307.36590990685096</v>
       </c>
       <c r="DU24" s="1">
-        <f t="shared" si="38"/>
-        <v>252.43026663248673</v>
+        <f t="shared" si="35"/>
+        <v>304.29225080778247</v>
       </c>
       <c r="DV24" s="1">
-        <f t="shared" si="38"/>
-        <v>249.90596396616186</v>
+        <f t="shared" si="35"/>
+        <v>301.24932829970464</v>
       </c>
       <c r="DW24" s="1">
-        <f t="shared" si="38"/>
-        <v>247.40690432650024</v>
+        <f t="shared" si="35"/>
+        <v>298.23683501670757</v>
       </c>
       <c r="DX24" s="1">
-        <f t="shared" si="38"/>
-        <v>244.93283528323522</v>
+        <f t="shared" si="35"/>
+        <v>295.25446666654051</v>
       </c>
       <c r="DY24" s="1">
-        <f t="shared" si="38"/>
-        <v>242.48350693040285</v>
+        <f t="shared" si="35"/>
+        <v>292.30192199987511</v>
       </c>
       <c r="DZ24" s="1">
-        <f t="shared" si="38"/>
-        <v>240.05867186109882</v>
+        <f t="shared" si="35"/>
+        <v>289.37890277987634</v>
       </c>
       <c r="EA24" s="1">
-        <f t="shared" si="38"/>
-        <v>237.65808514248783</v>
+        <f t="shared" si="35"/>
+        <v>286.48511375207755</v>
       </c>
       <c r="EB24" s="1">
-        <f t="shared" si="38"/>
-        <v>235.28150429106296</v>
+        <f t="shared" si="35"/>
+        <v>283.62026261455679</v>
       </c>
       <c r="EC24" s="1">
-        <f t="shared" si="38"/>
-        <v>232.92868924815232</v>
+        <f t="shared" si="35"/>
+        <v>280.78405998841123</v>
       </c>
       <c r="ED24" s="1">
-        <f t="shared" si="38"/>
-        <v>230.5994023556708</v>
+        <f t="shared" si="35"/>
+        <v>277.97621938852711</v>
       </c>
       <c r="EE24" s="1">
-        <f t="shared" si="38"/>
-        <v>228.2934083321141</v>
+        <f t="shared" si="35"/>
+        <v>275.19645719464182</v>
       </c>
       <c r="EF24" s="1">
-        <f t="shared" si="38"/>
-        <v>226.01047424879295</v>
+        <f t="shared" si="35"/>
+        <v>272.44449262269541</v>
       </c>
       <c r="EG24" s="1">
-        <f t="shared" si="38"/>
-        <v>223.75036950630502</v>
+        <f t="shared" si="35"/>
+        <v>269.72004769646844</v>
       </c>
       <c r="EH24" s="1">
-        <f t="shared" si="38"/>
-        <v>221.51286581124197</v>
+        <f t="shared" si="35"/>
+        <v>267.02284721950377</v>
       </c>
       <c r="EI24" s="1">
-        <f t="shared" si="38"/>
-        <v>219.29773715312953</v>
+        <f t="shared" si="35"/>
+        <v>264.35261874730872</v>
       </c>
       <c r="EJ24" s="1">
-        <f t="shared" si="38"/>
-        <v>217.10475978159823</v>
+        <f t="shared" si="35"/>
+        <v>261.70909255983565</v>
       </c>
       <c r="EK24" s="1">
-        <f t="shared" si="38"/>
-        <v>214.93371218378226</v>
+        <f t="shared" si="35"/>
+        <v>259.09200163423731</v>
       </c>
       <c r="EL24" s="1">
-        <f t="shared" si="38"/>
-        <v>212.78437506194444</v>
+        <f t="shared" si="35"/>
+        <v>256.50108161789495</v>
       </c>
       <c r="EM24" s="1">
-        <f t="shared" si="38"/>
-        <v>210.65653131132501</v>
+        <f t="shared" si="35"/>
+        <v>253.936070801716</v>
       </c>
       <c r="EN24" s="1">
-        <f t="shared" si="38"/>
-        <v>208.54996599821175</v>
+        <f t="shared" si="35"/>
+        <v>251.39671009369883</v>
       </c>
       <c r="EO24" s="1">
-        <f t="shared" si="38"/>
-        <v>206.46446633822961</v>
+        <f t="shared" si="35"/>
+        <v>248.88274299276185</v>
       </c>
       <c r="EP24" s="1">
-        <f t="shared" si="38"/>
-        <v>204.39982167484732</v>
+        <f t="shared" si="35"/>
+        <v>246.39391556283422</v>
       </c>
     </row>
     <row r="25" spans="2:146" x14ac:dyDescent="0.3">
@@ -3398,39 +3395,39 @@
         <v>2</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" ref="G25:O25" si="39">67.8+19.8+1.5</f>
+        <f t="shared" ref="G25:O25" si="36">67.8+19.8+1.5</f>
         <v>89.1</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>89.1</v>
       </c>
       <c r="P25" s="5">
@@ -3438,12 +3435,12 @@
         <v>88.399999999999991</v>
       </c>
       <c r="Q25" s="5">
-        <f>67.3+19.8+1.3</f>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="R25" s="5">
-        <f>67.3+19.8+1.3</f>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="Y25" s="5">
         <f>67.8+19.8+1.5</f>
@@ -3454,48 +3451,48 @@
         <v>89.1</v>
       </c>
       <c r="AA25" s="5">
-        <f t="shared" ref="AA25:AK25" si="40">67.3+19.8+1.3</f>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AB25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AC25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AD25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AE25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AF25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AG25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AH25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AI25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AJ25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
       <c r="AK25" s="5">
-        <f t="shared" si="40"/>
-        <v>88.399999999999991</v>
+        <f>89.4+1.3</f>
+        <v>90.7</v>
       </c>
     </row>
     <row r="26" spans="2:146" x14ac:dyDescent="0.3">
@@ -3503,52 +3500,52 @@
         <v>29</v>
       </c>
       <c r="G26" s="7">
-        <f t="shared" ref="G26:O26" si="41">G24/G25</f>
+        <f t="shared" ref="G26:O26" si="37">G24/G25</f>
         <v>0.1661054994388326</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.28170594837261481</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.36588103254769888</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.15375982042648681</v>
       </c>
       <c r="K26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.23120089786756401</v>
       </c>
       <c r="L26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.4399551066217729</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.6038159371492714</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.96071829405162823</v>
       </c>
       <c r="O26" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.18742985409652085</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" ref="P26:R26" si="42">P24/P25</f>
+        <f t="shared" ref="P26:R26" si="38">P24/P25</f>
         <v>0.3846153846153848</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="42"/>
-        <v>0.52489088235294101</v>
+        <f t="shared" si="38"/>
+        <v>0.14332965821389351</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="42"/>
-        <v>0.4796735294117645</v>
+        <f t="shared" si="38"/>
+        <v>9.4403417861080641E-2</v>
       </c>
       <c r="Y26" s="7">
         <f>Y24/Y25</f>
@@ -3560,47 +3557,47 @@
       </c>
       <c r="AA26" s="7">
         <f>AA24/AA25</f>
-        <v>1.5780938235294117</v>
+        <v>0.79671874310915525</v>
       </c>
       <c r="AB26" s="7">
         <f>AB24/AB25</f>
-        <v>4.1483878829411767</v>
+        <v>4.6594871510474078</v>
       </c>
       <c r="AC26" s="7">
-        <f t="shared" ref="AC26:AK26" si="43">AC24/AC25</f>
-        <v>4.8175783615196845</v>
+        <f t="shared" ref="AC26:AK26" si="39">AC24/AC25</f>
+        <v>5.299347672337376</v>
       </c>
       <c r="AD26" s="7">
-        <f t="shared" si="43"/>
-        <v>5.1307842770934062</v>
+        <f t="shared" si="39"/>
+        <v>6.0490119945347303</v>
       </c>
       <c r="AE26" s="7">
-        <f t="shared" si="43"/>
-        <v>5.4059163814249036</v>
+        <f t="shared" si="39"/>
+        <v>6.3731611676872308</v>
       </c>
       <c r="AF26" s="7">
-        <f t="shared" si="43"/>
-        <v>5.6350286158281451</v>
+        <f t="shared" si="39"/>
+        <v>6.6392409986842624</v>
       </c>
       <c r="AG26" s="7">
-        <f t="shared" si="43"/>
-        <v>5.8726821317155045</v>
+        <f t="shared" si="39"/>
+        <v>6.9151533655932438</v>
       </c>
       <c r="AH26" s="7">
-        <f t="shared" si="43"/>
-        <v>6.1191829868001895</v>
+        <f t="shared" si="39"/>
+        <v>7.2012478693643072</v>
       </c>
       <c r="AI26" s="7">
-        <f t="shared" si="43"/>
-        <v>6.3748482399611497</v>
+        <f t="shared" si="39"/>
+        <v>7.4978865725762063</v>
       </c>
       <c r="AJ26" s="7">
-        <f t="shared" si="43"/>
-        <v>6.6400063588192122</v>
+        <f t="shared" si="39"/>
+        <v>7.8054444568123023</v>
       </c>
       <c r="AK26" s="7">
-        <f t="shared" si="43"/>
-        <v>6.9149976431488804</v>
+        <f t="shared" si="39"/>
+        <v>8.1243098976311341</v>
       </c>
     </row>
     <row r="28" spans="2:146" x14ac:dyDescent="0.3">
@@ -3612,15 +3609,15 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9">
-        <f t="shared" ref="K28:M28" si="44">K3/G3-1</f>
+        <f t="shared" ref="K28:M28" si="40">K3/G3-1</f>
         <v>0.29323583180987201</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.29827315541601251</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.34616523541604982</v>
       </c>
       <c r="N28" s="9">
@@ -3628,20 +3625,20 @@
         <v>0.25744258576694068</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="45">O3/K3-1</f>
+        <f t="shared" ref="O28:R28" si="41">O3/K3-1</f>
         <v>0.19918009612666099</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="41"/>
         <v>0.1683192261185007</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="45"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="41"/>
+        <v>0.29443466783985928</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="45"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="41"/>
+        <v>0.35000000000000009</v>
       </c>
       <c r="Y28" s="9"/>
       <c r="Z28" s="9">
@@ -3649,47 +3646,47 @@
         <v>0.29858078602620086</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AK28" si="46">AA3/Z3-1</f>
-        <v>0.16499429532216414</v>
+        <f t="shared" ref="AA28:AK28" si="42">AA3/Z3-1</f>
+        <v>0.25768630276826987</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="46"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="42"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="46"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="42"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3698,31 +3695,31 @@
         <v>50</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:M29" si="47">G5/G3</f>
+        <f t="shared" ref="G29:M29" si="43">G5/G3</f>
         <v>0.26581352833638022</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.26200941915227627</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.26695291679005029</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.27672242699177768</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.26547921967769289</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.28029020556227324</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.29399472063352405</v>
       </c>
       <c r="N29" s="9">
@@ -3730,20 +3727,20 @@
         <v>0.32266065388951526</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:R29" si="48">O5/O3</f>
+        <f t="shared" ref="O29:R29" si="44">O5/O3</f>
         <v>0.30295885889425911</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>0.30273235354998962</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="48"/>
-        <v>0.31</v>
+        <f t="shared" si="44"/>
+        <v>0.3645169513127709</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="48"/>
-        <v>0.32</v>
+        <f t="shared" si="44"/>
+        <v>0.34</v>
       </c>
       <c r="Y29" s="9">
         <f>Y5/Y3</f>
@@ -3754,48 +3751,48 @@
         <v>0.29216957905482505</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AK29" si="49">AA5/AA3</f>
-        <v>0.3092797921719117</v>
+        <f t="shared" ref="AA29:AK29" si="45">AA5/AA3</f>
+        <v>0.33079078983491894</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.32</v>
+        <f t="shared" si="45"/>
+        <v>0.34</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.35</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="49"/>
-        <v>0.33</v>
+        <f t="shared" si="45"/>
+        <v>0.36</v>
       </c>
     </row>
     <row r="30" spans="2:146" x14ac:dyDescent="0.3">
@@ -3807,15 +3804,15 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9">
-        <f t="shared" ref="K30:M30" si="50">K6/G6-1</f>
+        <f t="shared" ref="K30:M30" si="46">K6/G6-1</f>
         <v>0.24970828471411899</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0.34104750304506704</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0.54914809960681521</v>
       </c>
       <c r="N30" s="9">
@@ -3823,20 +3820,20 @@
         <v>0.45657276995305152</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="51">O6/K6-1</f>
+        <f t="shared" ref="O30:R30" si="47">O6/K6-1</f>
         <v>0.43790849673202614</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0.18437783832879218</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="51"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="47"/>
+        <v>0.59390862944162448</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="51"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="47"/>
+        <v>0.55519742143432715</v>
       </c>
       <c r="Y30" s="9"/>
       <c r="Z30" s="9">
@@ -3844,47 +3841,47 @@
         <v>0.39538414819313683</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30:AK30" si="52">AA6/Z6-1</f>
-        <v>0.25170837867247009</v>
+        <f t="shared" ref="AA30:AK30" si="48">AA6/Z6-1</f>
+        <v>0.44896626768226322</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN30" t="s">
@@ -3899,31 +3896,31 @@
         <v>52</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:M31" si="53">G9/G3</f>
+        <f t="shared" ref="G31:M31" si="49">G9/G3</f>
         <v>1.1151736745886653E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>8.4772370486656205E-3</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>8.4394432928634883E-3</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>2.2540402608449108E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>1.1309018942606729E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>1.4026602176541716E-2</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>1.0338759348878134E-2</v>
       </c>
       <c r="N31" s="9">
@@ -3931,20 +3928,20 @@
         <v>1.3979706877113867E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31:R31" si="54">O9/O3</f>
+        <f t="shared" ref="O31:R31" si="50">O9/O3</f>
         <v>2.1926205351880234E-2</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>1.5731732560546469E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="54"/>
-        <v>1.7789169647468392E-2</v>
+        <f t="shared" si="50"/>
+        <v>2.9994052170957596E-2</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="54"/>
-        <v>1.8234400274496351E-2</v>
+        <f t="shared" si="50"/>
+        <v>3.0063885757234121E-2</v>
       </c>
       <c r="Y31" s="9">
         <f>Y9/Y3</f>
@@ -3955,48 +3952,48 @@
         <v>1.2430192758061608E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31:AK31" si="55">AA9/AA3</f>
-        <v>1.8298355982918096E-2</v>
+        <f t="shared" ref="AA31:AK31" si="51">AA9/AA3</f>
+        <v>2.5090418611313364E-2</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.02</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="55"/>
-        <v>0.02</v>
+        <f t="shared" si="51"/>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="AN31" t="s">
         <v>57</v>
@@ -4010,31 +4007,31 @@
         <v>53</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" ref="G32:M32" si="56">G10/G3</f>
+        <f t="shared" ref="G32:M32" si="52">G10/G3</f>
         <v>4.570383912248629E-3</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>6.2794348508634227E-3</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>6.9588392063962105E-3</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>5.5287779982988372E-3</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>6.2199604184337018E-3</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>4.7158403869407492E-3</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>6.8191816981962167E-3</v>
       </c>
       <c r="N32" s="9">
@@ -4042,19 +4039,19 @@
         <v>8.1172491544532141E-3</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="57">O10/O3</f>
+        <f t="shared" ref="O32:R32" si="53">O10/O3</f>
         <v>7.8981492396557832E-3</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="53"/>
         <v>7.3483750776236799E-3</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="57"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="53"/>
+        <v>6.5426119466394763E-3</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="53"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="Y32" s="9">
@@ -4066,47 +4063,47 @@
         <v>6.5153425809163501E-3</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" ref="AA32:AK32" si="58">AA10/AA3</f>
-        <v>7.8154701002285994E-3</v>
+        <f t="shared" ref="AA32:AK32" si="54">AA10/AA3</f>
+        <v>7.4196020387457167E-3</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AN32" t="s">
@@ -4114,7 +4111,7 @@
       </c>
       <c r="AO32" s="5">
         <f>NPV(AO31,AA24:EP24)</f>
-        <v>5339.3770819335095</v>
+        <v>6312.2008905832199</v>
       </c>
     </row>
     <row r="33" spans="2:41" x14ac:dyDescent="0.3">
@@ -4122,31 +4119,31 @@
         <v>54</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:M33" si="59">G13/G3</f>
+        <f t="shared" ref="G33:M33" si="55">G13/G3</f>
         <v>1.6087751371115143E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>5.3218210361067469E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>6.6183002665087295E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>3.8843209526509749E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>3.025162567147293E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>7.1584038694074925E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>8.8429388473383261E-2</v>
       </c>
       <c r="N33" s="9">
@@ -4154,20 +4151,20 @@
         <v>9.6956031567080103E-2</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" ref="O33:R33" si="60">O13/O3</f>
+        <f t="shared" ref="O33:R33" si="56">O13/O3</f>
         <v>2.9942237416008495E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>8.600703788035606E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="60"/>
-        <v>8.4398286118709212E-2</v>
+        <f t="shared" si="56"/>
+        <v>9.7374458322712312E-2</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="60"/>
-        <v>7.5893926768295664E-2</v>
+        <f t="shared" si="56"/>
+        <v>6.5600567873397644E-2</v>
       </c>
       <c r="Y33" s="9">
         <f>Y13/Y3</f>
@@ -4178,55 +4175,55 @@
         <v>7.4160811865729995E-2</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" ref="AA33:AK33" si="61">AA13/AA3</f>
-        <v>7.0657622296160169E-2</v>
+        <f t="shared" ref="AA33:AK33" si="57">AA13/AA3</f>
+        <v>7.2013416570180441E-2</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.14243242839244519</v>
+        <f t="shared" si="57"/>
+        <v>0.15720063875578594</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.1524324283924452</v>
+        <f t="shared" si="57"/>
+        <v>0.16574026742329331</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.15385688145537429</v>
+        <f t="shared" si="57"/>
+        <v>0.17722845535259529</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.15528133451830339</v>
+        <f t="shared" si="57"/>
+        <v>0.17871664328189721</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.15670578758123249</v>
+        <f t="shared" si="57"/>
+        <v>0.18020483121119918</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.15811641100277388</v>
+        <f t="shared" si="57"/>
+        <v>0.18167857071400312</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.15951333905129067</v>
+        <f t="shared" si="57"/>
+        <v>0.18313800206629433</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.16089670469156939</v>
+        <f t="shared" si="57"/>
+        <v>0.18458326418215557</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.16226663959747653</v>
+        <f t="shared" si="57"/>
+        <v>0.18601449462698905</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="61"/>
-        <v>0.16362327416449132</v>
+        <f t="shared" si="57"/>
+        <v>0.18743182963061047</v>
       </c>
       <c r="AN33" t="s">
         <v>59</v>
       </c>
       <c r="AO33" s="5">
         <f>Main!D8</f>
-        <v>-702.49999999999955</v>
+        <v>-3207.7</v>
       </c>
     </row>
     <row r="34" spans="2:41" x14ac:dyDescent="0.3">
@@ -4234,31 +4231,31 @@
         <v>26</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:M34" si="62">G22/G21</f>
+        <f t="shared" ref="G34:M34" si="58">G22/G21</f>
         <v>-0.2142857142857145</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>-9.8507462686567224E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>1.8987341772151913E-2</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.11926605504587169</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>4.6822742474916468E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>-3.4155597722960181E-2</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>1.3466154584733563</v>
       </c>
       <c r="N34" s="9">
@@ -4266,19 +4263,19 @@
         <v>0.12248186946011275</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" ref="O34:R34" si="63">O22/O21</f>
+        <f t="shared" ref="O34:R34" si="59">O22/O21</f>
         <v>-0.71052631578947323</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>0.26211849192100528</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="63"/>
-        <v>0.15</v>
+        <f t="shared" si="59"/>
+        <v>0.44793388429751962</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="Y34" s="9">
@@ -4290,47 +4287,47 @@
         <v>166.06250000003303</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" ref="AA34:AK34" si="64">AA22/AA21</f>
-        <v>0.13250055615343273</v>
+        <f t="shared" ref="AA34:AK34" si="60">AA22/AA21</f>
+        <v>0.23943957385692333</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AJ34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AK34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AN34" t="s">
@@ -4338,7 +4335,7 @@
       </c>
       <c r="AO34" s="5">
         <f>AO32+AO33</f>
-        <v>4636.8770819335095</v>
+        <v>3104.5008905832201</v>
       </c>
     </row>
     <row r="35" spans="2:41" x14ac:dyDescent="0.3">
@@ -4346,31 +4343,31 @@
         <v>27</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:M35" si="65">G23/G21</f>
+        <f t="shared" ref="G35:M35" si="61">G23/G21</f>
         <v>0.33333333333333365</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.3492537313432838</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.29324894514767957</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.25229357798165164</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.26421404682274297</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.29032258064516153</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>-8.8334133461353839E-2</v>
       </c>
       <c r="N35" s="9">
@@ -4378,20 +4375,20 @@
         <v>0.18775181305398864</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" ref="O35:R35" si="66">O23/O21</f>
+        <f t="shared" ref="O35:R35" si="62">O23/O21</f>
         <v>0.24561403508771912</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.12746858168761216</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="66"/>
-        <v>0.2</v>
+        <f t="shared" si="62"/>
+        <v>0.3371900826446273</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="66"/>
-        <v>0.2</v>
+        <f t="shared" si="62"/>
+        <v>0.5987074961700326</v>
       </c>
       <c r="Y35" s="9">
         <f>Y23/Y21</f>
@@ -4402,47 +4399,47 @@
         <v>-40.562500000008072</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" ref="AA35:AK35" si="67">AA23/AA21</f>
-        <v>0.18272144674897145</v>
+        <f t="shared" ref="AA35:AK35" si="63">AA23/AA21</f>
+        <v>0.31359518634481537</v>
       </c>
       <c r="AB35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AD35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AF35" s="9">
-        <f t="shared" si="67"/>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="63"/>
+        <v>0.17999999999999997</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AH35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="67"/>
-        <v>0.17999999999999997</v>
+        <f t="shared" si="63"/>
+        <v>0.18</v>
       </c>
       <c r="AJ35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AK35" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.18</v>
       </c>
       <c r="AN35" t="s">
@@ -4450,7 +4447,7 @@
       </c>
       <c r="AO35" s="4">
         <f>AO34/AK25</f>
-        <v>52.453360655356448</v>
+        <v>34.228234736308927</v>
       </c>
     </row>
     <row r="36" spans="2:41" x14ac:dyDescent="0.3">
@@ -4458,31 +4455,31 @@
         <v>55</v>
       </c>
       <c r="G36" s="9">
-        <f t="shared" ref="G36:M36" si="68">G24/G3</f>
+        <f t="shared" ref="G36:M36" si="64">G24/G3</f>
         <v>2.7056672760511855E-2</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>3.9403453689167936E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>4.8267693218833237E-2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.9421604763254854E-2</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>2.9120723777212261E-2</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>4.740024183796851E-2</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>5.9172899252089829E-2</v>
       </c>
       <c r="N36" s="9">
@@ -4490,20 +4487,20 @@
         <v>9.6505073280721609E-2</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" ref="O36:R36" si="69">O24/O3</f>
+        <f t="shared" ref="O36:R36" si="65">O24/O3</f>
         <v>1.9686431686903226E-2</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3.518940178016975E-2</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="69"/>
-        <v>4.4377621989709043E-2</v>
+        <f t="shared" si="65"/>
+        <v>1.1045968221599237E-2</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="69"/>
-        <v>4.1569668153521866E-2</v>
+        <f t="shared" si="65"/>
+        <v>7.1505198546912311E-3</v>
       </c>
       <c r="Y36" s="9">
         <f>Y24/Y3</f>
@@ -4514,55 +4511,55 @@
         <v>5.9809043415600879E-2</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" ref="AA36:AK36" si="70">AA24/AA3</f>
-        <v>3.5953304141871534E-2</v>
+        <f t="shared" ref="AA36:AK36" si="66">AA24/AA3</f>
+        <v>1.7251128591379585E-2</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="70"/>
-        <v>8.5145630708992448E-2</v>
+        <f t="shared" si="66"/>
+        <v>8.7730934681148856E-2</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.2411925558413141E-2</v>
+        <f t="shared" si="66"/>
+        <v>9.4130677747831321E-2</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.3733252741620796E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10233022268230767</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.4961139526131111E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10366712048768997</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.6102679092550769E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10484973640558905</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.7238586896604889E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10602627440210854</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.8369023463094105E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10719689841408823</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="70"/>
-        <v>9.9494149813616858E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.10836177282418304</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" si="70"/>
-        <v>0.10061412750165508</v>
+        <f t="shared" si="66"/>
+        <v>0.10952106249609637</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" si="70"/>
-        <v>0.10172911864809328</v>
+        <f t="shared" si="66"/>
+        <v>0.11067493281023989</v>
       </c>
       <c r="AN36" t="s">
         <v>62</v>
       </c>
       <c r="AO36" s="4">
         <f>Main!D3</f>
-        <v>79.099999999999994</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="37" spans="2:41" x14ac:dyDescent="0.3">
@@ -4571,7 +4568,7 @@
       </c>
       <c r="AO37" s="10">
         <f>AO35/AO36-1</f>
-        <v>-0.33687281093101828</v>
+        <v>-0.4883671937771461</v>
       </c>
     </row>
     <row r="38" spans="2:41" x14ac:dyDescent="0.3">
